--- a/Business Analysis/checkupp_sprint_plan_2026.xlsx
+++ b/Business Analysis/checkupp_sprint_plan_2026.xlsx
@@ -8,19 +8,21 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitHub\CheckUpp\Business Analysis\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C0F8B8C0-2E54-434B-8335-AFEC9F6EF476}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D9CE9CD9-6331-4BF6-A5C0-0B26EB142645}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="2" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sprint 01" sheetId="1" r:id="rId1"/>
     <sheet name="Sprint 01 Burndown" sheetId="4" r:id="rId2"/>
-    <sheet name="Sprint 02" sheetId="5" r:id="rId3"/>
+    <sheet name="Sprint 02" sheetId="7" r:id="rId3"/>
     <sheet name="Sprint 02 Burndown" sheetId="6" r:id="rId4"/>
+    <sheet name="Sprint 03" sheetId="5" r:id="rId5"/>
+    <sheet name="Sprint 03 Burndown" sheetId="8" r:id="rId6"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Sprint 01'!$E$1:$E$112</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Sprint 02'!$E$1:$E$110</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Sprint 03'!$E$1:$E$99</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -60,7 +62,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="322" uniqueCount="120">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="399" uniqueCount="132">
   <si>
     <t>Epic</t>
   </si>
@@ -5999,6 +6001,70 @@
 4. Auto-fill the extracted value directly into the **Weight (kg)** field without triggering secondary contextual modals.
 5. Implement the 10-second timeout fallback alert ("Having trouble reading the screen...").
 * **Acceptance Criteria Covered**: US 20.3 - Weight Scale (AC 1, 2, 3, 4, 5)</t>
+  </si>
+  <si>
+    <t>Native GCP Storage Integration &amp; Audit Logging
+Target: checkupp-api/src/modules/wallet/wallet.service.ts
+Native GCP Initialization: Implement the official @google-cloud/storage SDK using the new GCP_* environment variables, explicitly targeting the australia-southeast1 region bucket for onshore data sovereignty. Ensure firebase-admin/storage is completely removed.
+Raw Binary Buffer Streaming: In uploadPendingFile, process the incoming raw binary stream captured by express.raw() (eliminating multer), stream it directly into the standard GCP bucket with AES-256 encryption at rest, and generate/return a secure URL.
+Audit Compliance &amp; Cleanup: Ensure all uploads and deletions continue to pass through the controller-level tryCreateAuditLog wrapper. Completely remove obsolete local disk storage functions (fs.writeFile, fs.unlink), remove walletUploadsDir from configurations, and ensure the express.static block is deleted from src/app.ts.</t>
+  </si>
+  <si>
+    <t>Backend TDD: GCP &amp; Raw Binary Validation
+Target: checkupp-api/tests/modules/wallet/wallet.test.ts
+Mocking Storage: Initialize the Jest test suite using supertest. Mock the storage module to intercept bucket uploads and deletes without hitting the live network.
+Upload Assertions (US 6.1): Send a valid raw binary buffer payload to PUT /me/wallet/uploads/pending?objectKey=... (matching express.raw()). Assert a 201 response and verify the mocked bucket upload function is invoked.
+Deletion Assertions (US 6.3): DELETE /me/wallet/documents/:id. Assert a 200 OK response, verify the mocked bucket delete() method is called for physical documents, and confirm an immutable AuditLog row is written.</t>
+  </si>
+  <si>
+    <t>Offline-First Caching &amp; Native Viewers
+Scope: Frontend | Target: checkupp-mobile/components/wallet/WalletItemCard.tsx &amp; Viewers
+Smart Caching Layer: Refactor WalletItemCard.tsx to implement local caching checks against FileSystem.documentDirectory, downloading from the GCP URL only when the asset is missing.
+Native PDF Intents: Update DocumentViewer.tsx to completely remove react-native-webview, routing local file:// URIs through expo-sharing to launch the device's native PDF reader.
+Viewer Fallbacks: Implement a 5-second safety timeout inside ImageViewer.tsx to prevent infinite loading spinners if network latency spikes.</t>
+  </si>
+  <si>
+    <t>Smart Cache &amp; Native Sharing
+Target: checkupp-mobile/tests/wallet/walletCardInteractions.test.ts
+Mocking File System: Set up tests using @testing-library/react-native, mocking expo-file-system, expo-sharing, and expo-web-browser.
+Action Menu (US 6.3): Simulate pressing the 3-dot menu and assert that options render correctly ("View/Open", "Download" for documents, "Delete", "Cancel").
+Cross-Platform Sharing (US 6.2): Simulate pressing "Share". For e-scripts, assert native Share.share is invoked; for documents, verify FileSystem.getInfoAsync is checked before invoking Sharing.shareAsync.</t>
+  </si>
+  <si>
+    <t>Pregnancy</t>
+  </si>
+  <si>
+    <t>TDD-01: Extend Checkup Schema Validation (Backend)
+Target Files: src/modules/pregnancy/pregnancy.validation.ts, tests/modules/pregnancy/pregnancy.validation.test.ts (New)
+Description: Write unit tests verifying new payload flags (isConditional, isAlternative, isReferralOnly). Update checkupItemSchema to explicitly type these new fields while maintaining .unknown(true) backward compatibility.</t>
+  </si>
+  <si>
+    <t>Unit Tests for Milestone Calculation (Frontend)
+Target Files: test/Pregnancy/PregnancyCheckups.test.ts (New)
+Description: Write Jest tests asserting that calculateCheckupDates correctly generates the new 6-12 week batch (Early 75g OGTT, Cervical screening, Dating scan). Assert that alternative scan paths are correctly structured in the output array.</t>
+  </si>
+  <si>
+    <t>Update CHECKUP_META Data Structure (Frontend)
+Target Files: app/(tabs)/pregnancy-planner.tsx
+Description: Update the "Routine Blood &amp; Urine Tests" milestone in CHECKUP_META to explicitly list FBC, Rubella, Hep B/C, Syphilis, HIV, and MSU. Add new milestone objects for Cervical Screening, Early 75g OGTT, and the "Early Pregnancy Information" education block. Update the "Non-Invasive Prenatal Testing (NIPT)" and "First Trimester Screening (cFTS)" milestones to explicitly represent the "NIPS + Early Structural Ultrasound OR NT +/- cFTS" pathway.</t>
+  </si>
+  <si>
+    <t>UI Support for Conditional Milestones (Frontend)
+Target Files: app/(tabs)/pregnancy-planner.tsx
+Description: Modify the checklist rendering map function to display a visual "Conditional" badge for items like the "Dating scan (if LMP uncertain)". Add an "OR" visual separator between alternative screening paths (NIPS vs. NT scan) within the checklist UI. Update the "Influenza Vaccination" milestone to indicate "Anytime" rather than strictly week 14.</t>
+  </si>
+  <si>
+    <t>Update Educational Tips Content (Frontend)
+Target Files: components/PregnancyTips.tsx
+Description: Modify the pregnancyTips array objects for the 5-7 and 8-10 week ranges. Add explicitly required educational text: Covid-19 vaccine, Reproductive Carrier Screening, genetic counselling, CMV prevention, iodine/folic acid, pelvic floor exercises, and quitting smoking/alcohol.</t>
+  </si>
+  <si>
+    <t>Verify Calendar &amp; Reminder Sync (Frontend)
+Target Files: app/(tabs)/pregnancy-planner.tsx
+Description: Test the handleSave notification scheduling loop to ensure the newly added checkups correctly trigger addDatesToCalendar and scheduleNotifications. Ensure string-matching logic for getNotificationIdentifiersByTitles gracefully handles the longer, updated checklist names.</t>
+  </si>
+  <si>
+    <t>XL</t>
   </si>
 </sst>
 </file>
@@ -7225,6 +7291,518 @@
 </c:chartSpace>
 </file>
 
+<file path=xl/charts/chart3.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="en-US"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="en-IN"/>
+              <a:t>Sprint 02 - Burndown</a:t>
+            </a:r>
+            <a:r>
+              <a:rPr lang="en-IN" baseline="0"/>
+              <a:t> Chart</a:t>
+            </a:r>
+            <a:endParaRPr lang="en-IN"/>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-IN"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:lineChart>
+        <c:grouping val="standard"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'Sprint 03 Burndown'!$C$1</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Actual Story Points Left</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="28575" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:cat>
+            <c:numRef>
+              <c:f>'Sprint 03 Burndown'!$B$2:$B$10</c:f>
+              <c:numCache>
+                <c:formatCode>m/d/yyyy</c:formatCode>
+                <c:ptCount val="9"/>
+                <c:pt idx="0">
+                  <c:v>46272</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>46273</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>46274</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>46275</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>46276</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>46279</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>46280</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>46281</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>46282</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>'Sprint 03 Burndown'!$C$2:$C$10</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="9"/>
+                <c:pt idx="0">
+                  <c:v>44</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>44</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>44</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>31</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>18</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>18</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>18</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>18</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>18</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-8691-4B22-8ED6-2D07F6CFB302}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="1"/>
+          <c:order val="1"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'Sprint 03 Burndown'!$D$1</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Expected Story Points Left</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="28575" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent2"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:cat>
+            <c:numRef>
+              <c:f>'Sprint 03 Burndown'!$B$2:$B$10</c:f>
+              <c:numCache>
+                <c:formatCode>m/d/yyyy</c:formatCode>
+                <c:ptCount val="9"/>
+                <c:pt idx="0">
+                  <c:v>46272</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>46273</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>46274</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>46275</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>46276</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>46279</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>46280</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>46281</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>46282</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>'Sprint 03 Burndown'!$D$2:$D$10</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="9"/>
+                <c:pt idx="0">
+                  <c:v>44</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>38.5</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>33</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>27.5</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>22</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>16.5</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>11</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>5.5</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>0</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000001-8691-4B22-8ED6-2D07F6CFB302}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:smooth val="0"/>
+        <c:axId val="1501547104"/>
+        <c:axId val="1501322672"/>
+      </c:lineChart>
+      <c:catAx>
+        <c:axId val="1501547104"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="m/d/yyyy" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="25000"/>
+                <a:lumOff val="75000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1501322672"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="0"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="1501322672"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="25000"/>
+                <a:lumOff val="75000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1501547104"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="b"/>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:legend>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="en-US"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
 <file path=xl/charts/colors1.xml><?xml version="1.0" encoding="utf-8"?>
 <cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
   <a:schemeClr val="accent1"/>
@@ -7266,6 +7844,46 @@
 </file>
 
 <file path=xl/charts/colors2.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/colors3.xml><?xml version="1.0" encoding="utf-8"?>
 <cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
   <a:schemeClr val="accent1"/>
   <a:schemeClr val="accent2"/>
@@ -8337,6 +8955,522 @@
 </cs:chartStyle>
 </file>
 
+<file path=xl/charts/style3.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="240">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="75000"/>
+          <a:lumOff val="25000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="50000"/>
+            <a:lumOff val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
@@ -8403,6 +9537,49 @@
           </a:extLst>
         </xdr:cNvPr>
         <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing3.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>213360</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>167640</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>20</xdr:col>
+      <xdr:colOff>350520</xdr:colOff>
+      <xdr:row>22</xdr:row>
+      <xdr:rowOff>45720</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="2" name="Chart 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{F917FB92-B93B-42CC-81A6-86FDC094B383}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr>
+          <a:graphicFrameLocks/>
+        </xdr:cNvGraphicFramePr>
       </xdr:nvGraphicFramePr>
       <xdr:xfrm>
         <a:off x="0" y="0"/>
@@ -11243,8 +12420,7 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AA30D3B6-4BBC-427B-918A-C301767B692F}">
-  <sheetPr filterMode="1"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AE7CC14B-072D-418C-AC55-CBC1D249798C}">
   <dimension ref="A1:L110"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
@@ -11300,7 +12476,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="2" spans="1:12" ht="172.8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:12" ht="172.8" x14ac:dyDescent="0.3">
       <c r="A2" s="12">
         <v>1</v>
       </c>
@@ -11333,7 +12509,7 @@
       <c r="K2" s="12"/>
       <c r="L2" s="12"/>
     </row>
-    <row r="3" spans="1:12" ht="158.4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:12" ht="158.4" x14ac:dyDescent="0.3">
       <c r="A3" s="12">
         <v>2</v>
       </c>
@@ -11366,7 +12542,7 @@
       <c r="K3" s="12"/>
       <c r="L3" s="12"/>
     </row>
-    <row r="4" spans="1:12" ht="403.2" hidden="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:12" ht="403.2" x14ac:dyDescent="0.3">
       <c r="A4" s="12">
         <v>3</v>
       </c>
@@ -11397,7 +12573,7 @@
       <c r="K4" s="12"/>
       <c r="L4" s="12"/>
     </row>
-    <row r="5" spans="1:12" ht="409.6" hidden="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:12" ht="409.6" x14ac:dyDescent="0.3">
       <c r="A5" s="12">
         <v>4</v>
       </c>
@@ -11733,7 +12909,7 @@
       <c r="K14" s="14"/>
       <c r="L14" s="14"/>
     </row>
-    <row r="15" spans="1:12" ht="244.8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:12" ht="244.8" x14ac:dyDescent="0.3">
       <c r="A15" s="6">
         <v>14</v>
       </c>
@@ -11766,7 +12942,7 @@
       <c r="K15" s="6"/>
       <c r="L15" s="6"/>
     </row>
-    <row r="16" spans="1:12" ht="230.4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:12" ht="230.4" x14ac:dyDescent="0.3">
       <c r="A16" s="6">
         <v>15</v>
       </c>
@@ -11799,7 +12975,7 @@
       <c r="K16" s="6"/>
       <c r="L16" s="6"/>
     </row>
-    <row r="17" spans="1:12" ht="244.8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:12" ht="244.8" x14ac:dyDescent="0.3">
       <c r="A17" s="6">
         <v>16</v>
       </c>
@@ -11832,7 +13008,7 @@
       <c r="K17" s="6"/>
       <c r="L17" s="6"/>
     </row>
-    <row r="18" spans="1:12" ht="316.8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:12" ht="316.8" x14ac:dyDescent="0.3">
       <c r="A18" s="6">
         <v>17</v>
       </c>
@@ -11865,7 +13041,7 @@
       <c r="K18" s="6"/>
       <c r="L18" s="6"/>
     </row>
-    <row r="19" spans="1:12" ht="345.6" hidden="1" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:12" ht="345.6" x14ac:dyDescent="0.3">
       <c r="A19" s="6">
         <v>18</v>
       </c>
@@ -11898,7 +13074,7 @@
       <c r="K19" s="6"/>
       <c r="L19" s="6"/>
     </row>
-    <row r="20" spans="1:12" ht="409.6" hidden="1" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:12" ht="409.6" x14ac:dyDescent="0.3">
       <c r="A20" s="6">
         <v>19</v>
       </c>
@@ -11929,7 +13105,7 @@
       <c r="K20" s="6"/>
       <c r="L20" s="6"/>
     </row>
-    <row r="21" spans="1:12" ht="409.6" hidden="1" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:12" ht="409.6" x14ac:dyDescent="0.3">
       <c r="A21" s="6">
         <v>20</v>
       </c>
@@ -11960,7 +13136,7 @@
       <c r="K21" s="6"/>
       <c r="L21" s="6"/>
     </row>
-    <row r="22" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A22" s="6"/>
       <c r="B22" s="6"/>
       <c r="C22" s="6"/>
@@ -11974,7 +13150,7 @@
       <c r="K22" s="6"/>
       <c r="L22" s="6"/>
     </row>
-    <row r="23" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A23" s="6"/>
       <c r="B23" s="6"/>
       <c r="C23" s="6"/>
@@ -11988,7 +13164,7 @@
       <c r="K23" s="6"/>
       <c r="L23" s="6"/>
     </row>
-    <row r="24" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A24" s="6"/>
       <c r="B24" s="6"/>
       <c r="C24" s="6"/>
@@ -12005,7 +13181,7 @@
       <c r="K24" s="6"/>
       <c r="L24" s="6"/>
     </row>
-    <row r="25" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A25" s="6"/>
       <c r="B25" s="6"/>
       <c r="C25" s="6"/>
@@ -12022,7 +13198,7 @@
       <c r="K25" s="6"/>
       <c r="L25" s="6"/>
     </row>
-    <row r="26" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A26" s="6"/>
       <c r="B26" s="6"/>
       <c r="C26" s="6"/>
@@ -12039,7 +13215,7 @@
       <c r="K26" s="6"/>
       <c r="L26" s="6"/>
     </row>
-    <row r="27" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A27" s="6"/>
       <c r="B27" s="6"/>
       <c r="C27" s="6"/>
@@ -12056,7 +13232,7 @@
       <c r="K27" s="6"/>
       <c r="L27" s="6"/>
     </row>
-    <row r="28" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A28" s="6"/>
       <c r="B28" s="6"/>
       <c r="C28" s="6"/>
@@ -12073,7 +13249,7 @@
       <c r="K28" s="6"/>
       <c r="L28" s="6"/>
     </row>
-    <row r="29" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A29" s="6"/>
       <c r="B29" s="6"/>
       <c r="C29" s="6"/>
@@ -12090,7 +13266,7 @@
       <c r="K29" s="6"/>
       <c r="L29" s="6"/>
     </row>
-    <row r="30" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A30" s="6"/>
       <c r="B30" s="6"/>
       <c r="C30" s="6"/>
@@ -12107,7 +13283,7 @@
       <c r="K30" s="6"/>
       <c r="L30" s="6"/>
     </row>
-    <row r="31" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A31" s="6"/>
       <c r="B31" s="6"/>
       <c r="C31" s="6"/>
@@ -12124,7 +13300,7 @@
       <c r="K31" s="6"/>
       <c r="L31" s="6"/>
     </row>
-    <row r="32" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A32" s="6"/>
       <c r="B32" s="6"/>
       <c r="C32" s="6"/>
@@ -12141,7 +13317,7 @@
       <c r="K32" s="6"/>
       <c r="L32" s="6"/>
     </row>
-    <row r="33" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A33" s="6"/>
       <c r="B33" s="6"/>
       <c r="C33" s="6"/>
@@ -12158,7 +13334,7 @@
       <c r="K33" s="6"/>
       <c r="L33" s="6"/>
     </row>
-    <row r="34" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A34" s="6"/>
       <c r="B34" s="6"/>
       <c r="C34" s="6"/>
@@ -12175,7 +13351,7 @@
       <c r="K34" s="6"/>
       <c r="L34" s="6"/>
     </row>
-    <row r="35" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A35" s="6"/>
       <c r="B35" s="6"/>
       <c r="C35" s="6"/>
@@ -12192,7 +13368,7 @@
       <c r="K35" s="6"/>
       <c r="L35" s="6"/>
     </row>
-    <row r="36" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A36" s="6"/>
       <c r="B36" s="6"/>
       <c r="C36" s="6"/>
@@ -12209,7 +13385,7 @@
       <c r="K36" s="6"/>
       <c r="L36" s="6"/>
     </row>
-    <row r="37" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A37" s="6"/>
       <c r="B37" s="6"/>
       <c r="C37" s="6"/>
@@ -12226,7 +13402,7 @@
       <c r="K37" s="6"/>
       <c r="L37" s="6"/>
     </row>
-    <row r="38" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A38" s="6"/>
       <c r="B38" s="6"/>
       <c r="C38" s="6"/>
@@ -12243,7 +13419,7 @@
       <c r="K38" s="6"/>
       <c r="L38" s="6"/>
     </row>
-    <row r="39" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A39" s="6"/>
       <c r="B39" s="6"/>
       <c r="C39" s="6"/>
@@ -12260,7 +13436,7 @@
       <c r="K39" s="6"/>
       <c r="L39" s="6"/>
     </row>
-    <row r="40" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A40" s="6"/>
       <c r="B40" s="6"/>
       <c r="C40" s="6"/>
@@ -12277,7 +13453,7 @@
       <c r="K40" s="6"/>
       <c r="L40" s="6"/>
     </row>
-    <row r="41" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A41" s="6"/>
       <c r="B41" s="6"/>
       <c r="C41" s="6"/>
@@ -12294,7 +13470,7 @@
       <c r="K41" s="6"/>
       <c r="L41" s="6"/>
     </row>
-    <row r="42" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A42" s="6"/>
       <c r="B42" s="6"/>
       <c r="C42" s="6"/>
@@ -12311,7 +13487,7 @@
       <c r="K42" s="6"/>
       <c r="L42" s="6"/>
     </row>
-    <row r="43" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A43" s="6"/>
       <c r="B43" s="6"/>
       <c r="C43" s="6"/>
@@ -12328,7 +13504,7 @@
       <c r="K43" s="6"/>
       <c r="L43" s="6"/>
     </row>
-    <row r="44" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A44" s="6"/>
       <c r="B44" s="6"/>
       <c r="C44" s="6"/>
@@ -12345,7 +13521,7 @@
       <c r="K44" s="6"/>
       <c r="L44" s="6"/>
     </row>
-    <row r="45" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A45" s="6"/>
       <c r="B45" s="6"/>
       <c r="C45" s="6"/>
@@ -12362,7 +13538,7 @@
       <c r="K45" s="6"/>
       <c r="L45" s="6"/>
     </row>
-    <row r="46" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A46" s="6"/>
       <c r="B46" s="6"/>
       <c r="C46" s="6"/>
@@ -12379,7 +13555,7 @@
       <c r="K46" s="6"/>
       <c r="L46" s="6"/>
     </row>
-    <row r="47" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A47" s="6"/>
       <c r="B47" s="6"/>
       <c r="C47" s="6"/>
@@ -12396,7 +13572,7 @@
       <c r="K47" s="6"/>
       <c r="L47" s="6"/>
     </row>
-    <row r="48" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A48" s="6"/>
       <c r="B48" s="6"/>
       <c r="C48" s="6"/>
@@ -12413,7 +13589,7 @@
       <c r="K48" s="6"/>
       <c r="L48" s="6"/>
     </row>
-    <row r="49" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A49" s="6"/>
       <c r="B49" s="6"/>
       <c r="C49" s="6"/>
@@ -12430,7 +13606,7 @@
       <c r="K49" s="6"/>
       <c r="L49" s="6"/>
     </row>
-    <row r="50" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A50" s="6"/>
       <c r="B50" s="6"/>
       <c r="C50" s="6"/>
@@ -12447,7 +13623,7 @@
       <c r="K50" s="6"/>
       <c r="L50" s="6"/>
     </row>
-    <row r="51" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A51" s="6"/>
       <c r="B51" s="6"/>
       <c r="C51" s="6"/>
@@ -12464,7 +13640,7 @@
       <c r="K51" s="6"/>
       <c r="L51" s="6"/>
     </row>
-    <row r="52" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A52" s="6"/>
       <c r="B52" s="6"/>
       <c r="C52" s="6"/>
@@ -12481,7 +13657,7 @@
       <c r="K52" s="6"/>
       <c r="L52" s="6"/>
     </row>
-    <row r="53" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A53" s="6"/>
       <c r="B53" s="6"/>
       <c r="C53" s="6"/>
@@ -12498,7 +13674,7 @@
       <c r="K53" s="6"/>
       <c r="L53" s="6"/>
     </row>
-    <row r="54" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A54" s="6"/>
       <c r="B54" s="6"/>
       <c r="C54" s="6"/>
@@ -12515,7 +13691,7 @@
       <c r="K54" s="6"/>
       <c r="L54" s="6"/>
     </row>
-    <row r="55" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A55" s="6"/>
       <c r="B55" s="6"/>
       <c r="C55" s="6"/>
@@ -12532,7 +13708,7 @@
       <c r="K55" s="6"/>
       <c r="L55" s="6"/>
     </row>
-    <row r="56" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A56" s="6"/>
       <c r="B56" s="6"/>
       <c r="C56" s="6"/>
@@ -12549,7 +13725,7 @@
       <c r="K56" s="6"/>
       <c r="L56" s="6"/>
     </row>
-    <row r="57" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A57" s="6"/>
       <c r="B57" s="6"/>
       <c r="C57" s="6"/>
@@ -12566,7 +13742,7 @@
       <c r="K57" s="6"/>
       <c r="L57" s="6"/>
     </row>
-    <row r="58" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A58" s="6"/>
       <c r="B58" s="6"/>
       <c r="C58" s="6"/>
@@ -12583,7 +13759,7 @@
       <c r="K58" s="6"/>
       <c r="L58" s="6"/>
     </row>
-    <row r="59" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A59" s="6"/>
       <c r="B59" s="6"/>
       <c r="C59" s="6"/>
@@ -12600,7 +13776,7 @@
       <c r="K59" s="6"/>
       <c r="L59" s="6"/>
     </row>
-    <row r="60" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A60" s="6"/>
       <c r="B60" s="6"/>
       <c r="C60" s="6"/>
@@ -12617,7 +13793,7 @@
       <c r="K60" s="6"/>
       <c r="L60" s="6"/>
     </row>
-    <row r="61" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A61" s="6"/>
       <c r="B61" s="6"/>
       <c r="C61" s="6"/>
@@ -12634,7 +13810,7 @@
       <c r="K61" s="6"/>
       <c r="L61" s="6"/>
     </row>
-    <row r="62" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A62" s="6"/>
       <c r="B62" s="6"/>
       <c r="C62" s="6"/>
@@ -12651,7 +13827,7 @@
       <c r="K62" s="6"/>
       <c r="L62" s="6"/>
     </row>
-    <row r="63" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A63" s="6"/>
       <c r="B63" s="6"/>
       <c r="C63" s="6"/>
@@ -12668,7 +13844,7 @@
       <c r="K63" s="6"/>
       <c r="L63" s="6"/>
     </row>
-    <row r="64" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A64" s="6"/>
       <c r="B64" s="6"/>
       <c r="C64" s="6"/>
@@ -12685,7 +13861,7 @@
       <c r="K64" s="6"/>
       <c r="L64" s="6"/>
     </row>
-    <row r="65" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A65" s="6"/>
       <c r="B65" s="6"/>
       <c r="C65" s="6"/>
@@ -12702,7 +13878,7 @@
       <c r="K65" s="6"/>
       <c r="L65" s="6"/>
     </row>
-    <row r="66" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A66" s="6"/>
       <c r="B66" s="6"/>
       <c r="C66" s="6"/>
@@ -12719,7 +13895,7 @@
       <c r="K66" s="6"/>
       <c r="L66" s="6"/>
     </row>
-    <row r="67" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A67" s="6"/>
       <c r="B67" s="6"/>
       <c r="C67" s="6"/>
@@ -12736,7 +13912,7 @@
       <c r="K67" s="6"/>
       <c r="L67" s="6"/>
     </row>
-    <row r="68" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A68" s="6"/>
       <c r="B68" s="6"/>
       <c r="C68" s="6"/>
@@ -12753,7 +13929,7 @@
       <c r="K68" s="6"/>
       <c r="L68" s="6"/>
     </row>
-    <row r="69" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A69" s="6"/>
       <c r="B69" s="6"/>
       <c r="C69" s="6"/>
@@ -12770,7 +13946,7 @@
       <c r="K69" s="6"/>
       <c r="L69" s="6"/>
     </row>
-    <row r="70" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A70" s="6"/>
       <c r="B70" s="6"/>
       <c r="C70" s="6"/>
@@ -12787,7 +13963,7 @@
       <c r="K70" s="6"/>
       <c r="L70" s="6"/>
     </row>
-    <row r="71" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A71" s="6"/>
       <c r="B71" s="6"/>
       <c r="C71" s="6"/>
@@ -12804,7 +13980,7 @@
       <c r="K71" s="6"/>
       <c r="L71" s="6"/>
     </row>
-    <row r="72" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A72" s="6"/>
       <c r="B72" s="6"/>
       <c r="C72" s="6"/>
@@ -12821,7 +13997,7 @@
       <c r="K72" s="6"/>
       <c r="L72" s="6"/>
     </row>
-    <row r="73" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A73" s="6"/>
       <c r="B73" s="6"/>
       <c r="C73" s="6"/>
@@ -12838,7 +14014,7 @@
       <c r="K73" s="6"/>
       <c r="L73" s="6"/>
     </row>
-    <row r="74" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A74" s="6"/>
       <c r="B74" s="6"/>
       <c r="C74" s="6"/>
@@ -12855,7 +14031,7 @@
       <c r="K74" s="6"/>
       <c r="L74" s="6"/>
     </row>
-    <row r="75" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A75" s="6"/>
       <c r="B75" s="6"/>
       <c r="C75" s="6"/>
@@ -12872,7 +14048,7 @@
       <c r="K75" s="6"/>
       <c r="L75" s="6"/>
     </row>
-    <row r="76" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A76" s="6"/>
       <c r="B76" s="6"/>
       <c r="C76" s="6"/>
@@ -12889,7 +14065,7 @@
       <c r="K76" s="6"/>
       <c r="L76" s="6"/>
     </row>
-    <row r="77" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A77" s="6"/>
       <c r="B77" s="6"/>
       <c r="C77" s="6"/>
@@ -12906,7 +14082,7 @@
       <c r="K77" s="6"/>
       <c r="L77" s="6"/>
     </row>
-    <row r="78" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A78" s="6"/>
       <c r="B78" s="6"/>
       <c r="C78" s="6"/>
@@ -12923,7 +14099,7 @@
       <c r="K78" s="6"/>
       <c r="L78" s="6"/>
     </row>
-    <row r="79" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A79" s="6"/>
       <c r="B79" s="6"/>
       <c r="C79" s="6"/>
@@ -12940,7 +14116,7 @@
       <c r="K79" s="6"/>
       <c r="L79" s="6"/>
     </row>
-    <row r="80" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="80" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A80" s="6"/>
       <c r="B80" s="6"/>
       <c r="C80" s="6"/>
@@ -12957,7 +14133,7 @@
       <c r="K80" s="6"/>
       <c r="L80" s="6"/>
     </row>
-    <row r="81" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="81" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A81" s="6"/>
       <c r="B81" s="6"/>
       <c r="C81" s="6"/>
@@ -12974,7 +14150,7 @@
       <c r="K81" s="6"/>
       <c r="L81" s="6"/>
     </row>
-    <row r="82" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="82" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A82" s="6"/>
       <c r="B82" s="6"/>
       <c r="C82" s="6"/>
@@ -12991,7 +14167,7 @@
       <c r="K82" s="6"/>
       <c r="L82" s="6"/>
     </row>
-    <row r="83" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="83" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A83" s="6"/>
       <c r="B83" s="6"/>
       <c r="C83" s="6"/>
@@ -13008,7 +14184,7 @@
       <c r="K83" s="6"/>
       <c r="L83" s="6"/>
     </row>
-    <row r="84" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="84" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A84" s="6"/>
       <c r="B84" s="6"/>
       <c r="C84" s="6"/>
@@ -13025,7 +14201,7 @@
       <c r="K84" s="6"/>
       <c r="L84" s="6"/>
     </row>
-    <row r="85" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="85" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A85" s="6"/>
       <c r="B85" s="6"/>
       <c r="C85" s="6"/>
@@ -13042,7 +14218,7 @@
       <c r="K85" s="6"/>
       <c r="L85" s="6"/>
     </row>
-    <row r="86" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="86" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A86" s="6"/>
       <c r="B86" s="6"/>
       <c r="C86" s="6"/>
@@ -13059,7 +14235,7 @@
       <c r="K86" s="6"/>
       <c r="L86" s="6"/>
     </row>
-    <row r="87" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="87" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A87" s="6"/>
       <c r="B87" s="6"/>
       <c r="C87" s="6"/>
@@ -13076,7 +14252,7 @@
       <c r="K87" s="6"/>
       <c r="L87" s="6"/>
     </row>
-    <row r="88" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="88" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A88" s="6"/>
       <c r="B88" s="6"/>
       <c r="C88" s="6"/>
@@ -13093,7 +14269,7 @@
       <c r="K88" s="6"/>
       <c r="L88" s="6"/>
     </row>
-    <row r="89" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="89" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A89" s="6"/>
       <c r="B89" s="6"/>
       <c r="C89" s="6"/>
@@ -13110,7 +14286,7 @@
       <c r="K89" s="6"/>
       <c r="L89" s="6"/>
     </row>
-    <row r="90" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="90" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A90" s="6"/>
       <c r="B90" s="6"/>
       <c r="C90" s="6"/>
@@ -13127,7 +14303,7 @@
       <c r="K90" s="6"/>
       <c r="L90" s="6"/>
     </row>
-    <row r="91" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="91" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A91" s="6"/>
       <c r="B91" s="6"/>
       <c r="C91" s="6"/>
@@ -13144,7 +14320,7 @@
       <c r="K91" s="6"/>
       <c r="L91" s="6"/>
     </row>
-    <row r="92" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="92" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A92" s="6"/>
       <c r="B92" s="6"/>
       <c r="C92" s="6"/>
@@ -13161,7 +14337,7 @@
       <c r="K92" s="6"/>
       <c r="L92" s="6"/>
     </row>
-    <row r="93" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="93" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A93" s="6"/>
       <c r="B93" s="6"/>
       <c r="C93" s="6"/>
@@ -13178,7 +14354,7 @@
       <c r="K93" s="6"/>
       <c r="L93" s="6"/>
     </row>
-    <row r="94" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="94" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A94" s="6"/>
       <c r="B94" s="6"/>
       <c r="C94" s="6"/>
@@ -13195,7 +14371,7 @@
       <c r="K94" s="6"/>
       <c r="L94" s="6"/>
     </row>
-    <row r="95" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="95" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A95" s="6"/>
       <c r="B95" s="6"/>
       <c r="C95" s="6"/>
@@ -13212,7 +14388,7 @@
       <c r="K95" s="6"/>
       <c r="L95" s="6"/>
     </row>
-    <row r="96" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="96" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A96" s="6"/>
       <c r="B96" s="6"/>
       <c r="C96" s="6"/>
@@ -13229,7 +14405,7 @@
       <c r="K96" s="6"/>
       <c r="L96" s="6"/>
     </row>
-    <row r="97" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="97" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A97" s="6"/>
       <c r="B97" s="6"/>
       <c r="C97" s="6"/>
@@ -13246,7 +14422,7 @@
       <c r="K97" s="6"/>
       <c r="L97" s="6"/>
     </row>
-    <row r="98" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="98" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A98" s="6"/>
       <c r="B98" s="6"/>
       <c r="C98" s="6"/>
@@ -13263,7 +14439,7 @@
       <c r="K98" s="6"/>
       <c r="L98" s="6"/>
     </row>
-    <row r="99" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="99" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A99" s="6"/>
       <c r="B99" s="6"/>
       <c r="C99" s="6"/>
@@ -13280,7 +14456,7 @@
       <c r="K99" s="6"/>
       <c r="L99" s="6"/>
     </row>
-    <row r="100" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="100" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A100" s="6"/>
       <c r="B100" s="6"/>
       <c r="C100" s="6"/>
@@ -13297,7 +14473,7 @@
       <c r="K100" s="6"/>
       <c r="L100" s="6"/>
     </row>
-    <row r="101" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="101" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A101" s="6"/>
       <c r="B101" s="6"/>
       <c r="C101" s="6"/>
@@ -13314,7 +14490,7 @@
       <c r="K101" s="6"/>
       <c r="L101" s="6"/>
     </row>
-    <row r="102" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="102" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A102" s="6"/>
       <c r="B102" s="6"/>
       <c r="C102" s="6"/>
@@ -13331,7 +14507,7 @@
       <c r="K102" s="6"/>
       <c r="L102" s="6"/>
     </row>
-    <row r="103" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="103" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A103" s="6"/>
       <c r="B103" s="6"/>
       <c r="C103" s="6"/>
@@ -13348,7 +14524,7 @@
       <c r="K103" s="6"/>
       <c r="L103" s="6"/>
     </row>
-    <row r="104" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="104" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A104" s="6"/>
       <c r="B104" s="6"/>
       <c r="C104" s="6"/>
@@ -13365,7 +14541,7 @@
       <c r="K104" s="6"/>
       <c r="L104" s="6"/>
     </row>
-    <row r="105" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="105" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A105" s="6"/>
       <c r="B105" s="6"/>
       <c r="C105" s="6"/>
@@ -13382,7 +14558,7 @@
       <c r="K105" s="6"/>
       <c r="L105" s="6"/>
     </row>
-    <row r="106" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="106" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A106" s="6"/>
       <c r="B106" s="6"/>
       <c r="C106" s="6"/>
@@ -13399,7 +14575,7 @@
       <c r="K106" s="6"/>
       <c r="L106" s="6"/>
     </row>
-    <row r="107" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="107" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A107" s="6"/>
       <c r="B107" s="6"/>
       <c r="C107" s="6"/>
@@ -13416,7 +14592,7 @@
       <c r="K107" s="6"/>
       <c r="L107" s="6"/>
     </row>
-    <row r="108" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="108" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A108" s="6"/>
       <c r="B108" s="6"/>
       <c r="C108" s="6"/>
@@ -13433,7 +14609,7 @@
       <c r="K108" s="6"/>
       <c r="L108" s="6"/>
     </row>
-    <row r="109" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="109" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A109" s="6"/>
       <c r="B109" s="6"/>
       <c r="C109" s="6"/>
@@ -13450,7 +14626,7 @@
       <c r="K109" s="6"/>
       <c r="L109" s="6"/>
     </row>
-    <row r="110" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="110" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A110" s="6"/>
       <c r="B110" s="6"/>
       <c r="C110" s="6"/>
@@ -13468,15 +14644,6 @@
       <c r="L110" s="6"/>
     </row>
   </sheetData>
-  <autoFilter ref="E1:E110" xr:uid="{AA30D3B6-4BBC-427B-918A-C301767B692F}">
-    <filterColumn colId="0">
-      <filters>
-        <filter val="Backend"/>
-        <filter val="Frontend"/>
-      </filters>
-    </filterColumn>
-  </autoFilter>
-  <phoneticPr fontId="4" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -13686,4 +14853,2069 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AA30D3B6-4BBC-427B-918A-C301767B692F}">
+  <dimension ref="A1:L99"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="6.88671875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="13.109375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="7.44140625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11.109375" customWidth="1"/>
+    <col min="5" max="5" width="8.33203125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="99.44140625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="8" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="7.109375" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="6" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="6.77734375" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="8" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="5.77734375" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:12" ht="46.8" x14ac:dyDescent="0.3">
+      <c r="A1" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="B1" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" s="4" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1" s="4" t="s">
+        <v>2</v>
+      </c>
+      <c r="E1" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="F1" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="G1" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="H1" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="I1" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="K1" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="L1" s="4" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2" spans="1:12" ht="201.6" x14ac:dyDescent="0.3">
+      <c r="A2" s="12">
+        <v>1</v>
+      </c>
+      <c r="B2" s="12" t="s">
+        <v>94</v>
+      </c>
+      <c r="C2" s="12"/>
+      <c r="D2" s="12"/>
+      <c r="E2" s="12" t="s">
+        <v>22</v>
+      </c>
+      <c r="F2" s="13" t="s">
+        <v>120</v>
+      </c>
+      <c r="G2" s="12" t="s">
+        <v>24</v>
+      </c>
+      <c r="H2" s="12" t="s">
+        <v>131</v>
+      </c>
+      <c r="I2" s="12">
+        <f t="array" ref="I2">_xlfn.SWITCH(H2,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
+        <v>8</v>
+      </c>
+      <c r="J2" s="12" t="s">
+        <v>75</v>
+      </c>
+      <c r="K2" s="12"/>
+      <c r="L2" s="12"/>
+    </row>
+    <row r="3" spans="1:12" ht="172.8" x14ac:dyDescent="0.3">
+      <c r="A3" s="12">
+        <v>2</v>
+      </c>
+      <c r="B3" s="12" t="s">
+        <v>94</v>
+      </c>
+      <c r="C3" s="12"/>
+      <c r="D3" s="12"/>
+      <c r="E3" s="12" t="s">
+        <v>31</v>
+      </c>
+      <c r="F3" s="13" t="s">
+        <v>121</v>
+      </c>
+      <c r="G3" s="12" t="s">
+        <v>24</v>
+      </c>
+      <c r="H3" s="12" t="s">
+        <v>30</v>
+      </c>
+      <c r="I3" s="12">
+        <f t="array" ref="I3">_xlfn.SWITCH(H3,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
+        <v>5</v>
+      </c>
+      <c r="J3" s="12" t="s">
+        <v>75</v>
+      </c>
+      <c r="K3" s="12"/>
+      <c r="L3" s="12"/>
+    </row>
+    <row r="4" spans="1:12" ht="172.8" x14ac:dyDescent="0.3">
+      <c r="A4" s="12">
+        <v>3</v>
+      </c>
+      <c r="B4" s="12" t="s">
+        <v>94</v>
+      </c>
+      <c r="C4" s="12"/>
+      <c r="D4" s="12"/>
+      <c r="E4" s="12" t="s">
+        <v>20</v>
+      </c>
+      <c r="F4" s="13" t="s">
+        <v>122</v>
+      </c>
+      <c r="G4" s="12" t="s">
+        <v>24</v>
+      </c>
+      <c r="H4" s="12" t="s">
+        <v>131</v>
+      </c>
+      <c r="I4" s="12">
+        <f t="array" ref="I4">_xlfn.SWITCH(H4,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
+        <v>8</v>
+      </c>
+      <c r="J4" s="12" t="s">
+        <v>75</v>
+      </c>
+      <c r="K4" s="12"/>
+      <c r="L4" s="12"/>
+    </row>
+    <row r="5" spans="1:12" ht="172.8" x14ac:dyDescent="0.3">
+      <c r="A5" s="12">
+        <v>4</v>
+      </c>
+      <c r="B5" s="12" t="s">
+        <v>94</v>
+      </c>
+      <c r="C5" s="12"/>
+      <c r="D5" s="12"/>
+      <c r="E5" s="12" t="s">
+        <v>31</v>
+      </c>
+      <c r="F5" s="13" t="s">
+        <v>123</v>
+      </c>
+      <c r="G5" s="12" t="s">
+        <v>24</v>
+      </c>
+      <c r="H5" s="12" t="s">
+        <v>30</v>
+      </c>
+      <c r="I5" s="12">
+        <f t="array" ref="I5">_xlfn.SWITCH(H5,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
+        <v>5</v>
+      </c>
+      <c r="J5" s="12" t="s">
+        <v>75</v>
+      </c>
+      <c r="K5" s="12"/>
+      <c r="L5" s="12"/>
+    </row>
+    <row r="6" spans="1:12" ht="100.8" x14ac:dyDescent="0.3">
+      <c r="A6" s="14">
+        <v>5</v>
+      </c>
+      <c r="B6" s="14" t="s">
+        <v>124</v>
+      </c>
+      <c r="C6" s="14"/>
+      <c r="D6" s="14"/>
+      <c r="E6" s="14" t="s">
+        <v>22</v>
+      </c>
+      <c r="F6" s="15" t="s">
+        <v>125</v>
+      </c>
+      <c r="G6" s="14" t="s">
+        <v>29</v>
+      </c>
+      <c r="H6" s="14" t="s">
+        <v>30</v>
+      </c>
+      <c r="I6" s="14">
+        <f t="array" ref="I6">_xlfn.SWITCH(H6,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
+        <v>5</v>
+      </c>
+      <c r="J6" s="14" t="s">
+        <v>76</v>
+      </c>
+      <c r="K6" s="14"/>
+      <c r="L6" s="14"/>
+    </row>
+    <row r="7" spans="1:12" ht="100.8" x14ac:dyDescent="0.3">
+      <c r="A7" s="14">
+        <v>6</v>
+      </c>
+      <c r="B7" s="14" t="s">
+        <v>124</v>
+      </c>
+      <c r="C7" s="14"/>
+      <c r="D7" s="14"/>
+      <c r="E7" s="14" t="s">
+        <v>31</v>
+      </c>
+      <c r="F7" s="15" t="s">
+        <v>126</v>
+      </c>
+      <c r="G7" s="14" t="s">
+        <v>29</v>
+      </c>
+      <c r="H7" s="14" t="s">
+        <v>23</v>
+      </c>
+      <c r="I7" s="14">
+        <f t="array" ref="I7">_xlfn.SWITCH(H7,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
+        <v>2</v>
+      </c>
+      <c r="J7" s="14" t="s">
+        <v>76</v>
+      </c>
+      <c r="K7" s="14"/>
+      <c r="L7" s="14"/>
+    </row>
+    <row r="8" spans="1:12" ht="115.2" x14ac:dyDescent="0.3">
+      <c r="A8" s="14">
+        <v>7</v>
+      </c>
+      <c r="B8" s="14" t="s">
+        <v>124</v>
+      </c>
+      <c r="C8" s="14"/>
+      <c r="D8" s="14"/>
+      <c r="E8" s="14" t="s">
+        <v>20</v>
+      </c>
+      <c r="F8" s="15" t="s">
+        <v>127</v>
+      </c>
+      <c r="G8" s="14" t="s">
+        <v>29</v>
+      </c>
+      <c r="H8" s="14" t="s">
+        <v>27</v>
+      </c>
+      <c r="I8" s="14">
+        <f t="array" ref="I8">_xlfn.SWITCH(H8,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
+        <v>3</v>
+      </c>
+      <c r="J8" s="14" t="s">
+        <v>76</v>
+      </c>
+      <c r="K8" s="14"/>
+      <c r="L8" s="14"/>
+    </row>
+    <row r="9" spans="1:12" ht="115.2" x14ac:dyDescent="0.3">
+      <c r="A9" s="14">
+        <v>8</v>
+      </c>
+      <c r="B9" s="14" t="s">
+        <v>124</v>
+      </c>
+      <c r="C9" s="14"/>
+      <c r="D9" s="14"/>
+      <c r="E9" s="14" t="s">
+        <v>20</v>
+      </c>
+      <c r="F9" s="15" t="s">
+        <v>128</v>
+      </c>
+      <c r="G9" s="14" t="s">
+        <v>29</v>
+      </c>
+      <c r="H9" s="14" t="s">
+        <v>30</v>
+      </c>
+      <c r="I9" s="14">
+        <f t="array" ref="I9">_xlfn.SWITCH(H9,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
+        <v>5</v>
+      </c>
+      <c r="J9" s="14" t="s">
+        <v>76</v>
+      </c>
+      <c r="K9" s="14"/>
+      <c r="L9" s="14"/>
+    </row>
+    <row r="10" spans="1:12" ht="100.8" x14ac:dyDescent="0.3">
+      <c r="A10" s="14">
+        <v>9</v>
+      </c>
+      <c r="B10" s="14" t="s">
+        <v>124</v>
+      </c>
+      <c r="C10" s="14"/>
+      <c r="D10" s="14"/>
+      <c r="E10" s="14" t="s">
+        <v>20</v>
+      </c>
+      <c r="F10" s="15" t="s">
+        <v>129</v>
+      </c>
+      <c r="G10" s="14" t="s">
+        <v>29</v>
+      </c>
+      <c r="H10" s="14" t="s">
+        <v>23</v>
+      </c>
+      <c r="I10" s="14">
+        <f t="array" ref="I10">_xlfn.SWITCH(H10,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
+        <v>2</v>
+      </c>
+      <c r="J10" s="14" t="s">
+        <v>76</v>
+      </c>
+      <c r="K10" s="14"/>
+      <c r="L10" s="14"/>
+    </row>
+    <row r="11" spans="1:12" ht="100.8" x14ac:dyDescent="0.3">
+      <c r="A11" s="14">
+        <v>10</v>
+      </c>
+      <c r="B11" s="14" t="s">
+        <v>124</v>
+      </c>
+      <c r="C11" s="14"/>
+      <c r="D11" s="14"/>
+      <c r="E11" s="14" t="s">
+        <v>20</v>
+      </c>
+      <c r="F11" s="15" t="s">
+        <v>130</v>
+      </c>
+      <c r="G11" s="14" t="s">
+        <v>29</v>
+      </c>
+      <c r="H11" s="14" t="s">
+        <v>19</v>
+      </c>
+      <c r="I11" s="14">
+        <f t="array" ref="I11">_xlfn.SWITCH(H11,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
+        <v>1</v>
+      </c>
+      <c r="J11" s="14" t="s">
+        <v>76</v>
+      </c>
+      <c r="K11" s="14"/>
+      <c r="L11" s="14"/>
+    </row>
+    <row r="12" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A12" s="6"/>
+      <c r="B12" s="6"/>
+      <c r="C12" s="6"/>
+      <c r="D12" s="6"/>
+      <c r="E12" s="6"/>
+      <c r="F12" s="8"/>
+      <c r="G12" s="6"/>
+      <c r="H12" s="6"/>
+      <c r="I12" s="6"/>
+      <c r="J12" s="6"/>
+      <c r="K12" s="6"/>
+      <c r="L12" s="6"/>
+    </row>
+    <row r="13" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A13" s="6"/>
+      <c r="B13" s="6"/>
+      <c r="C13" s="6"/>
+      <c r="D13" s="6"/>
+      <c r="E13" s="6"/>
+      <c r="F13" s="8"/>
+      <c r="G13" s="6"/>
+      <c r="H13" s="6"/>
+      <c r="I13" s="6" t="str">
+        <f t="array" ref="I13">_xlfn.SWITCH(H13,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
+        <v/>
+      </c>
+      <c r="J13" s="6"/>
+      <c r="K13" s="6"/>
+      <c r="L13" s="6"/>
+    </row>
+    <row r="14" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A14" s="6"/>
+      <c r="B14" s="6"/>
+      <c r="C14" s="6"/>
+      <c r="D14" s="6"/>
+      <c r="E14" s="6"/>
+      <c r="F14" s="8"/>
+      <c r="G14" s="6"/>
+      <c r="H14" s="6"/>
+      <c r="I14" s="6" t="str">
+        <f t="array" ref="I14">_xlfn.SWITCH(H14,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
+        <v/>
+      </c>
+      <c r="J14" s="6"/>
+      <c r="K14" s="6"/>
+      <c r="L14" s="6"/>
+    </row>
+    <row r="15" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A15" s="6"/>
+      <c r="B15" s="6"/>
+      <c r="C15" s="6"/>
+      <c r="D15" s="6"/>
+      <c r="E15" s="6"/>
+      <c r="F15" s="8"/>
+      <c r="G15" s="6"/>
+      <c r="H15" s="6"/>
+      <c r="I15" s="6" t="str">
+        <f t="array" ref="I15">_xlfn.SWITCH(H15,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
+        <v/>
+      </c>
+      <c r="J15" s="6"/>
+      <c r="K15" s="6"/>
+      <c r="L15" s="6"/>
+    </row>
+    <row r="16" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A16" s="6"/>
+      <c r="B16" s="6"/>
+      <c r="C16" s="6"/>
+      <c r="D16" s="6"/>
+      <c r="E16" s="6"/>
+      <c r="F16" s="8"/>
+      <c r="G16" s="6"/>
+      <c r="H16" s="6"/>
+      <c r="I16" s="6" t="str">
+        <f t="array" ref="I16">_xlfn.SWITCH(H16,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
+        <v/>
+      </c>
+      <c r="J16" s="6"/>
+      <c r="K16" s="6"/>
+      <c r="L16" s="6"/>
+    </row>
+    <row r="17" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A17" s="6"/>
+      <c r="B17" s="6"/>
+      <c r="C17" s="6"/>
+      <c r="D17" s="6"/>
+      <c r="E17" s="6"/>
+      <c r="F17" s="8"/>
+      <c r="G17" s="6"/>
+      <c r="H17" s="6"/>
+      <c r="I17" s="6" t="str">
+        <f t="array" ref="I17">_xlfn.SWITCH(H17,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
+        <v/>
+      </c>
+      <c r="J17" s="6"/>
+      <c r="K17" s="6"/>
+      <c r="L17" s="6"/>
+    </row>
+    <row r="18" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A18" s="6"/>
+      <c r="B18" s="6"/>
+      <c r="C18" s="6"/>
+      <c r="D18" s="6"/>
+      <c r="E18" s="6"/>
+      <c r="F18" s="8"/>
+      <c r="G18" s="6"/>
+      <c r="H18" s="6"/>
+      <c r="I18" s="6" t="str">
+        <f t="array" ref="I18">_xlfn.SWITCH(H18,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
+        <v/>
+      </c>
+      <c r="J18" s="6"/>
+      <c r="K18" s="6"/>
+      <c r="L18" s="6"/>
+    </row>
+    <row r="19" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A19" s="6"/>
+      <c r="B19" s="6"/>
+      <c r="C19" s="6"/>
+      <c r="D19" s="6"/>
+      <c r="E19" s="6"/>
+      <c r="F19" s="8"/>
+      <c r="G19" s="6"/>
+      <c r="H19" s="6"/>
+      <c r="I19" s="6" t="str">
+        <f t="array" ref="I19">_xlfn.SWITCH(H19,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
+        <v/>
+      </c>
+      <c r="J19" s="6"/>
+      <c r="K19" s="6"/>
+      <c r="L19" s="6"/>
+    </row>
+    <row r="20" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A20" s="6"/>
+      <c r="B20" s="6"/>
+      <c r="C20" s="6"/>
+      <c r="D20" s="6"/>
+      <c r="E20" s="6"/>
+      <c r="F20" s="5"/>
+      <c r="G20" s="6"/>
+      <c r="H20" s="6"/>
+      <c r="I20" s="6" t="str">
+        <f t="array" ref="I20">_xlfn.SWITCH(H20,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
+        <v/>
+      </c>
+      <c r="J20" s="6"/>
+      <c r="K20" s="6"/>
+      <c r="L20" s="6"/>
+    </row>
+    <row r="21" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A21" s="6"/>
+      <c r="B21" s="6"/>
+      <c r="C21" s="6"/>
+      <c r="D21" s="6"/>
+      <c r="E21" s="6"/>
+      <c r="F21" s="7"/>
+      <c r="G21" s="6"/>
+      <c r="H21" s="6"/>
+      <c r="I21" s="6" t="str">
+        <f t="array" ref="I21">_xlfn.SWITCH(H21,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
+        <v/>
+      </c>
+      <c r="J21" s="6"/>
+      <c r="K21" s="6"/>
+      <c r="L21" s="6"/>
+    </row>
+    <row r="22" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A22" s="6"/>
+      <c r="B22" s="6"/>
+      <c r="C22" s="6"/>
+      <c r="D22" s="6"/>
+      <c r="E22" s="6"/>
+      <c r="F22" s="7"/>
+      <c r="G22" s="6"/>
+      <c r="H22" s="6"/>
+      <c r="I22" s="6" t="str">
+        <f t="array" ref="I22">_xlfn.SWITCH(H22,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
+        <v/>
+      </c>
+      <c r="J22" s="6"/>
+      <c r="K22" s="6"/>
+      <c r="L22" s="6"/>
+    </row>
+    <row r="23" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A23" s="6"/>
+      <c r="B23" s="6"/>
+      <c r="C23" s="6"/>
+      <c r="D23" s="6"/>
+      <c r="E23" s="6"/>
+      <c r="F23" s="7"/>
+      <c r="G23" s="6"/>
+      <c r="H23" s="6"/>
+      <c r="I23" s="6" t="str">
+        <f t="array" ref="I23">_xlfn.SWITCH(H23,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
+        <v/>
+      </c>
+      <c r="J23" s="6"/>
+      <c r="K23" s="6"/>
+      <c r="L23" s="6"/>
+    </row>
+    <row r="24" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A24" s="6"/>
+      <c r="B24" s="6"/>
+      <c r="C24" s="6"/>
+      <c r="D24" s="6"/>
+      <c r="E24" s="6"/>
+      <c r="F24" s="7"/>
+      <c r="G24" s="6"/>
+      <c r="H24" s="6"/>
+      <c r="I24" s="6" t="str">
+        <f t="array" ref="I24">_xlfn.SWITCH(H24,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
+        <v/>
+      </c>
+      <c r="J24" s="6"/>
+      <c r="K24" s="6"/>
+      <c r="L24" s="6"/>
+    </row>
+    <row r="25" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A25" s="6"/>
+      <c r="B25" s="6"/>
+      <c r="C25" s="6"/>
+      <c r="D25" s="6"/>
+      <c r="E25" s="6"/>
+      <c r="F25" s="7"/>
+      <c r="G25" s="6"/>
+      <c r="H25" s="6"/>
+      <c r="I25" s="6" t="str">
+        <f t="array" ref="I25">_xlfn.SWITCH(H25,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
+        <v/>
+      </c>
+      <c r="J25" s="6"/>
+      <c r="K25" s="6"/>
+      <c r="L25" s="6"/>
+    </row>
+    <row r="26" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A26" s="6"/>
+      <c r="B26" s="6"/>
+      <c r="C26" s="6"/>
+      <c r="D26" s="6"/>
+      <c r="E26" s="6"/>
+      <c r="F26" s="7"/>
+      <c r="G26" s="6"/>
+      <c r="H26" s="6"/>
+      <c r="I26" s="6" t="str">
+        <f t="array" ref="I26">_xlfn.SWITCH(H26,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
+        <v/>
+      </c>
+      <c r="J26" s="6"/>
+      <c r="K26" s="6"/>
+      <c r="L26" s="6"/>
+    </row>
+    <row r="27" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A27" s="6"/>
+      <c r="B27" s="6"/>
+      <c r="C27" s="6"/>
+      <c r="D27" s="6"/>
+      <c r="E27" s="6"/>
+      <c r="F27" s="7"/>
+      <c r="G27" s="6"/>
+      <c r="H27" s="6"/>
+      <c r="I27" s="6" t="str">
+        <f t="array" ref="I27">_xlfn.SWITCH(H27,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
+        <v/>
+      </c>
+      <c r="J27" s="6"/>
+      <c r="K27" s="6"/>
+      <c r="L27" s="6"/>
+    </row>
+    <row r="28" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A28" s="6"/>
+      <c r="B28" s="6"/>
+      <c r="C28" s="6"/>
+      <c r="D28" s="6"/>
+      <c r="E28" s="6"/>
+      <c r="F28" s="7"/>
+      <c r="G28" s="6"/>
+      <c r="H28" s="6"/>
+      <c r="I28" s="6" t="str">
+        <f t="array" ref="I28">_xlfn.SWITCH(H28,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
+        <v/>
+      </c>
+      <c r="J28" s="6"/>
+      <c r="K28" s="6"/>
+      <c r="L28" s="6"/>
+    </row>
+    <row r="29" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A29" s="6"/>
+      <c r="B29" s="6"/>
+      <c r="C29" s="6"/>
+      <c r="D29" s="6"/>
+      <c r="E29" s="6"/>
+      <c r="F29" s="7"/>
+      <c r="G29" s="6"/>
+      <c r="H29" s="6"/>
+      <c r="I29" s="6" t="str">
+        <f t="array" ref="I29">_xlfn.SWITCH(H29,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
+        <v/>
+      </c>
+      <c r="J29" s="6"/>
+      <c r="K29" s="6"/>
+      <c r="L29" s="6"/>
+    </row>
+    <row r="30" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A30" s="6"/>
+      <c r="B30" s="6"/>
+      <c r="C30" s="6"/>
+      <c r="D30" s="6"/>
+      <c r="E30" s="6"/>
+      <c r="F30" s="7"/>
+      <c r="G30" s="6"/>
+      <c r="H30" s="6"/>
+      <c r="I30" s="6" t="str">
+        <f t="array" ref="I30">_xlfn.SWITCH(H30,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
+        <v/>
+      </c>
+      <c r="J30" s="6"/>
+      <c r="K30" s="6"/>
+      <c r="L30" s="6"/>
+    </row>
+    <row r="31" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A31" s="6"/>
+      <c r="B31" s="6"/>
+      <c r="C31" s="6"/>
+      <c r="D31" s="6"/>
+      <c r="E31" s="6"/>
+      <c r="F31" s="7"/>
+      <c r="G31" s="6"/>
+      <c r="H31" s="6"/>
+      <c r="I31" s="6" t="str">
+        <f t="array" ref="I31">_xlfn.SWITCH(H31,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
+        <v/>
+      </c>
+      <c r="J31" s="6"/>
+      <c r="K31" s="6"/>
+      <c r="L31" s="6"/>
+    </row>
+    <row r="32" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A32" s="6"/>
+      <c r="B32" s="6"/>
+      <c r="C32" s="6"/>
+      <c r="D32" s="6"/>
+      <c r="E32" s="6"/>
+      <c r="F32" s="7"/>
+      <c r="G32" s="6"/>
+      <c r="H32" s="6"/>
+      <c r="I32" s="6" t="str">
+        <f t="array" ref="I32">_xlfn.SWITCH(H32,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
+        <v/>
+      </c>
+      <c r="J32" s="6"/>
+      <c r="K32" s="6"/>
+      <c r="L32" s="6"/>
+    </row>
+    <row r="33" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A33" s="6"/>
+      <c r="B33" s="6"/>
+      <c r="C33" s="6"/>
+      <c r="D33" s="6"/>
+      <c r="E33" s="6"/>
+      <c r="F33" s="7"/>
+      <c r="G33" s="6"/>
+      <c r="H33" s="6"/>
+      <c r="I33" s="6" t="str">
+        <f t="array" ref="I33">_xlfn.SWITCH(H33,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
+        <v/>
+      </c>
+      <c r="J33" s="6"/>
+      <c r="K33" s="6"/>
+      <c r="L33" s="6"/>
+    </row>
+    <row r="34" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A34" s="6"/>
+      <c r="B34" s="6"/>
+      <c r="C34" s="6"/>
+      <c r="D34" s="6"/>
+      <c r="E34" s="6"/>
+      <c r="F34" s="7"/>
+      <c r="G34" s="6"/>
+      <c r="H34" s="6"/>
+      <c r="I34" s="6" t="str">
+        <f t="array" ref="I34">_xlfn.SWITCH(H34,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
+        <v/>
+      </c>
+      <c r="J34" s="6"/>
+      <c r="K34" s="6"/>
+      <c r="L34" s="6"/>
+    </row>
+    <row r="35" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A35" s="6"/>
+      <c r="B35" s="6"/>
+      <c r="C35" s="6"/>
+      <c r="D35" s="6"/>
+      <c r="E35" s="6"/>
+      <c r="F35" s="7"/>
+      <c r="G35" s="6"/>
+      <c r="H35" s="6"/>
+      <c r="I35" s="6" t="str">
+        <f t="array" ref="I35">_xlfn.SWITCH(H35,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
+        <v/>
+      </c>
+      <c r="J35" s="6"/>
+      <c r="K35" s="6"/>
+      <c r="L35" s="6"/>
+    </row>
+    <row r="36" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A36" s="6"/>
+      <c r="B36" s="6"/>
+      <c r="C36" s="6"/>
+      <c r="D36" s="6"/>
+      <c r="E36" s="6"/>
+      <c r="F36" s="7"/>
+      <c r="G36" s="6"/>
+      <c r="H36" s="6"/>
+      <c r="I36" s="6" t="str">
+        <f t="array" ref="I36">_xlfn.SWITCH(H36,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
+        <v/>
+      </c>
+      <c r="J36" s="6"/>
+      <c r="K36" s="6"/>
+      <c r="L36" s="6"/>
+    </row>
+    <row r="37" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A37" s="6"/>
+      <c r="B37" s="6"/>
+      <c r="C37" s="6"/>
+      <c r="D37" s="6"/>
+      <c r="E37" s="6"/>
+      <c r="F37" s="7"/>
+      <c r="G37" s="6"/>
+      <c r="H37" s="6"/>
+      <c r="I37" s="6" t="str">
+        <f t="array" ref="I37">_xlfn.SWITCH(H37,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
+        <v/>
+      </c>
+      <c r="J37" s="6"/>
+      <c r="K37" s="6"/>
+      <c r="L37" s="6"/>
+    </row>
+    <row r="38" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A38" s="6"/>
+      <c r="B38" s="6"/>
+      <c r="C38" s="6"/>
+      <c r="D38" s="6"/>
+      <c r="E38" s="6"/>
+      <c r="F38" s="8"/>
+      <c r="G38" s="6"/>
+      <c r="H38" s="6"/>
+      <c r="I38" s="6" t="str">
+        <f t="array" ref="I38">_xlfn.SWITCH(H38,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
+        <v/>
+      </c>
+      <c r="J38" s="6"/>
+      <c r="K38" s="6"/>
+      <c r="L38" s="6"/>
+    </row>
+    <row r="39" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A39" s="6"/>
+      <c r="B39" s="6"/>
+      <c r="C39" s="6"/>
+      <c r="D39" s="6"/>
+      <c r="E39" s="6"/>
+      <c r="F39" s="8"/>
+      <c r="G39" s="6"/>
+      <c r="H39" s="6"/>
+      <c r="I39" s="6" t="str">
+        <f t="array" ref="I39">_xlfn.SWITCH(H39,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
+        <v/>
+      </c>
+      <c r="J39" s="6"/>
+      <c r="K39" s="6"/>
+      <c r="L39" s="6"/>
+    </row>
+    <row r="40" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A40" s="6"/>
+      <c r="B40" s="6"/>
+      <c r="C40" s="6"/>
+      <c r="D40" s="6"/>
+      <c r="E40" s="6"/>
+      <c r="F40" s="8"/>
+      <c r="G40" s="6"/>
+      <c r="H40" s="6"/>
+      <c r="I40" s="6" t="str">
+        <f t="array" ref="I40">_xlfn.SWITCH(H40,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
+        <v/>
+      </c>
+      <c r="J40" s="6"/>
+      <c r="K40" s="6"/>
+      <c r="L40" s="6"/>
+    </row>
+    <row r="41" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A41" s="6"/>
+      <c r="B41" s="6"/>
+      <c r="C41" s="6"/>
+      <c r="D41" s="6"/>
+      <c r="E41" s="6"/>
+      <c r="F41" s="8"/>
+      <c r="G41" s="6"/>
+      <c r="H41" s="6"/>
+      <c r="I41" s="6" t="str">
+        <f t="array" ref="I41">_xlfn.SWITCH(H41,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
+        <v/>
+      </c>
+      <c r="J41" s="6"/>
+      <c r="K41" s="6"/>
+      <c r="L41" s="6"/>
+    </row>
+    <row r="42" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A42" s="6"/>
+      <c r="B42" s="6"/>
+      <c r="C42" s="6"/>
+      <c r="D42" s="6"/>
+      <c r="E42" s="6"/>
+      <c r="F42" s="8"/>
+      <c r="G42" s="6"/>
+      <c r="H42" s="6"/>
+      <c r="I42" s="6" t="str">
+        <f t="array" ref="I42">_xlfn.SWITCH(H42,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
+        <v/>
+      </c>
+      <c r="J42" s="6"/>
+      <c r="K42" s="6"/>
+      <c r="L42" s="6"/>
+    </row>
+    <row r="43" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A43" s="6"/>
+      <c r="B43" s="6"/>
+      <c r="C43" s="6"/>
+      <c r="D43" s="6"/>
+      <c r="E43" s="6"/>
+      <c r="F43" s="8"/>
+      <c r="G43" s="6"/>
+      <c r="H43" s="6"/>
+      <c r="I43" s="6" t="str">
+        <f t="array" ref="I43">_xlfn.SWITCH(H43,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
+        <v/>
+      </c>
+      <c r="J43" s="6"/>
+      <c r="K43" s="6"/>
+      <c r="L43" s="6"/>
+    </row>
+    <row r="44" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A44" s="6"/>
+      <c r="B44" s="6"/>
+      <c r="C44" s="6"/>
+      <c r="D44" s="6"/>
+      <c r="E44" s="6"/>
+      <c r="F44" s="7"/>
+      <c r="G44" s="6"/>
+      <c r="H44" s="6"/>
+      <c r="I44" s="6" t="str">
+        <f t="array" ref="I44">_xlfn.SWITCH(H44,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
+        <v/>
+      </c>
+      <c r="J44" s="6"/>
+      <c r="K44" s="6"/>
+      <c r="L44" s="6"/>
+    </row>
+    <row r="45" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A45" s="6"/>
+      <c r="B45" s="6"/>
+      <c r="C45" s="6"/>
+      <c r="D45" s="6"/>
+      <c r="E45" s="6"/>
+      <c r="F45" s="7"/>
+      <c r="G45" s="6"/>
+      <c r="H45" s="6"/>
+      <c r="I45" s="6" t="str">
+        <f t="array" ref="I45">_xlfn.SWITCH(H45,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
+        <v/>
+      </c>
+      <c r="J45" s="6"/>
+      <c r="K45" s="6"/>
+      <c r="L45" s="6"/>
+    </row>
+    <row r="46" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A46" s="6"/>
+      <c r="B46" s="6"/>
+      <c r="C46" s="6"/>
+      <c r="D46" s="6"/>
+      <c r="E46" s="6"/>
+      <c r="F46" s="7"/>
+      <c r="G46" s="6"/>
+      <c r="H46" s="6"/>
+      <c r="I46" s="6" t="str">
+        <f t="array" ref="I46">_xlfn.SWITCH(H46,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
+        <v/>
+      </c>
+      <c r="J46" s="6"/>
+      <c r="K46" s="6"/>
+      <c r="L46" s="6"/>
+    </row>
+    <row r="47" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A47" s="6"/>
+      <c r="B47" s="6"/>
+      <c r="C47" s="6"/>
+      <c r="D47" s="6"/>
+      <c r="E47" s="6"/>
+      <c r="F47" s="7"/>
+      <c r="G47" s="6"/>
+      <c r="H47" s="6"/>
+      <c r="I47" s="6" t="str">
+        <f t="array" ref="I47">_xlfn.SWITCH(H47,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
+        <v/>
+      </c>
+      <c r="J47" s="6"/>
+      <c r="K47" s="6"/>
+      <c r="L47" s="6"/>
+    </row>
+    <row r="48" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A48" s="6"/>
+      <c r="B48" s="6"/>
+      <c r="C48" s="6"/>
+      <c r="D48" s="6"/>
+      <c r="E48" s="6"/>
+      <c r="F48" s="7"/>
+      <c r="G48" s="6"/>
+      <c r="H48" s="6"/>
+      <c r="I48" s="6" t="str">
+        <f t="array" ref="I48">_xlfn.SWITCH(H48,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
+        <v/>
+      </c>
+      <c r="J48" s="6"/>
+      <c r="K48" s="6"/>
+      <c r="L48" s="6"/>
+    </row>
+    <row r="49" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A49" s="6"/>
+      <c r="B49" s="6"/>
+      <c r="C49" s="6"/>
+      <c r="D49" s="6"/>
+      <c r="E49" s="6"/>
+      <c r="F49" s="7"/>
+      <c r="G49" s="6"/>
+      <c r="H49" s="6"/>
+      <c r="I49" s="6" t="str">
+        <f t="array" ref="I49">_xlfn.SWITCH(H49,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
+        <v/>
+      </c>
+      <c r="J49" s="6"/>
+      <c r="K49" s="6"/>
+      <c r="L49" s="6"/>
+    </row>
+    <row r="50" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A50" s="6"/>
+      <c r="B50" s="6"/>
+      <c r="C50" s="6"/>
+      <c r="D50" s="6"/>
+      <c r="E50" s="6"/>
+      <c r="F50" s="7"/>
+      <c r="G50" s="6"/>
+      <c r="H50" s="6"/>
+      <c r="I50" s="6" t="str">
+        <f t="array" ref="I50">_xlfn.SWITCH(H50,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
+        <v/>
+      </c>
+      <c r="J50" s="6"/>
+      <c r="K50" s="6"/>
+      <c r="L50" s="6"/>
+    </row>
+    <row r="51" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A51" s="6"/>
+      <c r="B51" s="6"/>
+      <c r="C51" s="6"/>
+      <c r="D51" s="6"/>
+      <c r="E51" s="6"/>
+      <c r="F51" s="7"/>
+      <c r="G51" s="6"/>
+      <c r="H51" s="6"/>
+      <c r="I51" s="6" t="str">
+        <f t="array" ref="I51">_xlfn.SWITCH(H51,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
+        <v/>
+      </c>
+      <c r="J51" s="6"/>
+      <c r="K51" s="6"/>
+      <c r="L51" s="6"/>
+    </row>
+    <row r="52" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A52" s="6"/>
+      <c r="B52" s="6"/>
+      <c r="C52" s="6"/>
+      <c r="D52" s="6"/>
+      <c r="E52" s="6"/>
+      <c r="F52" s="7"/>
+      <c r="G52" s="6"/>
+      <c r="H52" s="6"/>
+      <c r="I52" s="6" t="str">
+        <f t="array" ref="I52">_xlfn.SWITCH(H52,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
+        <v/>
+      </c>
+      <c r="J52" s="6"/>
+      <c r="K52" s="6"/>
+      <c r="L52" s="6"/>
+    </row>
+    <row r="53" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A53" s="6"/>
+      <c r="B53" s="6"/>
+      <c r="C53" s="6"/>
+      <c r="D53" s="6"/>
+      <c r="E53" s="6"/>
+      <c r="F53" s="7"/>
+      <c r="G53" s="6"/>
+      <c r="H53" s="6"/>
+      <c r="I53" s="6" t="str">
+        <f t="array" ref="I53">_xlfn.SWITCH(H53,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
+        <v/>
+      </c>
+      <c r="J53" s="6"/>
+      <c r="K53" s="6"/>
+      <c r="L53" s="6"/>
+    </row>
+    <row r="54" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A54" s="6"/>
+      <c r="B54" s="6"/>
+      <c r="C54" s="6"/>
+      <c r="D54" s="6"/>
+      <c r="E54" s="6"/>
+      <c r="F54" s="7"/>
+      <c r="G54" s="6"/>
+      <c r="H54" s="6"/>
+      <c r="I54" s="6" t="str">
+        <f t="array" ref="I54">_xlfn.SWITCH(H54,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
+        <v/>
+      </c>
+      <c r="J54" s="6"/>
+      <c r="K54" s="6"/>
+      <c r="L54" s="6"/>
+    </row>
+    <row r="55" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A55" s="6"/>
+      <c r="B55" s="6"/>
+      <c r="C55" s="6"/>
+      <c r="D55" s="6"/>
+      <c r="E55" s="6"/>
+      <c r="F55" s="5"/>
+      <c r="G55" s="6"/>
+      <c r="H55" s="6"/>
+      <c r="I55" s="6" t="str">
+        <f t="array" ref="I55">_xlfn.SWITCH(H55,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
+        <v/>
+      </c>
+      <c r="J55" s="6"/>
+      <c r="K55" s="6"/>
+      <c r="L55" s="6"/>
+    </row>
+    <row r="56" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A56" s="6"/>
+      <c r="B56" s="6"/>
+      <c r="C56" s="6"/>
+      <c r="D56" s="6"/>
+      <c r="E56" s="6"/>
+      <c r="F56" s="7"/>
+      <c r="G56" s="6"/>
+      <c r="H56" s="6"/>
+      <c r="I56" s="6" t="str">
+        <f t="array" ref="I56">_xlfn.SWITCH(H56,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
+        <v/>
+      </c>
+      <c r="J56" s="6"/>
+      <c r="K56" s="6"/>
+      <c r="L56" s="6"/>
+    </row>
+    <row r="57" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A57" s="6"/>
+      <c r="B57" s="6"/>
+      <c r="C57" s="6"/>
+      <c r="D57" s="6"/>
+      <c r="E57" s="6"/>
+      <c r="F57" s="5"/>
+      <c r="G57" s="6"/>
+      <c r="H57" s="6"/>
+      <c r="I57" s="6" t="str">
+        <f t="array" ref="I57">_xlfn.SWITCH(H57,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
+        <v/>
+      </c>
+      <c r="J57" s="6"/>
+      <c r="K57" s="6"/>
+      <c r="L57" s="6"/>
+    </row>
+    <row r="58" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A58" s="6"/>
+      <c r="B58" s="6"/>
+      <c r="C58" s="6"/>
+      <c r="D58" s="6"/>
+      <c r="E58" s="6"/>
+      <c r="F58" s="5"/>
+      <c r="G58" s="6"/>
+      <c r="H58" s="6"/>
+      <c r="I58" s="6" t="str">
+        <f t="array" ref="I58">_xlfn.SWITCH(H58,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
+        <v/>
+      </c>
+      <c r="J58" s="6"/>
+      <c r="K58" s="6"/>
+      <c r="L58" s="6"/>
+    </row>
+    <row r="59" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A59" s="6"/>
+      <c r="B59" s="6"/>
+      <c r="C59" s="6"/>
+      <c r="D59" s="6"/>
+      <c r="E59" s="6"/>
+      <c r="F59" s="7"/>
+      <c r="G59" s="6"/>
+      <c r="H59" s="6"/>
+      <c r="I59" s="6" t="str">
+        <f t="array" ref="I59">_xlfn.SWITCH(H59,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
+        <v/>
+      </c>
+      <c r="J59" s="6"/>
+      <c r="K59" s="6"/>
+      <c r="L59" s="6"/>
+    </row>
+    <row r="60" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A60" s="6"/>
+      <c r="B60" s="6"/>
+      <c r="C60" s="6"/>
+      <c r="D60" s="6"/>
+      <c r="E60" s="6"/>
+      <c r="F60" s="7"/>
+      <c r="G60" s="6"/>
+      <c r="H60" s="6"/>
+      <c r="I60" s="6" t="str">
+        <f t="array" ref="I60">_xlfn.SWITCH(H60,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
+        <v/>
+      </c>
+      <c r="J60" s="6"/>
+      <c r="K60" s="6"/>
+      <c r="L60" s="6"/>
+    </row>
+    <row r="61" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A61" s="6"/>
+      <c r="B61" s="6"/>
+      <c r="C61" s="6"/>
+      <c r="D61" s="6"/>
+      <c r="E61" s="6"/>
+      <c r="F61" s="7"/>
+      <c r="G61" s="6"/>
+      <c r="H61" s="6"/>
+      <c r="I61" s="6" t="str">
+        <f t="array" ref="I61">_xlfn.SWITCH(H61,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
+        <v/>
+      </c>
+      <c r="J61" s="6"/>
+      <c r="K61" s="6"/>
+      <c r="L61" s="6"/>
+    </row>
+    <row r="62" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A62" s="6"/>
+      <c r="B62" s="6"/>
+      <c r="C62" s="6"/>
+      <c r="D62" s="6"/>
+      <c r="E62" s="6"/>
+      <c r="F62" s="7"/>
+      <c r="G62" s="6"/>
+      <c r="H62" s="6"/>
+      <c r="I62" s="6" t="str">
+        <f t="array" ref="I62">_xlfn.SWITCH(H62,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
+        <v/>
+      </c>
+      <c r="J62" s="6"/>
+      <c r="K62" s="6"/>
+      <c r="L62" s="6"/>
+    </row>
+    <row r="63" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A63" s="6"/>
+      <c r="B63" s="6"/>
+      <c r="C63" s="6"/>
+      <c r="D63" s="6"/>
+      <c r="E63" s="6"/>
+      <c r="F63" s="7"/>
+      <c r="G63" s="6"/>
+      <c r="H63" s="6"/>
+      <c r="I63" s="6" t="str">
+        <f t="array" ref="I63">_xlfn.SWITCH(H63,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
+        <v/>
+      </c>
+      <c r="J63" s="6"/>
+      <c r="K63" s="6"/>
+      <c r="L63" s="6"/>
+    </row>
+    <row r="64" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A64" s="6"/>
+      <c r="B64" s="6"/>
+      <c r="C64" s="6"/>
+      <c r="D64" s="6"/>
+      <c r="E64" s="6"/>
+      <c r="F64" s="8"/>
+      <c r="G64" s="6"/>
+      <c r="H64" s="6"/>
+      <c r="I64" s="6" t="str">
+        <f t="array" ref="I64">_xlfn.SWITCH(H64,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
+        <v/>
+      </c>
+      <c r="J64" s="6"/>
+      <c r="K64" s="6"/>
+      <c r="L64" s="6"/>
+    </row>
+    <row r="65" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A65" s="6"/>
+      <c r="B65" s="6"/>
+      <c r="C65" s="6"/>
+      <c r="D65" s="6"/>
+      <c r="E65" s="6"/>
+      <c r="F65" s="8"/>
+      <c r="G65" s="6"/>
+      <c r="H65" s="6"/>
+      <c r="I65" s="6" t="str">
+        <f t="array" ref="I65">_xlfn.SWITCH(H65,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
+        <v/>
+      </c>
+      <c r="J65" s="6"/>
+      <c r="K65" s="6"/>
+      <c r="L65" s="6"/>
+    </row>
+    <row r="66" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A66" s="6"/>
+      <c r="B66" s="6"/>
+      <c r="C66" s="6"/>
+      <c r="D66" s="6"/>
+      <c r="E66" s="6"/>
+      <c r="F66" s="8"/>
+      <c r="G66" s="6"/>
+      <c r="H66" s="6"/>
+      <c r="I66" s="6" t="str">
+        <f t="array" ref="I66">_xlfn.SWITCH(H66,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
+        <v/>
+      </c>
+      <c r="J66" s="6"/>
+      <c r="K66" s="6"/>
+      <c r="L66" s="6"/>
+    </row>
+    <row r="67" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A67" s="6"/>
+      <c r="B67" s="6"/>
+      <c r="C67" s="6"/>
+      <c r="D67" s="6"/>
+      <c r="E67" s="6"/>
+      <c r="F67" s="8"/>
+      <c r="G67" s="6"/>
+      <c r="H67" s="6"/>
+      <c r="I67" s="6" t="str">
+        <f t="array" ref="I67">_xlfn.SWITCH(H67,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
+        <v/>
+      </c>
+      <c r="J67" s="6"/>
+      <c r="K67" s="6"/>
+      <c r="L67" s="6"/>
+    </row>
+    <row r="68" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A68" s="6"/>
+      <c r="B68" s="6"/>
+      <c r="C68" s="6"/>
+      <c r="D68" s="6"/>
+      <c r="E68" s="6"/>
+      <c r="F68" s="8"/>
+      <c r="G68" s="6"/>
+      <c r="H68" s="6"/>
+      <c r="I68" s="6" t="str">
+        <f t="array" ref="I68">_xlfn.SWITCH(H68,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
+        <v/>
+      </c>
+      <c r="J68" s="6"/>
+      <c r="K68" s="6"/>
+      <c r="L68" s="6"/>
+    </row>
+    <row r="69" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A69" s="6"/>
+      <c r="B69" s="6"/>
+      <c r="C69" s="6"/>
+      <c r="D69" s="6"/>
+      <c r="E69" s="6"/>
+      <c r="F69" s="8"/>
+      <c r="G69" s="6"/>
+      <c r="H69" s="6"/>
+      <c r="I69" s="6" t="str">
+        <f t="array" ref="I69">_xlfn.SWITCH(H69,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
+        <v/>
+      </c>
+      <c r="J69" s="6"/>
+      <c r="K69" s="6"/>
+      <c r="L69" s="6"/>
+    </row>
+    <row r="70" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A70" s="6"/>
+      <c r="B70" s="6"/>
+      <c r="C70" s="6"/>
+      <c r="D70" s="6"/>
+      <c r="E70" s="6"/>
+      <c r="F70" s="8"/>
+      <c r="G70" s="6"/>
+      <c r="H70" s="6"/>
+      <c r="I70" s="6" t="str">
+        <f t="array" ref="I70">_xlfn.SWITCH(H70,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
+        <v/>
+      </c>
+      <c r="J70" s="6"/>
+      <c r="K70" s="6"/>
+      <c r="L70" s="6"/>
+    </row>
+    <row r="71" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A71" s="6"/>
+      <c r="B71" s="6"/>
+      <c r="C71" s="6"/>
+      <c r="D71" s="6"/>
+      <c r="E71" s="6"/>
+      <c r="F71" s="8"/>
+      <c r="G71" s="6"/>
+      <c r="H71" s="6"/>
+      <c r="I71" s="6" t="str">
+        <f t="array" ref="I71">_xlfn.SWITCH(H71,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
+        <v/>
+      </c>
+      <c r="J71" s="6"/>
+      <c r="K71" s="6"/>
+      <c r="L71" s="6"/>
+    </row>
+    <row r="72" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A72" s="6"/>
+      <c r="B72" s="6"/>
+      <c r="C72" s="6"/>
+      <c r="D72" s="6"/>
+      <c r="E72" s="6"/>
+      <c r="F72" s="8"/>
+      <c r="G72" s="6"/>
+      <c r="H72" s="6"/>
+      <c r="I72" s="6" t="str">
+        <f t="array" ref="I72">_xlfn.SWITCH(H72,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
+        <v/>
+      </c>
+      <c r="J72" s="6"/>
+      <c r="K72" s="6"/>
+      <c r="L72" s="6"/>
+    </row>
+    <row r="73" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A73" s="6"/>
+      <c r="B73" s="6"/>
+      <c r="C73" s="6"/>
+      <c r="D73" s="6"/>
+      <c r="E73" s="6"/>
+      <c r="F73" s="8"/>
+      <c r="G73" s="6"/>
+      <c r="H73" s="6"/>
+      <c r="I73" s="6" t="str">
+        <f t="array" ref="I73">_xlfn.SWITCH(H73,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
+        <v/>
+      </c>
+      <c r="J73" s="6"/>
+      <c r="K73" s="6"/>
+      <c r="L73" s="6"/>
+    </row>
+    <row r="74" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A74" s="6"/>
+      <c r="B74" s="6"/>
+      <c r="C74" s="6"/>
+      <c r="D74" s="6"/>
+      <c r="E74" s="6"/>
+      <c r="F74" s="8"/>
+      <c r="G74" s="6"/>
+      <c r="H74" s="6"/>
+      <c r="I74" s="6" t="str">
+        <f t="array" ref="I74">_xlfn.SWITCH(H74,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
+        <v/>
+      </c>
+      <c r="J74" s="6"/>
+      <c r="K74" s="6"/>
+      <c r="L74" s="6"/>
+    </row>
+    <row r="75" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A75" s="6"/>
+      <c r="B75" s="6"/>
+      <c r="C75" s="6"/>
+      <c r="D75" s="6"/>
+      <c r="E75" s="6"/>
+      <c r="F75" s="8"/>
+      <c r="G75" s="6"/>
+      <c r="H75" s="6"/>
+      <c r="I75" s="6" t="str">
+        <f t="array" ref="I75">_xlfn.SWITCH(H75,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
+        <v/>
+      </c>
+      <c r="J75" s="6"/>
+      <c r="K75" s="6"/>
+      <c r="L75" s="6"/>
+    </row>
+    <row r="76" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A76" s="6"/>
+      <c r="B76" s="6"/>
+      <c r="C76" s="6"/>
+      <c r="D76" s="6"/>
+      <c r="E76" s="6"/>
+      <c r="F76" s="8"/>
+      <c r="G76" s="6"/>
+      <c r="H76" s="6"/>
+      <c r="I76" s="6" t="str">
+        <f t="array" ref="I76">_xlfn.SWITCH(H76,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
+        <v/>
+      </c>
+      <c r="J76" s="6"/>
+      <c r="K76" s="6"/>
+      <c r="L76" s="6"/>
+    </row>
+    <row r="77" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A77" s="6"/>
+      <c r="B77" s="6"/>
+      <c r="C77" s="6"/>
+      <c r="D77" s="6"/>
+      <c r="E77" s="6"/>
+      <c r="F77" s="8"/>
+      <c r="G77" s="6"/>
+      <c r="H77" s="6"/>
+      <c r="I77" s="6" t="str">
+        <f t="array" ref="I77">_xlfn.SWITCH(H77,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
+        <v/>
+      </c>
+      <c r="J77" s="6"/>
+      <c r="K77" s="6"/>
+      <c r="L77" s="6"/>
+    </row>
+    <row r="78" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A78" s="6"/>
+      <c r="B78" s="6"/>
+      <c r="C78" s="6"/>
+      <c r="D78" s="6"/>
+      <c r="E78" s="6"/>
+      <c r="F78" s="8"/>
+      <c r="G78" s="6"/>
+      <c r="H78" s="6"/>
+      <c r="I78" s="6" t="str">
+        <f t="array" ref="I78">_xlfn.SWITCH(H78,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
+        <v/>
+      </c>
+      <c r="J78" s="6"/>
+      <c r="K78" s="6"/>
+      <c r="L78" s="6"/>
+    </row>
+    <row r="79" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A79" s="6"/>
+      <c r="B79" s="6"/>
+      <c r="C79" s="6"/>
+      <c r="D79" s="6"/>
+      <c r="E79" s="6"/>
+      <c r="F79" s="8"/>
+      <c r="G79" s="6"/>
+      <c r="H79" s="6"/>
+      <c r="I79" s="6" t="str">
+        <f t="array" ref="I79">_xlfn.SWITCH(H79,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
+        <v/>
+      </c>
+      <c r="J79" s="6"/>
+      <c r="K79" s="6"/>
+      <c r="L79" s="6"/>
+    </row>
+    <row r="80" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A80" s="6"/>
+      <c r="B80" s="6"/>
+      <c r="C80" s="6"/>
+      <c r="D80" s="6"/>
+      <c r="E80" s="6"/>
+      <c r="F80" s="8"/>
+      <c r="G80" s="6"/>
+      <c r="H80" s="6"/>
+      <c r="I80" s="6" t="str">
+        <f t="array" ref="I80">_xlfn.SWITCH(H80,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
+        <v/>
+      </c>
+      <c r="J80" s="6"/>
+      <c r="K80" s="6"/>
+      <c r="L80" s="6"/>
+    </row>
+    <row r="81" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A81" s="6"/>
+      <c r="B81" s="6"/>
+      <c r="C81" s="6"/>
+      <c r="D81" s="6"/>
+      <c r="E81" s="6"/>
+      <c r="F81" s="8"/>
+      <c r="G81" s="6"/>
+      <c r="H81" s="6"/>
+      <c r="I81" s="6" t="str">
+        <f t="array" ref="I81">_xlfn.SWITCH(H81,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
+        <v/>
+      </c>
+      <c r="J81" s="6"/>
+      <c r="K81" s="6"/>
+      <c r="L81" s="6"/>
+    </row>
+    <row r="82" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A82" s="6"/>
+      <c r="B82" s="6"/>
+      <c r="C82" s="6"/>
+      <c r="D82" s="6"/>
+      <c r="E82" s="6"/>
+      <c r="F82" s="8"/>
+      <c r="G82" s="6"/>
+      <c r="H82" s="6"/>
+      <c r="I82" s="6" t="str">
+        <f t="array" ref="I82">_xlfn.SWITCH(H82,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
+        <v/>
+      </c>
+      <c r="J82" s="6"/>
+      <c r="K82" s="6"/>
+      <c r="L82" s="6"/>
+    </row>
+    <row r="83" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A83" s="6"/>
+      <c r="B83" s="6"/>
+      <c r="C83" s="6"/>
+      <c r="D83" s="6"/>
+      <c r="E83" s="6"/>
+      <c r="F83" s="8"/>
+      <c r="G83" s="6"/>
+      <c r="H83" s="6"/>
+      <c r="I83" s="6" t="str">
+        <f t="array" ref="I83">_xlfn.SWITCH(H83,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
+        <v/>
+      </c>
+      <c r="J83" s="6"/>
+      <c r="K83" s="6"/>
+      <c r="L83" s="6"/>
+    </row>
+    <row r="84" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A84" s="6"/>
+      <c r="B84" s="6"/>
+      <c r="C84" s="6"/>
+      <c r="D84" s="6"/>
+      <c r="E84" s="6"/>
+      <c r="F84" s="8"/>
+      <c r="G84" s="6"/>
+      <c r="H84" s="6"/>
+      <c r="I84" s="6" t="str">
+        <f t="array" ref="I84">_xlfn.SWITCH(H84,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
+        <v/>
+      </c>
+      <c r="J84" s="6"/>
+      <c r="K84" s="6"/>
+      <c r="L84" s="6"/>
+    </row>
+    <row r="85" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A85" s="6"/>
+      <c r="B85" s="6"/>
+      <c r="C85" s="6"/>
+      <c r="D85" s="6"/>
+      <c r="E85" s="6"/>
+      <c r="F85" s="8"/>
+      <c r="G85" s="6"/>
+      <c r="H85" s="6"/>
+      <c r="I85" s="6" t="str">
+        <f t="array" ref="I85">_xlfn.SWITCH(H85,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
+        <v/>
+      </c>
+      <c r="J85" s="6"/>
+      <c r="K85" s="6"/>
+      <c r="L85" s="6"/>
+    </row>
+    <row r="86" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A86" s="6"/>
+      <c r="B86" s="6"/>
+      <c r="C86" s="6"/>
+      <c r="D86" s="6"/>
+      <c r="E86" s="6"/>
+      <c r="F86" s="8"/>
+      <c r="G86" s="6"/>
+      <c r="H86" s="6"/>
+      <c r="I86" s="6" t="str">
+        <f t="array" ref="I86">_xlfn.SWITCH(H86,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
+        <v/>
+      </c>
+      <c r="J86" s="6"/>
+      <c r="K86" s="6"/>
+      <c r="L86" s="6"/>
+    </row>
+    <row r="87" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A87" s="6"/>
+      <c r="B87" s="6"/>
+      <c r="C87" s="6"/>
+      <c r="D87" s="6"/>
+      <c r="E87" s="6"/>
+      <c r="F87" s="8"/>
+      <c r="G87" s="6"/>
+      <c r="H87" s="6"/>
+      <c r="I87" s="6" t="str">
+        <f t="array" ref="I87">_xlfn.SWITCH(H87,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
+        <v/>
+      </c>
+      <c r="J87" s="6"/>
+      <c r="K87" s="6"/>
+      <c r="L87" s="6"/>
+    </row>
+    <row r="88" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A88" s="6"/>
+      <c r="B88" s="6"/>
+      <c r="C88" s="6"/>
+      <c r="D88" s="6"/>
+      <c r="E88" s="6"/>
+      <c r="F88" s="8"/>
+      <c r="G88" s="6"/>
+      <c r="H88" s="6"/>
+      <c r="I88" s="6" t="str">
+        <f t="array" ref="I88">_xlfn.SWITCH(H88,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
+        <v/>
+      </c>
+      <c r="J88" s="6"/>
+      <c r="K88" s="6"/>
+      <c r="L88" s="6"/>
+    </row>
+    <row r="89" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A89" s="6"/>
+      <c r="B89" s="6"/>
+      <c r="C89" s="6"/>
+      <c r="D89" s="6"/>
+      <c r="E89" s="6"/>
+      <c r="F89" s="8"/>
+      <c r="G89" s="6"/>
+      <c r="H89" s="6"/>
+      <c r="I89" s="6" t="str">
+        <f t="array" ref="I89">_xlfn.SWITCH(H89,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
+        <v/>
+      </c>
+      <c r="J89" s="6"/>
+      <c r="K89" s="6"/>
+      <c r="L89" s="6"/>
+    </row>
+    <row r="90" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A90" s="6"/>
+      <c r="B90" s="6"/>
+      <c r="C90" s="6"/>
+      <c r="D90" s="6"/>
+      <c r="E90" s="6"/>
+      <c r="F90" s="8"/>
+      <c r="G90" s="6"/>
+      <c r="H90" s="6"/>
+      <c r="I90" s="6" t="str">
+        <f t="array" ref="I90">_xlfn.SWITCH(H90,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
+        <v/>
+      </c>
+      <c r="J90" s="6"/>
+      <c r="K90" s="6"/>
+      <c r="L90" s="6"/>
+    </row>
+    <row r="91" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A91" s="6"/>
+      <c r="B91" s="6"/>
+      <c r="C91" s="6"/>
+      <c r="D91" s="6"/>
+      <c r="E91" s="6"/>
+      <c r="F91" s="8"/>
+      <c r="G91" s="6"/>
+      <c r="H91" s="6"/>
+      <c r="I91" s="6" t="str">
+        <f t="array" ref="I91">_xlfn.SWITCH(H91,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
+        <v/>
+      </c>
+      <c r="J91" s="6"/>
+      <c r="K91" s="6"/>
+      <c r="L91" s="6"/>
+    </row>
+    <row r="92" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A92" s="6"/>
+      <c r="B92" s="6"/>
+      <c r="C92" s="6"/>
+      <c r="D92" s="6"/>
+      <c r="E92" s="6"/>
+      <c r="F92" s="8"/>
+      <c r="G92" s="6"/>
+      <c r="H92" s="6"/>
+      <c r="I92" s="6" t="str">
+        <f t="array" ref="I92">_xlfn.SWITCH(H92,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
+        <v/>
+      </c>
+      <c r="J92" s="6"/>
+      <c r="K92" s="6"/>
+      <c r="L92" s="6"/>
+    </row>
+    <row r="93" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A93" s="6"/>
+      <c r="B93" s="6"/>
+      <c r="C93" s="6"/>
+      <c r="D93" s="6"/>
+      <c r="E93" s="6"/>
+      <c r="F93" s="8"/>
+      <c r="G93" s="6"/>
+      <c r="H93" s="6"/>
+      <c r="I93" s="6" t="str">
+        <f t="array" ref="I93">_xlfn.SWITCH(H93,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
+        <v/>
+      </c>
+      <c r="J93" s="6"/>
+      <c r="K93" s="6"/>
+      <c r="L93" s="6"/>
+    </row>
+    <row r="94" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A94" s="6"/>
+      <c r="B94" s="6"/>
+      <c r="C94" s="6"/>
+      <c r="D94" s="6"/>
+      <c r="E94" s="6"/>
+      <c r="F94" s="8"/>
+      <c r="G94" s="6"/>
+      <c r="H94" s="6"/>
+      <c r="I94" s="6" t="str">
+        <f t="array" ref="I94">_xlfn.SWITCH(H94,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
+        <v/>
+      </c>
+      <c r="J94" s="6"/>
+      <c r="K94" s="6"/>
+      <c r="L94" s="6"/>
+    </row>
+    <row r="95" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A95" s="6"/>
+      <c r="B95" s="6"/>
+      <c r="C95" s="6"/>
+      <c r="D95" s="6"/>
+      <c r="E95" s="6"/>
+      <c r="F95" s="8"/>
+      <c r="G95" s="6"/>
+      <c r="H95" s="6"/>
+      <c r="I95" s="6" t="str">
+        <f t="array" ref="I95">_xlfn.SWITCH(H95,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
+        <v/>
+      </c>
+      <c r="J95" s="6"/>
+      <c r="K95" s="6"/>
+      <c r="L95" s="6"/>
+    </row>
+    <row r="96" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A96" s="6"/>
+      <c r="B96" s="6"/>
+      <c r="C96" s="6"/>
+      <c r="D96" s="6"/>
+      <c r="E96" s="6"/>
+      <c r="F96" s="8"/>
+      <c r="G96" s="6"/>
+      <c r="H96" s="6"/>
+      <c r="I96" s="6" t="str">
+        <f t="array" ref="I96">_xlfn.SWITCH(H96,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
+        <v/>
+      </c>
+      <c r="J96" s="6"/>
+      <c r="K96" s="6"/>
+      <c r="L96" s="6"/>
+    </row>
+    <row r="97" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A97" s="6"/>
+      <c r="B97" s="6"/>
+      <c r="C97" s="6"/>
+      <c r="D97" s="6"/>
+      <c r="E97" s="6"/>
+      <c r="F97" s="8"/>
+      <c r="G97" s="6"/>
+      <c r="H97" s="6"/>
+      <c r="I97" s="6" t="str">
+        <f t="array" ref="I97">_xlfn.SWITCH(H97,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
+        <v/>
+      </c>
+      <c r="J97" s="6"/>
+      <c r="K97" s="6"/>
+      <c r="L97" s="6"/>
+    </row>
+    <row r="98" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A98" s="6"/>
+      <c r="B98" s="6"/>
+      <c r="C98" s="6"/>
+      <c r="D98" s="6"/>
+      <c r="E98" s="6"/>
+      <c r="F98" s="8"/>
+      <c r="G98" s="6"/>
+      <c r="H98" s="6"/>
+      <c r="I98" s="6" t="str">
+        <f t="array" ref="I98">_xlfn.SWITCH(H98,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
+        <v/>
+      </c>
+      <c r="J98" s="6"/>
+      <c r="K98" s="6"/>
+      <c r="L98" s="6"/>
+    </row>
+    <row r="99" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A99" s="6"/>
+      <c r="B99" s="6"/>
+      <c r="C99" s="6"/>
+      <c r="D99" s="6"/>
+      <c r="E99" s="6"/>
+      <c r="F99" s="8"/>
+      <c r="G99" s="6"/>
+      <c r="H99" s="6"/>
+      <c r="I99" s="6" t="str">
+        <f t="array" ref="I99">_xlfn.SWITCH(H99,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
+        <v/>
+      </c>
+      <c r="J99" s="6"/>
+      <c r="K99" s="6"/>
+      <c r="L99" s="6"/>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="4" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D768F6E0-6E10-4552-9483-4F3EB0450BB5}">
+  <dimension ref="A1:L10"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="4.88671875" style="1" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="10.88671875" style="1" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="9.77734375" style="3" customWidth="1"/>
+    <col min="4" max="4" width="10.77734375" style="1" customWidth="1"/>
+    <col min="5" max="5" width="8.88671875" style="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:12" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="A1" s="21" t="s">
+        <v>12</v>
+      </c>
+      <c r="B1" s="21" t="s">
+        <v>62</v>
+      </c>
+      <c r="C1" s="22" t="s">
+        <v>13</v>
+      </c>
+      <c r="D1" s="22" t="s">
+        <v>14</v>
+      </c>
+      <c r="E1" s="22" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="2" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A2" s="17">
+        <v>0</v>
+      </c>
+      <c r="B2" s="18">
+        <v>46272</v>
+      </c>
+      <c r="C2" s="19">
+        <f>44-SUM(E$2:E2)</f>
+        <v>44</v>
+      </c>
+      <c r="D2" s="20">
+        <f>44*(1-(A2/8))</f>
+        <v>44</v>
+      </c>
+      <c r="E2" s="20">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A3" s="17">
+        <v>1</v>
+      </c>
+      <c r="B3" s="18">
+        <v>46273</v>
+      </c>
+      <c r="C3" s="19">
+        <f>44-SUM(E$2:E3)</f>
+        <v>44</v>
+      </c>
+      <c r="D3" s="20">
+        <f t="shared" ref="D3:D10" si="0">44*(1-(A3/8))</f>
+        <v>38.5</v>
+      </c>
+      <c r="E3" s="20">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A4" s="17">
+        <v>2</v>
+      </c>
+      <c r="B4" s="18">
+        <v>46274</v>
+      </c>
+      <c r="C4" s="19">
+        <f>44-SUM(E$2:E4)</f>
+        <v>44</v>
+      </c>
+      <c r="D4" s="20">
+        <f t="shared" si="0"/>
+        <v>33</v>
+      </c>
+      <c r="E4" s="20">
+        <v>0</v>
+      </c>
+      <c r="L4" s="2"/>
+    </row>
+    <row r="5" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A5" s="17">
+        <v>3</v>
+      </c>
+      <c r="B5" s="18">
+        <v>46275</v>
+      </c>
+      <c r="C5" s="19">
+        <f>44-SUM(E$2:E5)</f>
+        <v>31</v>
+      </c>
+      <c r="D5" s="20">
+        <f t="shared" si="0"/>
+        <v>27.5</v>
+      </c>
+      <c r="E5" s="20">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="6" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A6" s="17">
+        <v>4</v>
+      </c>
+      <c r="B6" s="18">
+        <v>46276</v>
+      </c>
+      <c r="C6" s="19">
+        <f>44-SUM(E$2:E6)</f>
+        <v>18</v>
+      </c>
+      <c r="D6" s="20">
+        <f t="shared" si="0"/>
+        <v>22</v>
+      </c>
+      <c r="E6" s="20">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="7" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A7" s="17">
+        <v>5</v>
+      </c>
+      <c r="B7" s="18">
+        <v>46279</v>
+      </c>
+      <c r="C7" s="19">
+        <f>44-SUM(E$2:E7)</f>
+        <v>18</v>
+      </c>
+      <c r="D7" s="20">
+        <f t="shared" si="0"/>
+        <v>16.5</v>
+      </c>
+      <c r="E7" s="20"/>
+    </row>
+    <row r="8" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A8" s="17">
+        <v>6</v>
+      </c>
+      <c r="B8" s="18">
+        <v>46280</v>
+      </c>
+      <c r="C8" s="19">
+        <f>44-SUM(E$2:E8)</f>
+        <v>18</v>
+      </c>
+      <c r="D8" s="20">
+        <f t="shared" si="0"/>
+        <v>11</v>
+      </c>
+      <c r="E8" s="20"/>
+    </row>
+    <row r="9" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A9" s="17">
+        <v>7</v>
+      </c>
+      <c r="B9" s="18">
+        <v>46281</v>
+      </c>
+      <c r="C9" s="19">
+        <f>44-SUM(E$2:E9)</f>
+        <v>18</v>
+      </c>
+      <c r="D9" s="20">
+        <f t="shared" si="0"/>
+        <v>5.5</v>
+      </c>
+      <c r="E9" s="20"/>
+    </row>
+    <row r="10" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A10" s="17">
+        <v>8</v>
+      </c>
+      <c r="B10" s="18">
+        <v>46282</v>
+      </c>
+      <c r="C10" s="19">
+        <f>44-SUM(E$2:E10)</f>
+        <v>18</v>
+      </c>
+      <c r="D10" s="20">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="E10" s="20"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
+</worksheet>
 </file>
--- a/Business Analysis/checkupp_sprint_plan_2026.xlsx
+++ b/Business Analysis/checkupp_sprint_plan_2026.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitHub\CheckUpp\Business Analysis\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D9CE9CD9-6331-4BF6-A5C0-0B26EB142645}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{782DCFAC-0583-462F-A2C1-C10DDA8407FA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="2" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="2" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sprint 01" sheetId="1" r:id="rId1"/>
@@ -22,7 +22,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Sprint 01'!$E$1:$E$112</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Sprint 03'!$E$1:$E$99</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Sprint 03'!$J$1:$J$107</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -62,7 +62,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="399" uniqueCount="132">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="447" uniqueCount="140">
   <si>
     <t>Epic</t>
   </si>
@@ -6065,6 +6065,119 @@
   </si>
   <si>
     <t>XL</t>
+  </si>
+  <si>
+    <t>TDD - Write Unit Tests for Crypto Utility
+Target Files: tests/utils/crypto.util.test.ts
+Implementation Steps:
+- Scaffold the Jest test suite for a new crypto.util module.
+- Define the failing test assertions required to validate AES-256-GCM encryption and decryption.
+- Mock process.env.WALLET_ENCRYPTION_KEY to provide a valid 32-byte string during the test run.
+TDD Test Assertions (To be written):
+[ ] it('should encrypt a plaintext string into a structured iv:tag:ciphertext format')
+[ ] it('should successfully decrypt a valid iv:tag:ciphertext string back to the original plaintext')
+[ ] it('should throw a decipher authentication error if the ciphertext payload is altered')
+[ ] it('should throw a decipher authentication error if the authentication tag is altered')
+Acceptance Criteria:
+[ ] The test suite runs and correctly fails (Red phase of TDD) awaiting the implementation ticket.</t>
+  </si>
+  <si>
+    <t>Implement Crypto Utility (AES-256-GCM)
+Target Files: checkupp-api/src/utils/crypto.util.ts
+Implementation Steps:
+1. Environment Variable: Read WALLET_ENCRYPTION_KEY from process.env. Throw an initialization error if missing or not exactly 32 bytes.
+2. Algorithm: Hardcode the cipher algorithm strictly as aes-256-gcm.
+3. Encrypt Function (encryptLink):
+Accept a plain text URL string.
+Generate a 16-byte Initialization Vector via crypto.randomBytes(16).
+Create a cipher using crypto.createCipheriv.
+Extract the 16-byte Authentication Tag via cipher.getAuthTag().
+Return a formatted string exact match: iv_hex:tag_hex:ciphertext_hex.
+4. Decrypt Function (decryptLink):
+Accept the formatted ciphertext string and split it by :.
+Create a decipher using crypto.createDecipheriv.
+Set the auth tag via decipher.setAuthTag(Buffer.from(tag_hex, 'hex')).
+Decrypt and return the original UTF-8 string.
+Acceptance Criteria:
+[ ] All tests defined in Ticket 1 pass successfully (Green phase).
+[ ] 100% statement coverage achieved on crypto.util.ts.</t>
+  </si>
+  <si>
+    <t>TDD - Write Unit Tests for Wallet Service Encryption Integration
+Target Files: checkupp-api/tests/modules/wallet/wallet.service.test.ts
+Implementation Steps:
+Locate the existing wallet.service test suite.
+Mock the incoming crypto.util.ts dependencies (encryptLink, decryptLink).
+Write failing test assertions for the createLink and listDocuments flows to ensure data is intercepted before Prisma queries.
+TDD Test Assertions (To be written):
+[ ] it('should pass the URL to encryptLink before calling prisma.walletItem.create')
+[ ] it('should pass stored database ciphertext to decryptLink before returning the item list')
+[ ] it('should gracefully skip decryption and return null/undefined if the externalUrl field is empty')
+[ ] it('should throw a 500 Internal Server Error if decryption fails during the database read cycle')
+Acceptance Criteria:
+[ ] The test suite runs and correctly fails awaiting implementation.</t>
+  </si>
+  <si>
+    <t>Integrate Encryption into Wallet Service
+Target Files: checkupp-api/src/modules/wallet/wallet.service.ts
+Implementation Steps:
+Write Operation (createLink): Intercept the externalUrl or publicUrl payload before it hits prisma.walletItem.create. Pass it through encryptLink() and map the resulting iv:tag:ciphertext string to the Prisma creation object.
+Read Operation (getWalletItems / listDocuments): When querying prisma.walletItem.findMany, map over the returned object array. If an item contains a populated externalUrl (an e-script), pass that string through decryptLink() to mutate it back to plain text before returning it to the controller.
+Acceptance Criteria:
+[ ] All tests defined in Ticket 3 pass successfully.
+[ ] E-script URLs are persisted in the database exclusively as encrypted strings, while API responses to the client remain plain-text.</t>
+  </si>
+  <si>
+    <t>TDD - Write Unit Tests for Frontend Picker Restrictions
+Target Files: checkupp-mobile/test/hooks/useDocumentUpload.test.ts
+Implementation Steps:
+Scaffold or locate the tests for the useDocumentUpload hook.
+Write tests that assert the correct MIME type arrays are being passed to Expo's picker configurations.
+Mock a scenario where a user bypasses the picker (e.g., via intent) and provides a non-whitelisted file.
+TDD Test Assertions (To be written):
+[ ] it('should configure DocumentPicker with the exact array of whitelisted document MIME types') = ['application/pdf', 'application/msword', 'application/vnd.openxmlformats-officedocument.wordprocessingml.document', 'text/csv', 'application/vnd.openxmlformats-officedocument.spreadsheetml.sheet']
+[ ] it('should configure ImagePicker with the exact array of whitelisted image MIME types') = ['image/jpeg', 'image/png', 'image/heic', 'public.heic']
+[ ] it('should abort upload and trigger showToast("Unsupported file format") if an unwhitelisted file bypasses the picker')
+Acceptance Criteria:
+[ ] Tests correctly fail awaiting the hook update.</t>
+  </si>
+  <si>
+    <t>Implement Frontend OS-Level Picker Restrictions
+Target Files: checkupp-mobile/hooks/useDocumentUpload.ts
+Implementation Steps:
+Document Picker Config: Update expo-document-picker options. Set the type property strictly to: ['application/pdf', 'application/msword', 'application/vnd.openxmlformats-officedocument.wordprocessingml.document', 'text/csv', 'application/vnd.openxmlformats-officedocument.spreadsheetml.sheet'].
+Image Picker Config: Update expo-image-picker to strictly accept: ['image/jpeg', 'image/png', 'image/heic', 'public.heic'].
+Bypass Fallback: Add a manual string validation check on the selected file's returned mimeType against a hardcoded whitelist. If it fails, trigger the existing error toast and abort the upload function early.
+Acceptance Criteria:
+[ ] All tests defined in Ticket 5 pass successfully.
+[ ] Non-whitelisted files (e.g., .mp4, .exe) are physically unselectable in the native iOS/Android file explorers.</t>
+  </si>
+  <si>
+    <t>TDD - Write Unit Tests for Signed URL Pre-Flight Validation
+Target Files: checkupp-api/tests/modules/wallet/wallet.controller.test.ts
+Implementation Steps:
+Locate the test suite for the GCP Signed URL generation controller.
+Mock the Express req object to simulate payloads with missing, invalid, and valid mimeType fields.
+Ensure the GCP SDK mock is specifically checked to not be called during failure states.
+TDD Test Assertions (To be written):
+[ ] it('should generate and return a GCP Signed URL when the body contains a valid mimeType (e.g., application/pdf)')
+[ ] it('should return a 415 error if the requested mimeType is not in the hardcoded whitelist (e.g., application/x-msdownload)')
+[ ] it('should return a 400 error if the mimeType is entirely missing from the request payload')
+[ ] it('should not invoke the GCP Storage SDK if validation fails')
+Acceptance Criteria:
+[ ] Tests correctly fail awaiting controller logic updates.</t>
+  </si>
+  <si>
+    <t>Implement Backend Signed URL Pre-Flight Validation
+Target Files: checkupp-api/src/modules/wallet/wallet.controller.ts
+Implementation Steps:
+Extract Content-Type: Update the /upload-url POST route to require mimeType in the incoming JSON body.
+Strict Whitelist Array: Define a constant array containing the 8 allowed MIME types from Ticket 6.
+Validation Logic: Intercept the request. If req.body.mimeType is missing, return HTTP 400 Bad Request.
+Rejection: If req.body.mimeType is not found within the whitelist array, return HTTP 415 Unsupported Media Type before any GCP Storage logic is executed.
+Acceptance Criteria:
+[ ] All tests defined in Ticket 7 pass successfully.
+[ ] API requests attempting to generate a Signed URL for unsupported files fail securely at the controller level.</t>
   </si>
 </sst>
 </file>
@@ -7326,7 +7439,7 @@
             </a:pPr>
             <a:r>
               <a:rPr lang="en-IN"/>
-              <a:t>Sprint 02 - Burndown</a:t>
+              <a:t>Sprint 03 - Burndown</a:t>
             </a:r>
             <a:r>
               <a:rPr lang="en-IN" baseline="0"/>
@@ -7399,10 +7512,10 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>'Sprint 03 Burndown'!$B$2:$B$10</c:f>
+              <c:f>'Sprint 03 Burndown'!$B$2:$B$14</c:f>
               <c:numCache>
                 <c:formatCode>m/d/yyyy</c:formatCode>
-                <c:ptCount val="9"/>
+                <c:ptCount val="13"/>
                 <c:pt idx="0">
                   <c:v>46272</c:v>
                 </c:pt>
@@ -7430,41 +7543,65 @@
                 <c:pt idx="8">
                   <c:v>46282</c:v>
                 </c:pt>
+                <c:pt idx="9">
+                  <c:v>46283</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>46286</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>46287</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>46288</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>'Sprint 03 Burndown'!$C$2:$C$10</c:f>
+              <c:f>'Sprint 03 Burndown'!$C$2:$C$14</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="9"/>
+                <c:ptCount val="13"/>
                 <c:pt idx="0">
-                  <c:v>44</c:v>
+                  <c:v>61</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>44</c:v>
+                  <c:v>61</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>44</c:v>
+                  <c:v>61</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>31</c:v>
+                  <c:v>48</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>18</c:v>
+                  <c:v>35</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>18</c:v>
+                  <c:v>35</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>18</c:v>
+                  <c:v>35</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>18</c:v>
+                  <c:v>35</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>18</c:v>
+                  <c:v>30</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>25</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>17</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>17</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>17</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -7504,10 +7641,10 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>'Sprint 03 Burndown'!$B$2:$B$10</c:f>
+              <c:f>'Sprint 03 Burndown'!$B$2:$B$14</c:f>
               <c:numCache>
                 <c:formatCode>m/d/yyyy</c:formatCode>
-                <c:ptCount val="9"/>
+                <c:ptCount val="13"/>
                 <c:pt idx="0">
                   <c:v>46272</c:v>
                 </c:pt>
@@ -7535,40 +7672,64 @@
                 <c:pt idx="8">
                   <c:v>46282</c:v>
                 </c:pt>
+                <c:pt idx="9">
+                  <c:v>46283</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>46286</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>46287</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>46288</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>'Sprint 03 Burndown'!$D$2:$D$10</c:f>
+              <c:f>'Sprint 03 Burndown'!$D$2:$D$14</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="9"/>
+                <c:ptCount val="13"/>
                 <c:pt idx="0">
-                  <c:v>44</c:v>
+                  <c:v>61</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>38.5</c:v>
+                  <c:v>55.916666666666664</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>33</c:v>
+                  <c:v>50.833333333333336</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>27.5</c:v>
+                  <c:v>45.75</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>22</c:v>
+                  <c:v>40.666666666666671</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>16.5</c:v>
+                  <c:v>35.583333333333329</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>11</c:v>
+                  <c:v>30.5</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>5.5</c:v>
+                  <c:v>25.416666666666664</c:v>
                 </c:pt>
                 <c:pt idx="8">
+                  <c:v>20.333333333333336</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>15.25</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>10.166666666666664</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>5.0833333333333357</c:v>
+                </c:pt>
+                <c:pt idx="12">
                   <c:v>0</c:v>
                 </c:pt>
               </c:numCache>
@@ -14857,7 +15018,8 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AA30D3B6-4BBC-427B-918A-C301767B692F}">
-  <dimension ref="A1:L99"/>
+  <sheetPr filterMode="1"/>
+  <dimension ref="A1:L107"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="6.88671875" bestFit="1" customWidth="1"/>
@@ -14912,7 +15074,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="2" spans="1:12" ht="201.6" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:12" ht="201.6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A2" s="12">
         <v>1</v>
       </c>
@@ -14943,7 +15105,7 @@
       <c r="K2" s="12"/>
       <c r="L2" s="12"/>
     </row>
-    <row r="3" spans="1:12" ht="172.8" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:12" ht="172.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A3" s="12">
         <v>2</v>
       </c>
@@ -14974,7 +15136,7 @@
       <c r="K3" s="12"/>
       <c r="L3" s="12"/>
     </row>
-    <row r="4" spans="1:12" ht="172.8" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:12" ht="172.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A4" s="12">
         <v>3</v>
       </c>
@@ -15005,7 +15167,7 @@
       <c r="K4" s="12"/>
       <c r="L4" s="12"/>
     </row>
-    <row r="5" spans="1:12" ht="172.8" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:12" ht="172.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A5" s="12">
         <v>4</v>
       </c>
@@ -15036,349 +15198,461 @@
       <c r="K5" s="12"/>
       <c r="L5" s="12"/>
     </row>
-    <row r="6" spans="1:12" ht="100.8" x14ac:dyDescent="0.3">
-      <c r="A6" s="14">
+    <row r="6" spans="1:12" ht="230.4" x14ac:dyDescent="0.3">
+      <c r="A6" s="12">
         <v>5</v>
       </c>
-      <c r="B6" s="14" t="s">
-        <v>124</v>
-      </c>
-      <c r="C6" s="14"/>
-      <c r="D6" s="14"/>
-      <c r="E6" s="14" t="s">
+      <c r="B6" s="12" t="s">
+        <v>94</v>
+      </c>
+      <c r="C6" s="12"/>
+      <c r="D6" s="12"/>
+      <c r="E6" s="12" t="s">
+        <v>31</v>
+      </c>
+      <c r="F6" s="13" t="s">
+        <v>132</v>
+      </c>
+      <c r="G6" s="12" t="s">
+        <v>24</v>
+      </c>
+      <c r="H6" s="12" t="s">
+        <v>23</v>
+      </c>
+      <c r="I6" s="12">
+        <f t="array" ref="I6">_xlfn.SWITCH(H6,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
+        <v>2</v>
+      </c>
+      <c r="J6" s="12" t="s">
+        <v>76</v>
+      </c>
+      <c r="K6" s="12"/>
+      <c r="L6" s="12"/>
+    </row>
+    <row r="7" spans="1:12" ht="316.8" x14ac:dyDescent="0.3">
+      <c r="A7" s="12">
+        <v>6</v>
+      </c>
+      <c r="B7" s="12" t="s">
+        <v>94</v>
+      </c>
+      <c r="C7" s="12"/>
+      <c r="D7" s="12"/>
+      <c r="E7" s="12" t="s">
         <v>22</v>
       </c>
-      <c r="F6" s="15" t="s">
-        <v>125</v>
-      </c>
-      <c r="G6" s="14" t="s">
-        <v>29</v>
-      </c>
-      <c r="H6" s="14" t="s">
-        <v>30</v>
-      </c>
-      <c r="I6" s="14">
-        <f t="array" ref="I6">_xlfn.SWITCH(H6,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
-        <v>5</v>
-      </c>
-      <c r="J6" s="14" t="s">
-        <v>76</v>
-      </c>
-      <c r="K6" s="14"/>
-      <c r="L6" s="14"/>
-    </row>
-    <row r="7" spans="1:12" ht="100.8" x14ac:dyDescent="0.3">
-      <c r="A7" s="14">
-        <v>6</v>
-      </c>
-      <c r="B7" s="14" t="s">
-        <v>124</v>
-      </c>
-      <c r="C7" s="14"/>
-      <c r="D7" s="14"/>
-      <c r="E7" s="14" t="s">
-        <v>31</v>
-      </c>
-      <c r="F7" s="15" t="s">
-        <v>126</v>
-      </c>
-      <c r="G7" s="14" t="s">
-        <v>29</v>
-      </c>
-      <c r="H7" s="14" t="s">
+      <c r="F7" s="13" t="s">
+        <v>133</v>
+      </c>
+      <c r="G7" s="12" t="s">
+        <v>24</v>
+      </c>
+      <c r="H7" s="12" t="s">
         <v>23</v>
       </c>
-      <c r="I7" s="14">
+      <c r="I7" s="12">
         <f t="array" ref="I7">_xlfn.SWITCH(H7,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
         <v>2</v>
       </c>
-      <c r="J7" s="14" t="s">
+      <c r="J7" s="12" t="s">
         <v>76</v>
       </c>
-      <c r="K7" s="14"/>
-      <c r="L7" s="14"/>
-    </row>
-    <row r="8" spans="1:12" ht="115.2" x14ac:dyDescent="0.3">
-      <c r="A8" s="14">
+      <c r="K7" s="12"/>
+      <c r="L7" s="12"/>
+    </row>
+    <row r="8" spans="1:12" ht="244.8" x14ac:dyDescent="0.3">
+      <c r="A8" s="12">
         <v>7</v>
       </c>
-      <c r="B8" s="14" t="s">
-        <v>124</v>
-      </c>
-      <c r="C8" s="14"/>
-      <c r="D8" s="14"/>
-      <c r="E8" s="14" t="s">
-        <v>20</v>
-      </c>
-      <c r="F8" s="15" t="s">
-        <v>127</v>
-      </c>
-      <c r="G8" s="14" t="s">
+      <c r="B8" s="12" t="s">
+        <v>94</v>
+      </c>
+      <c r="C8" s="12"/>
+      <c r="D8" s="12"/>
+      <c r="E8" s="12" t="s">
+        <v>31</v>
+      </c>
+      <c r="F8" s="13" t="s">
+        <v>134</v>
+      </c>
+      <c r="G8" s="12" t="s">
+        <v>24</v>
+      </c>
+      <c r="H8" s="12" t="s">
+        <v>23</v>
+      </c>
+      <c r="I8" s="12">
+        <f t="array" ref="I8">_xlfn.SWITCH(H8,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
+        <v>2</v>
+      </c>
+      <c r="J8" s="12" t="s">
+        <v>76</v>
+      </c>
+      <c r="K8" s="12"/>
+      <c r="L8" s="12"/>
+    </row>
+    <row r="9" spans="1:12" ht="201.6" x14ac:dyDescent="0.3">
+      <c r="A9" s="12">
+        <v>8</v>
+      </c>
+      <c r="B9" s="12" t="s">
+        <v>94</v>
+      </c>
+      <c r="C9" s="12"/>
+      <c r="D9" s="12"/>
+      <c r="E9" s="12" t="s">
+        <v>22</v>
+      </c>
+      <c r="F9" s="13" t="s">
+        <v>135</v>
+      </c>
+      <c r="G9" s="12" t="s">
+        <v>24</v>
+      </c>
+      <c r="H9" s="12" t="s">
+        <v>27</v>
+      </c>
+      <c r="I9" s="12">
+        <f t="array" ref="I9">_xlfn.SWITCH(H9,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
+        <v>3</v>
+      </c>
+      <c r="J9" s="12" t="s">
+        <v>76</v>
+      </c>
+      <c r="K9" s="12"/>
+      <c r="L9" s="12"/>
+    </row>
+    <row r="10" spans="1:12" ht="273.60000000000002" x14ac:dyDescent="0.3">
+      <c r="A10" s="12">
+        <v>9</v>
+      </c>
+      <c r="B10" s="12" t="s">
+        <v>94</v>
+      </c>
+      <c r="C10" s="12"/>
+      <c r="D10" s="12"/>
+      <c r="E10" s="12" t="s">
+        <v>31</v>
+      </c>
+      <c r="F10" s="13" t="s">
+        <v>136</v>
+      </c>
+      <c r="G10" s="12" t="s">
         <v>29</v>
       </c>
-      <c r="H8" s="14" t="s">
-        <v>27</v>
-      </c>
-      <c r="I8" s="14">
-        <f t="array" ref="I8">_xlfn.SWITCH(H8,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
-        <v>3</v>
-      </c>
-      <c r="J8" s="14" t="s">
-        <v>76</v>
-      </c>
-      <c r="K8" s="14"/>
-      <c r="L8" s="14"/>
-    </row>
-    <row r="9" spans="1:12" ht="115.2" x14ac:dyDescent="0.3">
-      <c r="A9" s="14">
-        <v>8</v>
-      </c>
-      <c r="B9" s="14" t="s">
-        <v>124</v>
-      </c>
-      <c r="C9" s="14"/>
-      <c r="D9" s="14"/>
-      <c r="E9" s="14" t="s">
-        <v>20</v>
-      </c>
-      <c r="F9" s="15" t="s">
-        <v>128</v>
-      </c>
-      <c r="G9" s="14" t="s">
-        <v>29</v>
-      </c>
-      <c r="H9" s="14" t="s">
-        <v>30</v>
-      </c>
-      <c r="I9" s="14">
-        <f t="array" ref="I9">_xlfn.SWITCH(H9,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
-        <v>5</v>
-      </c>
-      <c r="J9" s="14" t="s">
-        <v>76</v>
-      </c>
-      <c r="K9" s="14"/>
-      <c r="L9" s="14"/>
-    </row>
-    <row r="10" spans="1:12" ht="100.8" x14ac:dyDescent="0.3">
-      <c r="A10" s="14">
-        <v>9</v>
-      </c>
-      <c r="B10" s="14" t="s">
-        <v>124</v>
-      </c>
-      <c r="C10" s="14"/>
-      <c r="D10" s="14"/>
-      <c r="E10" s="14" t="s">
-        <v>20</v>
-      </c>
-      <c r="F10" s="15" t="s">
-        <v>129</v>
-      </c>
-      <c r="G10" s="14" t="s">
-        <v>29</v>
-      </c>
-      <c r="H10" s="14" t="s">
+      <c r="H10" s="12" t="s">
         <v>23</v>
       </c>
-      <c r="I10" s="14">
+      <c r="I10" s="12">
         <f t="array" ref="I10">_xlfn.SWITCH(H10,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
         <v>2</v>
       </c>
-      <c r="J10" s="14" t="s">
+      <c r="J10" s="12" t="s">
         <v>76</v>
       </c>
-      <c r="K10" s="14"/>
-      <c r="L10" s="14"/>
-    </row>
-    <row r="11" spans="1:12" ht="100.8" x14ac:dyDescent="0.3">
-      <c r="A11" s="14">
+      <c r="K10" s="12"/>
+      <c r="L10" s="12"/>
+    </row>
+    <row r="11" spans="1:12" ht="216" x14ac:dyDescent="0.3">
+      <c r="A11" s="12">
         <v>10</v>
       </c>
-      <c r="B11" s="14" t="s">
+      <c r="B11" s="12" t="s">
+        <v>94</v>
+      </c>
+      <c r="C11" s="12"/>
+      <c r="D11" s="12"/>
+      <c r="E11" s="12" t="s">
+        <v>20</v>
+      </c>
+      <c r="F11" s="13" t="s">
+        <v>137</v>
+      </c>
+      <c r="G11" s="12" t="s">
+        <v>29</v>
+      </c>
+      <c r="H11" s="12" t="s">
+        <v>23</v>
+      </c>
+      <c r="I11" s="12">
+        <f t="array" ref="I11">_xlfn.SWITCH(H11,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
+        <v>2</v>
+      </c>
+      <c r="J11" s="12" t="s">
+        <v>76</v>
+      </c>
+      <c r="K11" s="12"/>
+      <c r="L11" s="12"/>
+    </row>
+    <row r="12" spans="1:12" ht="244.8" x14ac:dyDescent="0.3">
+      <c r="A12" s="12">
+        <v>11</v>
+      </c>
+      <c r="B12" s="12" t="s">
+        <v>94</v>
+      </c>
+      <c r="C12" s="12"/>
+      <c r="D12" s="12"/>
+      <c r="E12" s="12" t="s">
+        <v>31</v>
+      </c>
+      <c r="F12" s="13" t="s">
+        <v>138</v>
+      </c>
+      <c r="G12" s="12" t="s">
+        <v>29</v>
+      </c>
+      <c r="H12" s="12" t="s">
+        <v>23</v>
+      </c>
+      <c r="I12" s="12">
+        <f t="array" ref="I12">_xlfn.SWITCH(H12,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
+        <v>2</v>
+      </c>
+      <c r="J12" s="12" t="s">
+        <v>76</v>
+      </c>
+      <c r="K12" s="12"/>
+      <c r="L12" s="12"/>
+    </row>
+    <row r="13" spans="1:12" ht="187.2" x14ac:dyDescent="0.3">
+      <c r="A13" s="12">
+        <v>12</v>
+      </c>
+      <c r="B13" s="12" t="s">
+        <v>94</v>
+      </c>
+      <c r="C13" s="12"/>
+      <c r="D13" s="12"/>
+      <c r="E13" s="12" t="s">
+        <v>22</v>
+      </c>
+      <c r="F13" s="13" t="s">
+        <v>139</v>
+      </c>
+      <c r="G13" s="12" t="s">
+        <v>29</v>
+      </c>
+      <c r="H13" s="12" t="s">
+        <v>23</v>
+      </c>
+      <c r="I13" s="12">
+        <f t="array" ref="I13">_xlfn.SWITCH(H13,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
+        <v>2</v>
+      </c>
+      <c r="J13" s="12" t="s">
+        <v>76</v>
+      </c>
+      <c r="K13" s="12"/>
+      <c r="L13" s="12"/>
+    </row>
+    <row r="14" spans="1:12" ht="100.8" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A14" s="14">
+        <v>13</v>
+      </c>
+      <c r="B14" s="14" t="s">
         <v>124</v>
       </c>
-      <c r="C11" s="14"/>
-      <c r="D11" s="14"/>
-      <c r="E11" s="14" t="s">
+      <c r="C14" s="14"/>
+      <c r="D14" s="14"/>
+      <c r="E14" s="14" t="s">
+        <v>22</v>
+      </c>
+      <c r="F14" s="15" t="s">
+        <v>125</v>
+      </c>
+      <c r="G14" s="14" t="s">
+        <v>29</v>
+      </c>
+      <c r="H14" s="14" t="s">
+        <v>30</v>
+      </c>
+      <c r="I14" s="14">
+        <f t="array" ref="I14">_xlfn.SWITCH(H14,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
+        <v>5</v>
+      </c>
+      <c r="J14" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="K14" s="14"/>
+      <c r="L14" s="14"/>
+    </row>
+    <row r="15" spans="1:12" ht="100.8" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A15" s="14">
+        <v>14</v>
+      </c>
+      <c r="B15" s="14" t="s">
+        <v>124</v>
+      </c>
+      <c r="C15" s="14"/>
+      <c r="D15" s="14"/>
+      <c r="E15" s="14" t="s">
+        <v>31</v>
+      </c>
+      <c r="F15" s="15" t="s">
+        <v>126</v>
+      </c>
+      <c r="G15" s="14" t="s">
+        <v>29</v>
+      </c>
+      <c r="H15" s="14" t="s">
+        <v>23</v>
+      </c>
+      <c r="I15" s="14">
+        <f t="array" ref="I15">_xlfn.SWITCH(H15,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
+        <v>2</v>
+      </c>
+      <c r="J15" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="K15" s="14"/>
+      <c r="L15" s="14"/>
+    </row>
+    <row r="16" spans="1:12" ht="115.2" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A16" s="14">
+        <v>15</v>
+      </c>
+      <c r="B16" s="14" t="s">
+        <v>124</v>
+      </c>
+      <c r="C16" s="14"/>
+      <c r="D16" s="14"/>
+      <c r="E16" s="14" t="s">
         <v>20</v>
       </c>
-      <c r="F11" s="15" t="s">
+      <c r="F16" s="15" t="s">
+        <v>127</v>
+      </c>
+      <c r="G16" s="14" t="s">
+        <v>29</v>
+      </c>
+      <c r="H16" s="14" t="s">
+        <v>27</v>
+      </c>
+      <c r="I16" s="14">
+        <f t="array" ref="I16">_xlfn.SWITCH(H16,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
+        <v>3</v>
+      </c>
+      <c r="J16" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="K16" s="14"/>
+      <c r="L16" s="14"/>
+    </row>
+    <row r="17" spans="1:12" ht="115.2" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A17" s="14">
+        <v>16</v>
+      </c>
+      <c r="B17" s="14" t="s">
+        <v>124</v>
+      </c>
+      <c r="C17" s="14"/>
+      <c r="D17" s="14"/>
+      <c r="E17" s="14" t="s">
+        <v>20</v>
+      </c>
+      <c r="F17" s="15" t="s">
+        <v>128</v>
+      </c>
+      <c r="G17" s="14" t="s">
+        <v>29</v>
+      </c>
+      <c r="H17" s="14" t="s">
+        <v>30</v>
+      </c>
+      <c r="I17" s="14">
+        <f t="array" ref="I17">_xlfn.SWITCH(H17,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
+        <v>5</v>
+      </c>
+      <c r="J17" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="K17" s="14"/>
+      <c r="L17" s="14"/>
+    </row>
+    <row r="18" spans="1:12" ht="100.8" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A18" s="14">
+        <v>17</v>
+      </c>
+      <c r="B18" s="14" t="s">
+        <v>124</v>
+      </c>
+      <c r="C18" s="14"/>
+      <c r="D18" s="14"/>
+      <c r="E18" s="14" t="s">
+        <v>20</v>
+      </c>
+      <c r="F18" s="15" t="s">
+        <v>129</v>
+      </c>
+      <c r="G18" s="14" t="s">
+        <v>29</v>
+      </c>
+      <c r="H18" s="14" t="s">
+        <v>23</v>
+      </c>
+      <c r="I18" s="14">
+        <f t="array" ref="I18">_xlfn.SWITCH(H18,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
+        <v>2</v>
+      </c>
+      <c r="J18" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="K18" s="14"/>
+      <c r="L18" s="14"/>
+    </row>
+    <row r="19" spans="1:12" ht="100.8" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A19" s="14">
+        <v>18</v>
+      </c>
+      <c r="B19" s="14" t="s">
+        <v>124</v>
+      </c>
+      <c r="C19" s="14"/>
+      <c r="D19" s="14"/>
+      <c r="E19" s="14" t="s">
+        <v>20</v>
+      </c>
+      <c r="F19" s="15" t="s">
         <v>130</v>
       </c>
-      <c r="G11" s="14" t="s">
+      <c r="G19" s="14" t="s">
         <v>29</v>
       </c>
-      <c r="H11" s="14" t="s">
+      <c r="H19" s="14" t="s">
         <v>19</v>
       </c>
-      <c r="I11" s="14">
-        <f t="array" ref="I11">_xlfn.SWITCH(H11,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
+      <c r="I19" s="14">
+        <f t="array" ref="I19">_xlfn.SWITCH(H19,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
         <v>1</v>
       </c>
-      <c r="J11" s="14" t="s">
-        <v>76</v>
-      </c>
-      <c r="K11" s="14"/>
-      <c r="L11" s="14"/>
-    </row>
-    <row r="12" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A12" s="6"/>
-      <c r="B12" s="6"/>
-      <c r="C12" s="6"/>
-      <c r="D12" s="6"/>
-      <c r="E12" s="6"/>
-      <c r="F12" s="8"/>
-      <c r="G12" s="6"/>
-      <c r="H12" s="6"/>
-      <c r="I12" s="6"/>
-      <c r="J12" s="6"/>
-      <c r="K12" s="6"/>
-      <c r="L12" s="6"/>
-    </row>
-    <row r="13" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A13" s="6"/>
-      <c r="B13" s="6"/>
-      <c r="C13" s="6"/>
-      <c r="D13" s="6"/>
-      <c r="E13" s="6"/>
-      <c r="F13" s="8"/>
-      <c r="G13" s="6"/>
-      <c r="H13" s="6"/>
-      <c r="I13" s="6" t="str">
-        <f t="array" ref="I13">_xlfn.SWITCH(H13,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
-        <v/>
-      </c>
-      <c r="J13" s="6"/>
-      <c r="K13" s="6"/>
-      <c r="L13" s="6"/>
-    </row>
-    <row r="14" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A14" s="6"/>
-      <c r="B14" s="6"/>
-      <c r="C14" s="6"/>
-      <c r="D14" s="6"/>
-      <c r="E14" s="6"/>
-      <c r="F14" s="8"/>
-      <c r="G14" s="6"/>
-      <c r="H14" s="6"/>
-      <c r="I14" s="6" t="str">
-        <f t="array" ref="I14">_xlfn.SWITCH(H14,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
-        <v/>
-      </c>
-      <c r="J14" s="6"/>
-      <c r="K14" s="6"/>
-      <c r="L14" s="6"/>
-    </row>
-    <row r="15" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A15" s="6"/>
-      <c r="B15" s="6"/>
-      <c r="C15" s="6"/>
-      <c r="D15" s="6"/>
-      <c r="E15" s="6"/>
-      <c r="F15" s="8"/>
-      <c r="G15" s="6"/>
-      <c r="H15" s="6"/>
-      <c r="I15" s="6" t="str">
-        <f t="array" ref="I15">_xlfn.SWITCH(H15,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
-        <v/>
-      </c>
-      <c r="J15" s="6"/>
-      <c r="K15" s="6"/>
-      <c r="L15" s="6"/>
-    </row>
-    <row r="16" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A16" s="6"/>
-      <c r="B16" s="6"/>
-      <c r="C16" s="6"/>
-      <c r="D16" s="6"/>
-      <c r="E16" s="6"/>
-      <c r="F16" s="8"/>
-      <c r="G16" s="6"/>
-      <c r="H16" s="6"/>
-      <c r="I16" s="6" t="str">
-        <f t="array" ref="I16">_xlfn.SWITCH(H16,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
-        <v/>
-      </c>
-      <c r="J16" s="6"/>
-      <c r="K16" s="6"/>
-      <c r="L16" s="6"/>
-    </row>
-    <row r="17" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A17" s="6"/>
-      <c r="B17" s="6"/>
-      <c r="C17" s="6"/>
-      <c r="D17" s="6"/>
-      <c r="E17" s="6"/>
-      <c r="F17" s="8"/>
-      <c r="G17" s="6"/>
-      <c r="H17" s="6"/>
-      <c r="I17" s="6" t="str">
-        <f t="array" ref="I17">_xlfn.SWITCH(H17,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
-        <v/>
-      </c>
-      <c r="J17" s="6"/>
-      <c r="K17" s="6"/>
-      <c r="L17" s="6"/>
-    </row>
-    <row r="18" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A18" s="6"/>
-      <c r="B18" s="6"/>
-      <c r="C18" s="6"/>
-      <c r="D18" s="6"/>
-      <c r="E18" s="6"/>
-      <c r="F18" s="8"/>
-      <c r="G18" s="6"/>
-      <c r="H18" s="6"/>
-      <c r="I18" s="6" t="str">
-        <f t="array" ref="I18">_xlfn.SWITCH(H18,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
-        <v/>
-      </c>
-      <c r="J18" s="6"/>
-      <c r="K18" s="6"/>
-      <c r="L18" s="6"/>
-    </row>
-    <row r="19" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A19" s="6"/>
-      <c r="B19" s="6"/>
-      <c r="C19" s="6"/>
-      <c r="D19" s="6"/>
-      <c r="E19" s="6"/>
-      <c r="F19" s="8"/>
-      <c r="G19" s="6"/>
-      <c r="H19" s="6"/>
-      <c r="I19" s="6" t="str">
-        <f t="array" ref="I19">_xlfn.SWITCH(H19,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
-        <v/>
-      </c>
-      <c r="J19" s="6"/>
-      <c r="K19" s="6"/>
-      <c r="L19" s="6"/>
-    </row>
-    <row r="20" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="J19" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="K19" s="14"/>
+      <c r="L19" s="14"/>
+    </row>
+    <row r="20" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A20" s="6"/>
       <c r="B20" s="6"/>
       <c r="C20" s="6"/>
       <c r="D20" s="6"/>
       <c r="E20" s="6"/>
-      <c r="F20" s="5"/>
+      <c r="F20" s="8"/>
       <c r="G20" s="6"/>
       <c r="H20" s="6"/>
-      <c r="I20" s="6" t="str">
-        <f t="array" ref="I20">_xlfn.SWITCH(H20,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
-        <v/>
-      </c>
+      <c r="I20" s="6"/>
       <c r="J20" s="6"/>
       <c r="K20" s="6"/>
       <c r="L20" s="6"/>
     </row>
-    <row r="21" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A21" s="6"/>
       <c r="B21" s="6"/>
       <c r="C21" s="6"/>
       <c r="D21" s="6"/>
       <c r="E21" s="6"/>
-      <c r="F21" s="7"/>
+      <c r="F21" s="8"/>
       <c r="G21" s="6"/>
       <c r="H21" s="6"/>
       <c r="I21" s="6" t="str">
@@ -15389,13 +15663,13 @@
       <c r="K21" s="6"/>
       <c r="L21" s="6"/>
     </row>
-    <row r="22" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A22" s="6"/>
       <c r="B22" s="6"/>
       <c r="C22" s="6"/>
       <c r="D22" s="6"/>
       <c r="E22" s="6"/>
-      <c r="F22" s="7"/>
+      <c r="F22" s="8"/>
       <c r="G22" s="6"/>
       <c r="H22" s="6"/>
       <c r="I22" s="6" t="str">
@@ -15406,13 +15680,13 @@
       <c r="K22" s="6"/>
       <c r="L22" s="6"/>
     </row>
-    <row r="23" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A23" s="6"/>
       <c r="B23" s="6"/>
       <c r="C23" s="6"/>
       <c r="D23" s="6"/>
       <c r="E23" s="6"/>
-      <c r="F23" s="7"/>
+      <c r="F23" s="8"/>
       <c r="G23" s="6"/>
       <c r="H23" s="6"/>
       <c r="I23" s="6" t="str">
@@ -15423,13 +15697,13 @@
       <c r="K23" s="6"/>
       <c r="L23" s="6"/>
     </row>
-    <row r="24" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A24" s="6"/>
       <c r="B24" s="6"/>
       <c r="C24" s="6"/>
       <c r="D24" s="6"/>
       <c r="E24" s="6"/>
-      <c r="F24" s="7"/>
+      <c r="F24" s="8"/>
       <c r="G24" s="6"/>
       <c r="H24" s="6"/>
       <c r="I24" s="6" t="str">
@@ -15440,13 +15714,13 @@
       <c r="K24" s="6"/>
       <c r="L24" s="6"/>
     </row>
-    <row r="25" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A25" s="6"/>
       <c r="B25" s="6"/>
       <c r="C25" s="6"/>
       <c r="D25" s="6"/>
       <c r="E25" s="6"/>
-      <c r="F25" s="7"/>
+      <c r="F25" s="8"/>
       <c r="G25" s="6"/>
       <c r="H25" s="6"/>
       <c r="I25" s="6" t="str">
@@ -15457,13 +15731,13 @@
       <c r="K25" s="6"/>
       <c r="L25" s="6"/>
     </row>
-    <row r="26" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A26" s="6"/>
       <c r="B26" s="6"/>
       <c r="C26" s="6"/>
       <c r="D26" s="6"/>
       <c r="E26" s="6"/>
-      <c r="F26" s="7"/>
+      <c r="F26" s="8"/>
       <c r="G26" s="6"/>
       <c r="H26" s="6"/>
       <c r="I26" s="6" t="str">
@@ -15474,13 +15748,13 @@
       <c r="K26" s="6"/>
       <c r="L26" s="6"/>
     </row>
-    <row r="27" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A27" s="6"/>
       <c r="B27" s="6"/>
       <c r="C27" s="6"/>
       <c r="D27" s="6"/>
       <c r="E27" s="6"/>
-      <c r="F27" s="7"/>
+      <c r="F27" s="8"/>
       <c r="G27" s="6"/>
       <c r="H27" s="6"/>
       <c r="I27" s="6" t="str">
@@ -15491,13 +15765,13 @@
       <c r="K27" s="6"/>
       <c r="L27" s="6"/>
     </row>
-    <row r="28" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A28" s="6"/>
       <c r="B28" s="6"/>
       <c r="C28" s="6"/>
       <c r="D28" s="6"/>
       <c r="E28" s="6"/>
-      <c r="F28" s="7"/>
+      <c r="F28" s="5"/>
       <c r="G28" s="6"/>
       <c r="H28" s="6"/>
       <c r="I28" s="6" t="str">
@@ -15508,7 +15782,7 @@
       <c r="K28" s="6"/>
       <c r="L28" s="6"/>
     </row>
-    <row r="29" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A29" s="6"/>
       <c r="B29" s="6"/>
       <c r="C29" s="6"/>
@@ -15525,7 +15799,7 @@
       <c r="K29" s="6"/>
       <c r="L29" s="6"/>
     </row>
-    <row r="30" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A30" s="6"/>
       <c r="B30" s="6"/>
       <c r="C30" s="6"/>
@@ -15542,7 +15816,7 @@
       <c r="K30" s="6"/>
       <c r="L30" s="6"/>
     </row>
-    <row r="31" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A31" s="6"/>
       <c r="B31" s="6"/>
       <c r="C31" s="6"/>
@@ -15559,7 +15833,7 @@
       <c r="K31" s="6"/>
       <c r="L31" s="6"/>
     </row>
-    <row r="32" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A32" s="6"/>
       <c r="B32" s="6"/>
       <c r="C32" s="6"/>
@@ -15576,7 +15850,7 @@
       <c r="K32" s="6"/>
       <c r="L32" s="6"/>
     </row>
-    <row r="33" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A33" s="6"/>
       <c r="B33" s="6"/>
       <c r="C33" s="6"/>
@@ -15593,7 +15867,7 @@
       <c r="K33" s="6"/>
       <c r="L33" s="6"/>
     </row>
-    <row r="34" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A34" s="6"/>
       <c r="B34" s="6"/>
       <c r="C34" s="6"/>
@@ -15610,7 +15884,7 @@
       <c r="K34" s="6"/>
       <c r="L34" s="6"/>
     </row>
-    <row r="35" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A35" s="6"/>
       <c r="B35" s="6"/>
       <c r="C35" s="6"/>
@@ -15627,7 +15901,7 @@
       <c r="K35" s="6"/>
       <c r="L35" s="6"/>
     </row>
-    <row r="36" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A36" s="6"/>
       <c r="B36" s="6"/>
       <c r="C36" s="6"/>
@@ -15644,7 +15918,7 @@
       <c r="K36" s="6"/>
       <c r="L36" s="6"/>
     </row>
-    <row r="37" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A37" s="6"/>
       <c r="B37" s="6"/>
       <c r="C37" s="6"/>
@@ -15661,13 +15935,13 @@
       <c r="K37" s="6"/>
       <c r="L37" s="6"/>
     </row>
-    <row r="38" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A38" s="6"/>
       <c r="B38" s="6"/>
       <c r="C38" s="6"/>
       <c r="D38" s="6"/>
       <c r="E38" s="6"/>
-      <c r="F38" s="8"/>
+      <c r="F38" s="7"/>
       <c r="G38" s="6"/>
       <c r="H38" s="6"/>
       <c r="I38" s="6" t="str">
@@ -15678,13 +15952,13 @@
       <c r="K38" s="6"/>
       <c r="L38" s="6"/>
     </row>
-    <row r="39" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A39" s="6"/>
       <c r="B39" s="6"/>
       <c r="C39" s="6"/>
       <c r="D39" s="6"/>
       <c r="E39" s="6"/>
-      <c r="F39" s="8"/>
+      <c r="F39" s="7"/>
       <c r="G39" s="6"/>
       <c r="H39" s="6"/>
       <c r="I39" s="6" t="str">
@@ -15695,13 +15969,13 @@
       <c r="K39" s="6"/>
       <c r="L39" s="6"/>
     </row>
-    <row r="40" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A40" s="6"/>
       <c r="B40" s="6"/>
       <c r="C40" s="6"/>
       <c r="D40" s="6"/>
       <c r="E40" s="6"/>
-      <c r="F40" s="8"/>
+      <c r="F40" s="7"/>
       <c r="G40" s="6"/>
       <c r="H40" s="6"/>
       <c r="I40" s="6" t="str">
@@ -15712,13 +15986,13 @@
       <c r="K40" s="6"/>
       <c r="L40" s="6"/>
     </row>
-    <row r="41" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A41" s="6"/>
       <c r="B41" s="6"/>
       <c r="C41" s="6"/>
       <c r="D41" s="6"/>
       <c r="E41" s="6"/>
-      <c r="F41" s="8"/>
+      <c r="F41" s="7"/>
       <c r="G41" s="6"/>
       <c r="H41" s="6"/>
       <c r="I41" s="6" t="str">
@@ -15729,13 +16003,13 @@
       <c r="K41" s="6"/>
       <c r="L41" s="6"/>
     </row>
-    <row r="42" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A42" s="6"/>
       <c r="B42" s="6"/>
       <c r="C42" s="6"/>
       <c r="D42" s="6"/>
       <c r="E42" s="6"/>
-      <c r="F42" s="8"/>
+      <c r="F42" s="7"/>
       <c r="G42" s="6"/>
       <c r="H42" s="6"/>
       <c r="I42" s="6" t="str">
@@ -15746,13 +16020,13 @@
       <c r="K42" s="6"/>
       <c r="L42" s="6"/>
     </row>
-    <row r="43" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A43" s="6"/>
       <c r="B43" s="6"/>
       <c r="C43" s="6"/>
       <c r="D43" s="6"/>
       <c r="E43" s="6"/>
-      <c r="F43" s="8"/>
+      <c r="F43" s="7"/>
       <c r="G43" s="6"/>
       <c r="H43" s="6"/>
       <c r="I43" s="6" t="str">
@@ -15763,7 +16037,7 @@
       <c r="K43" s="6"/>
       <c r="L43" s="6"/>
     </row>
-    <row r="44" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A44" s="6"/>
       <c r="B44" s="6"/>
       <c r="C44" s="6"/>
@@ -15780,7 +16054,7 @@
       <c r="K44" s="6"/>
       <c r="L44" s="6"/>
     </row>
-    <row r="45" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A45" s="6"/>
       <c r="B45" s="6"/>
       <c r="C45" s="6"/>
@@ -15797,13 +16071,13 @@
       <c r="K45" s="6"/>
       <c r="L45" s="6"/>
     </row>
-    <row r="46" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A46" s="6"/>
       <c r="B46" s="6"/>
       <c r="C46" s="6"/>
       <c r="D46" s="6"/>
       <c r="E46" s="6"/>
-      <c r="F46" s="7"/>
+      <c r="F46" s="8"/>
       <c r="G46" s="6"/>
       <c r="H46" s="6"/>
       <c r="I46" s="6" t="str">
@@ -15814,13 +16088,13 @@
       <c r="K46" s="6"/>
       <c r="L46" s="6"/>
     </row>
-    <row r="47" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A47" s="6"/>
       <c r="B47" s="6"/>
       <c r="C47" s="6"/>
       <c r="D47" s="6"/>
       <c r="E47" s="6"/>
-      <c r="F47" s="7"/>
+      <c r="F47" s="8"/>
       <c r="G47" s="6"/>
       <c r="H47" s="6"/>
       <c r="I47" s="6" t="str">
@@ -15831,13 +16105,13 @@
       <c r="K47" s="6"/>
       <c r="L47" s="6"/>
     </row>
-    <row r="48" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A48" s="6"/>
       <c r="B48" s="6"/>
       <c r="C48" s="6"/>
       <c r="D48" s="6"/>
       <c r="E48" s="6"/>
-      <c r="F48" s="7"/>
+      <c r="F48" s="8"/>
       <c r="G48" s="6"/>
       <c r="H48" s="6"/>
       <c r="I48" s="6" t="str">
@@ -15848,13 +16122,13 @@
       <c r="K48" s="6"/>
       <c r="L48" s="6"/>
     </row>
-    <row r="49" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A49" s="6"/>
       <c r="B49" s="6"/>
       <c r="C49" s="6"/>
       <c r="D49" s="6"/>
       <c r="E49" s="6"/>
-      <c r="F49" s="7"/>
+      <c r="F49" s="8"/>
       <c r="G49" s="6"/>
       <c r="H49" s="6"/>
       <c r="I49" s="6" t="str">
@@ -15865,13 +16139,13 @@
       <c r="K49" s="6"/>
       <c r="L49" s="6"/>
     </row>
-    <row r="50" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A50" s="6"/>
       <c r="B50" s="6"/>
       <c r="C50" s="6"/>
       <c r="D50" s="6"/>
       <c r="E50" s="6"/>
-      <c r="F50" s="7"/>
+      <c r="F50" s="8"/>
       <c r="G50" s="6"/>
       <c r="H50" s="6"/>
       <c r="I50" s="6" t="str">
@@ -15882,13 +16156,13 @@
       <c r="K50" s="6"/>
       <c r="L50" s="6"/>
     </row>
-    <row r="51" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A51" s="6"/>
       <c r="B51" s="6"/>
       <c r="C51" s="6"/>
       <c r="D51" s="6"/>
       <c r="E51" s="6"/>
-      <c r="F51" s="7"/>
+      <c r="F51" s="8"/>
       <c r="G51" s="6"/>
       <c r="H51" s="6"/>
       <c r="I51" s="6" t="str">
@@ -15899,7 +16173,7 @@
       <c r="K51" s="6"/>
       <c r="L51" s="6"/>
     </row>
-    <row r="52" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A52" s="6"/>
       <c r="B52" s="6"/>
       <c r="C52" s="6"/>
@@ -15916,7 +16190,7 @@
       <c r="K52" s="6"/>
       <c r="L52" s="6"/>
     </row>
-    <row r="53" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A53" s="6"/>
       <c r="B53" s="6"/>
       <c r="C53" s="6"/>
@@ -15933,7 +16207,7 @@
       <c r="K53" s="6"/>
       <c r="L53" s="6"/>
     </row>
-    <row r="54" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A54" s="6"/>
       <c r="B54" s="6"/>
       <c r="C54" s="6"/>
@@ -15950,13 +16224,13 @@
       <c r="K54" s="6"/>
       <c r="L54" s="6"/>
     </row>
-    <row r="55" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A55" s="6"/>
       <c r="B55" s="6"/>
       <c r="C55" s="6"/>
       <c r="D55" s="6"/>
       <c r="E55" s="6"/>
-      <c r="F55" s="5"/>
+      <c r="F55" s="7"/>
       <c r="G55" s="6"/>
       <c r="H55" s="6"/>
       <c r="I55" s="6" t="str">
@@ -15967,7 +16241,7 @@
       <c r="K55" s="6"/>
       <c r="L55" s="6"/>
     </row>
-    <row r="56" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A56" s="6"/>
       <c r="B56" s="6"/>
       <c r="C56" s="6"/>
@@ -15984,13 +16258,13 @@
       <c r="K56" s="6"/>
       <c r="L56" s="6"/>
     </row>
-    <row r="57" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A57" s="6"/>
       <c r="B57" s="6"/>
       <c r="C57" s="6"/>
       <c r="D57" s="6"/>
       <c r="E57" s="6"/>
-      <c r="F57" s="5"/>
+      <c r="F57" s="7"/>
       <c r="G57" s="6"/>
       <c r="H57" s="6"/>
       <c r="I57" s="6" t="str">
@@ -16001,13 +16275,13 @@
       <c r="K57" s="6"/>
       <c r="L57" s="6"/>
     </row>
-    <row r="58" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A58" s="6"/>
       <c r="B58" s="6"/>
       <c r="C58" s="6"/>
       <c r="D58" s="6"/>
       <c r="E58" s="6"/>
-      <c r="F58" s="5"/>
+      <c r="F58" s="7"/>
       <c r="G58" s="6"/>
       <c r="H58" s="6"/>
       <c r="I58" s="6" t="str">
@@ -16018,7 +16292,7 @@
       <c r="K58" s="6"/>
       <c r="L58" s="6"/>
     </row>
-    <row r="59" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A59" s="6"/>
       <c r="B59" s="6"/>
       <c r="C59" s="6"/>
@@ -16035,7 +16309,7 @@
       <c r="K59" s="6"/>
       <c r="L59" s="6"/>
     </row>
-    <row r="60" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A60" s="6"/>
       <c r="B60" s="6"/>
       <c r="C60" s="6"/>
@@ -16052,7 +16326,7 @@
       <c r="K60" s="6"/>
       <c r="L60" s="6"/>
     </row>
-    <row r="61" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A61" s="6"/>
       <c r="B61" s="6"/>
       <c r="C61" s="6"/>
@@ -16069,7 +16343,7 @@
       <c r="K61" s="6"/>
       <c r="L61" s="6"/>
     </row>
-    <row r="62" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A62" s="6"/>
       <c r="B62" s="6"/>
       <c r="C62" s="6"/>
@@ -16086,13 +16360,13 @@
       <c r="K62" s="6"/>
       <c r="L62" s="6"/>
     </row>
-    <row r="63" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A63" s="6"/>
       <c r="B63" s="6"/>
       <c r="C63" s="6"/>
       <c r="D63" s="6"/>
       <c r="E63" s="6"/>
-      <c r="F63" s="7"/>
+      <c r="F63" s="5"/>
       <c r="G63" s="6"/>
       <c r="H63" s="6"/>
       <c r="I63" s="6" t="str">
@@ -16103,13 +16377,13 @@
       <c r="K63" s="6"/>
       <c r="L63" s="6"/>
     </row>
-    <row r="64" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A64" s="6"/>
       <c r="B64" s="6"/>
       <c r="C64" s="6"/>
       <c r="D64" s="6"/>
       <c r="E64" s="6"/>
-      <c r="F64" s="8"/>
+      <c r="F64" s="7"/>
       <c r="G64" s="6"/>
       <c r="H64" s="6"/>
       <c r="I64" s="6" t="str">
@@ -16120,13 +16394,13 @@
       <c r="K64" s="6"/>
       <c r="L64" s="6"/>
     </row>
-    <row r="65" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A65" s="6"/>
       <c r="B65" s="6"/>
       <c r="C65" s="6"/>
       <c r="D65" s="6"/>
       <c r="E65" s="6"/>
-      <c r="F65" s="8"/>
+      <c r="F65" s="5"/>
       <c r="G65" s="6"/>
       <c r="H65" s="6"/>
       <c r="I65" s="6" t="str">
@@ -16137,13 +16411,13 @@
       <c r="K65" s="6"/>
       <c r="L65" s="6"/>
     </row>
-    <row r="66" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A66" s="6"/>
       <c r="B66" s="6"/>
       <c r="C66" s="6"/>
       <c r="D66" s="6"/>
       <c r="E66" s="6"/>
-      <c r="F66" s="8"/>
+      <c r="F66" s="5"/>
       <c r="G66" s="6"/>
       <c r="H66" s="6"/>
       <c r="I66" s="6" t="str">
@@ -16154,13 +16428,13 @@
       <c r="K66" s="6"/>
       <c r="L66" s="6"/>
     </row>
-    <row r="67" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A67" s="6"/>
       <c r="B67" s="6"/>
       <c r="C67" s="6"/>
       <c r="D67" s="6"/>
       <c r="E67" s="6"/>
-      <c r="F67" s="8"/>
+      <c r="F67" s="7"/>
       <c r="G67" s="6"/>
       <c r="H67" s="6"/>
       <c r="I67" s="6" t="str">
@@ -16171,13 +16445,13 @@
       <c r="K67" s="6"/>
       <c r="L67" s="6"/>
     </row>
-    <row r="68" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A68" s="6"/>
       <c r="B68" s="6"/>
       <c r="C68" s="6"/>
       <c r="D68" s="6"/>
       <c r="E68" s="6"/>
-      <c r="F68" s="8"/>
+      <c r="F68" s="7"/>
       <c r="G68" s="6"/>
       <c r="H68" s="6"/>
       <c r="I68" s="6" t="str">
@@ -16188,13 +16462,13 @@
       <c r="K68" s="6"/>
       <c r="L68" s="6"/>
     </row>
-    <row r="69" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A69" s="6"/>
       <c r="B69" s="6"/>
       <c r="C69" s="6"/>
       <c r="D69" s="6"/>
       <c r="E69" s="6"/>
-      <c r="F69" s="8"/>
+      <c r="F69" s="7"/>
       <c r="G69" s="6"/>
       <c r="H69" s="6"/>
       <c r="I69" s="6" t="str">
@@ -16205,13 +16479,13 @@
       <c r="K69" s="6"/>
       <c r="L69" s="6"/>
     </row>
-    <row r="70" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A70" s="6"/>
       <c r="B70" s="6"/>
       <c r="C70" s="6"/>
       <c r="D70" s="6"/>
       <c r="E70" s="6"/>
-      <c r="F70" s="8"/>
+      <c r="F70" s="7"/>
       <c r="G70" s="6"/>
       <c r="H70" s="6"/>
       <c r="I70" s="6" t="str">
@@ -16222,13 +16496,13 @@
       <c r="K70" s="6"/>
       <c r="L70" s="6"/>
     </row>
-    <row r="71" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A71" s="6"/>
       <c r="B71" s="6"/>
       <c r="C71" s="6"/>
       <c r="D71" s="6"/>
       <c r="E71" s="6"/>
-      <c r="F71" s="8"/>
+      <c r="F71" s="7"/>
       <c r="G71" s="6"/>
       <c r="H71" s="6"/>
       <c r="I71" s="6" t="str">
@@ -16239,7 +16513,7 @@
       <c r="K71" s="6"/>
       <c r="L71" s="6"/>
     </row>
-    <row r="72" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A72" s="6"/>
       <c r="B72" s="6"/>
       <c r="C72" s="6"/>
@@ -16256,7 +16530,7 @@
       <c r="K72" s="6"/>
       <c r="L72" s="6"/>
     </row>
-    <row r="73" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A73" s="6"/>
       <c r="B73" s="6"/>
       <c r="C73" s="6"/>
@@ -16273,7 +16547,7 @@
       <c r="K73" s="6"/>
       <c r="L73" s="6"/>
     </row>
-    <row r="74" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A74" s="6"/>
       <c r="B74" s="6"/>
       <c r="C74" s="6"/>
@@ -16290,7 +16564,7 @@
       <c r="K74" s="6"/>
       <c r="L74" s="6"/>
     </row>
-    <row r="75" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A75" s="6"/>
       <c r="B75" s="6"/>
       <c r="C75" s="6"/>
@@ -16307,7 +16581,7 @@
       <c r="K75" s="6"/>
       <c r="L75" s="6"/>
     </row>
-    <row r="76" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A76" s="6"/>
       <c r="B76" s="6"/>
       <c r="C76" s="6"/>
@@ -16324,7 +16598,7 @@
       <c r="K76" s="6"/>
       <c r="L76" s="6"/>
     </row>
-    <row r="77" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A77" s="6"/>
       <c r="B77" s="6"/>
       <c r="C77" s="6"/>
@@ -16341,7 +16615,7 @@
       <c r="K77" s="6"/>
       <c r="L77" s="6"/>
     </row>
-    <row r="78" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A78" s="6"/>
       <c r="B78" s="6"/>
       <c r="C78" s="6"/>
@@ -16358,7 +16632,7 @@
       <c r="K78" s="6"/>
       <c r="L78" s="6"/>
     </row>
-    <row r="79" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A79" s="6"/>
       <c r="B79" s="6"/>
       <c r="C79" s="6"/>
@@ -16375,7 +16649,7 @@
       <c r="K79" s="6"/>
       <c r="L79" s="6"/>
     </row>
-    <row r="80" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="80" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A80" s="6"/>
       <c r="B80" s="6"/>
       <c r="C80" s="6"/>
@@ -16392,7 +16666,7 @@
       <c r="K80" s="6"/>
       <c r="L80" s="6"/>
     </row>
-    <row r="81" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="81" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A81" s="6"/>
       <c r="B81" s="6"/>
       <c r="C81" s="6"/>
@@ -16409,7 +16683,7 @@
       <c r="K81" s="6"/>
       <c r="L81" s="6"/>
     </row>
-    <row r="82" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="82" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A82" s="6"/>
       <c r="B82" s="6"/>
       <c r="C82" s="6"/>
@@ -16426,7 +16700,7 @@
       <c r="K82" s="6"/>
       <c r="L82" s="6"/>
     </row>
-    <row r="83" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="83" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A83" s="6"/>
       <c r="B83" s="6"/>
       <c r="C83" s="6"/>
@@ -16443,7 +16717,7 @@
       <c r="K83" s="6"/>
       <c r="L83" s="6"/>
     </row>
-    <row r="84" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="84" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A84" s="6"/>
       <c r="B84" s="6"/>
       <c r="C84" s="6"/>
@@ -16460,7 +16734,7 @@
       <c r="K84" s="6"/>
       <c r="L84" s="6"/>
     </row>
-    <row r="85" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="85" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A85" s="6"/>
       <c r="B85" s="6"/>
       <c r="C85" s="6"/>
@@ -16477,7 +16751,7 @@
       <c r="K85" s="6"/>
       <c r="L85" s="6"/>
     </row>
-    <row r="86" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="86" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A86" s="6"/>
       <c r="B86" s="6"/>
       <c r="C86" s="6"/>
@@ -16494,7 +16768,7 @@
       <c r="K86" s="6"/>
       <c r="L86" s="6"/>
     </row>
-    <row r="87" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="87" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A87" s="6"/>
       <c r="B87" s="6"/>
       <c r="C87" s="6"/>
@@ -16511,7 +16785,7 @@
       <c r="K87" s="6"/>
       <c r="L87" s="6"/>
     </row>
-    <row r="88" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="88" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A88" s="6"/>
       <c r="B88" s="6"/>
       <c r="C88" s="6"/>
@@ -16528,7 +16802,7 @@
       <c r="K88" s="6"/>
       <c r="L88" s="6"/>
     </row>
-    <row r="89" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="89" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A89" s="6"/>
       <c r="B89" s="6"/>
       <c r="C89" s="6"/>
@@ -16545,7 +16819,7 @@
       <c r="K89" s="6"/>
       <c r="L89" s="6"/>
     </row>
-    <row r="90" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="90" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A90" s="6"/>
       <c r="B90" s="6"/>
       <c r="C90" s="6"/>
@@ -16562,7 +16836,7 @@
       <c r="K90" s="6"/>
       <c r="L90" s="6"/>
     </row>
-    <row r="91" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="91" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A91" s="6"/>
       <c r="B91" s="6"/>
       <c r="C91" s="6"/>
@@ -16579,7 +16853,7 @@
       <c r="K91" s="6"/>
       <c r="L91" s="6"/>
     </row>
-    <row r="92" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="92" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A92" s="6"/>
       <c r="B92" s="6"/>
       <c r="C92" s="6"/>
@@ -16596,7 +16870,7 @@
       <c r="K92" s="6"/>
       <c r="L92" s="6"/>
     </row>
-    <row r="93" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="93" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A93" s="6"/>
       <c r="B93" s="6"/>
       <c r="C93" s="6"/>
@@ -16613,7 +16887,7 @@
       <c r="K93" s="6"/>
       <c r="L93" s="6"/>
     </row>
-    <row r="94" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="94" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A94" s="6"/>
       <c r="B94" s="6"/>
       <c r="C94" s="6"/>
@@ -16630,7 +16904,7 @@
       <c r="K94" s="6"/>
       <c r="L94" s="6"/>
     </row>
-    <row r="95" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="95" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A95" s="6"/>
       <c r="B95" s="6"/>
       <c r="C95" s="6"/>
@@ -16647,7 +16921,7 @@
       <c r="K95" s="6"/>
       <c r="L95" s="6"/>
     </row>
-    <row r="96" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="96" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A96" s="6"/>
       <c r="B96" s="6"/>
       <c r="C96" s="6"/>
@@ -16664,7 +16938,7 @@
       <c r="K96" s="6"/>
       <c r="L96" s="6"/>
     </row>
-    <row r="97" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="97" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A97" s="6"/>
       <c r="B97" s="6"/>
       <c r="C97" s="6"/>
@@ -16681,7 +16955,7 @@
       <c r="K97" s="6"/>
       <c r="L97" s="6"/>
     </row>
-    <row r="98" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="98" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A98" s="6"/>
       <c r="B98" s="6"/>
       <c r="C98" s="6"/>
@@ -16698,7 +16972,7 @@
       <c r="K98" s="6"/>
       <c r="L98" s="6"/>
     </row>
-    <row r="99" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="99" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A99" s="6"/>
       <c r="B99" s="6"/>
       <c r="C99" s="6"/>
@@ -16715,7 +16989,150 @@
       <c r="K99" s="6"/>
       <c r="L99" s="6"/>
     </row>
+    <row r="100" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A100" s="6"/>
+      <c r="B100" s="6"/>
+      <c r="C100" s="6"/>
+      <c r="D100" s="6"/>
+      <c r="E100" s="6"/>
+      <c r="F100" s="8"/>
+      <c r="G100" s="6"/>
+      <c r="H100" s="6"/>
+      <c r="I100" s="6" t="str">
+        <f t="array" ref="I100">_xlfn.SWITCH(H100,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
+        <v/>
+      </c>
+      <c r="J100" s="6"/>
+      <c r="K100" s="6"/>
+      <c r="L100" s="6"/>
+    </row>
+    <row r="101" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A101" s="6"/>
+      <c r="B101" s="6"/>
+      <c r="C101" s="6"/>
+      <c r="D101" s="6"/>
+      <c r="E101" s="6"/>
+      <c r="F101" s="8"/>
+      <c r="G101" s="6"/>
+      <c r="H101" s="6"/>
+      <c r="I101" s="6" t="str">
+        <f t="array" ref="I101">_xlfn.SWITCH(H101,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
+        <v/>
+      </c>
+      <c r="J101" s="6"/>
+      <c r="K101" s="6"/>
+      <c r="L101" s="6"/>
+    </row>
+    <row r="102" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A102" s="6"/>
+      <c r="B102" s="6"/>
+      <c r="C102" s="6"/>
+      <c r="D102" s="6"/>
+      <c r="E102" s="6"/>
+      <c r="F102" s="8"/>
+      <c r="G102" s="6"/>
+      <c r="H102" s="6"/>
+      <c r="I102" s="6" t="str">
+        <f t="array" ref="I102">_xlfn.SWITCH(H102,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
+        <v/>
+      </c>
+      <c r="J102" s="6"/>
+      <c r="K102" s="6"/>
+      <c r="L102" s="6"/>
+    </row>
+    <row r="103" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A103" s="6"/>
+      <c r="B103" s="6"/>
+      <c r="C103" s="6"/>
+      <c r="D103" s="6"/>
+      <c r="E103" s="6"/>
+      <c r="F103" s="8"/>
+      <c r="G103" s="6"/>
+      <c r="H103" s="6"/>
+      <c r="I103" s="6" t="str">
+        <f t="array" ref="I103">_xlfn.SWITCH(H103,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
+        <v/>
+      </c>
+      <c r="J103" s="6"/>
+      <c r="K103" s="6"/>
+      <c r="L103" s="6"/>
+    </row>
+    <row r="104" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A104" s="6"/>
+      <c r="B104" s="6"/>
+      <c r="C104" s="6"/>
+      <c r="D104" s="6"/>
+      <c r="E104" s="6"/>
+      <c r="F104" s="8"/>
+      <c r="G104" s="6"/>
+      <c r="H104" s="6"/>
+      <c r="I104" s="6" t="str">
+        <f t="array" ref="I104">_xlfn.SWITCH(H104,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
+        <v/>
+      </c>
+      <c r="J104" s="6"/>
+      <c r="K104" s="6"/>
+      <c r="L104" s="6"/>
+    </row>
+    <row r="105" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A105" s="6"/>
+      <c r="B105" s="6"/>
+      <c r="C105" s="6"/>
+      <c r="D105" s="6"/>
+      <c r="E105" s="6"/>
+      <c r="F105" s="8"/>
+      <c r="G105" s="6"/>
+      <c r="H105" s="6"/>
+      <c r="I105" s="6" t="str">
+        <f t="array" ref="I105">_xlfn.SWITCH(H105,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
+        <v/>
+      </c>
+      <c r="J105" s="6"/>
+      <c r="K105" s="6"/>
+      <c r="L105" s="6"/>
+    </row>
+    <row r="106" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A106" s="6"/>
+      <c r="B106" s="6"/>
+      <c r="C106" s="6"/>
+      <c r="D106" s="6"/>
+      <c r="E106" s="6"/>
+      <c r="F106" s="8"/>
+      <c r="G106" s="6"/>
+      <c r="H106" s="6"/>
+      <c r="I106" s="6" t="str">
+        <f t="array" ref="I106">_xlfn.SWITCH(H106,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
+        <v/>
+      </c>
+      <c r="J106" s="6"/>
+      <c r="K106" s="6"/>
+      <c r="L106" s="6"/>
+    </row>
+    <row r="107" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A107" s="6"/>
+      <c r="B107" s="6"/>
+      <c r="C107" s="6"/>
+      <c r="D107" s="6"/>
+      <c r="E107" s="6"/>
+      <c r="F107" s="8"/>
+      <c r="G107" s="6"/>
+      <c r="H107" s="6"/>
+      <c r="I107" s="6" t="str">
+        <f t="array" ref="I107">_xlfn.SWITCH(H107,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
+        <v/>
+      </c>
+      <c r="J107" s="6"/>
+      <c r="K107" s="6"/>
+      <c r="L107" s="6"/>
+    </row>
   </sheetData>
+  <autoFilter ref="J1:J107" xr:uid="{AA30D3B6-4BBC-427B-918A-C301767B692F}">
+    <filterColumn colId="0">
+      <filters>
+        <filter val="ToDo"/>
+      </filters>
+    </filterColumn>
+  </autoFilter>
   <phoneticPr fontId="4" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -16723,7 +17140,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D768F6E0-6E10-4552-9483-4F3EB0450BB5}">
-  <dimension ref="A1:L10"/>
+  <dimension ref="A1:L14"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="4.88671875" style="1" bestFit="1" customWidth="1"/>
@@ -16758,12 +17175,12 @@
         <v>46272</v>
       </c>
       <c r="C2" s="19">
-        <f>44-SUM(E$2:E2)</f>
-        <v>44</v>
+        <f>61-SUM(E$2:E2)</f>
+        <v>61</v>
       </c>
       <c r="D2" s="20">
-        <f>44*(1-(A2/8))</f>
-        <v>44</v>
+        <f>61*(1-(A2/12))</f>
+        <v>61</v>
       </c>
       <c r="E2" s="20">
         <v>0</v>
@@ -16777,12 +17194,12 @@
         <v>46273</v>
       </c>
       <c r="C3" s="19">
-        <f>44-SUM(E$2:E3)</f>
-        <v>44</v>
+        <f>61-SUM(E$2:E3)</f>
+        <v>61</v>
       </c>
       <c r="D3" s="20">
-        <f t="shared" ref="D3:D10" si="0">44*(1-(A3/8))</f>
-        <v>38.5</v>
+        <f t="shared" ref="D3:D14" si="0">61*(1-(A3/12))</f>
+        <v>55.916666666666664</v>
       </c>
       <c r="E3" s="20">
         <v>0</v>
@@ -16796,12 +17213,12 @@
         <v>46274</v>
       </c>
       <c r="C4" s="19">
-        <f>44-SUM(E$2:E4)</f>
-        <v>44</v>
+        <f>61-SUM(E$2:E4)</f>
+        <v>61</v>
       </c>
       <c r="D4" s="20">
         <f t="shared" si="0"/>
-        <v>33</v>
+        <v>50.833333333333336</v>
       </c>
       <c r="E4" s="20">
         <v>0</v>
@@ -16816,12 +17233,12 @@
         <v>46275</v>
       </c>
       <c r="C5" s="19">
-        <f>44-SUM(E$2:E5)</f>
-        <v>31</v>
+        <f>61-SUM(E$2:E5)</f>
+        <v>48</v>
       </c>
       <c r="D5" s="20">
         <f t="shared" si="0"/>
-        <v>27.5</v>
+        <v>45.75</v>
       </c>
       <c r="E5" s="20">
         <v>13</v>
@@ -16835,12 +17252,12 @@
         <v>46276</v>
       </c>
       <c r="C6" s="19">
-        <f>44-SUM(E$2:E6)</f>
-        <v>18</v>
+        <f>61-SUM(E$2:E6)</f>
+        <v>35</v>
       </c>
       <c r="D6" s="20">
         <f t="shared" si="0"/>
-        <v>22</v>
+        <v>40.666666666666671</v>
       </c>
       <c r="E6" s="20">
         <v>13</v>
@@ -16854,14 +17271,16 @@
         <v>46279</v>
       </c>
       <c r="C7" s="19">
-        <f>44-SUM(E$2:E7)</f>
-        <v>18</v>
+        <f>61-SUM(E$2:E7)</f>
+        <v>35</v>
       </c>
       <c r="D7" s="20">
         <f t="shared" si="0"/>
-        <v>16.5</v>
-      </c>
-      <c r="E7" s="20"/>
+        <v>35.583333333333329</v>
+      </c>
+      <c r="E7" s="20">
+        <v>0</v>
+      </c>
     </row>
     <row r="8" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A8" s="17">
@@ -16871,14 +17290,16 @@
         <v>46280</v>
       </c>
       <c r="C8" s="19">
-        <f>44-SUM(E$2:E8)</f>
-        <v>18</v>
+        <f>61-SUM(E$2:E8)</f>
+        <v>35</v>
       </c>
       <c r="D8" s="20">
         <f t="shared" si="0"/>
-        <v>11</v>
-      </c>
-      <c r="E8" s="20"/>
+        <v>30.5</v>
+      </c>
+      <c r="E8" s="20">
+        <v>0</v>
+      </c>
     </row>
     <row r="9" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A9" s="17">
@@ -16888,14 +17309,16 @@
         <v>46281</v>
       </c>
       <c r="C9" s="19">
-        <f>44-SUM(E$2:E9)</f>
-        <v>18</v>
+        <f>61-SUM(E$2:E9)</f>
+        <v>35</v>
       </c>
       <c r="D9" s="20">
         <f t="shared" si="0"/>
-        <v>5.5</v>
-      </c>
-      <c r="E9" s="20"/>
+        <v>25.416666666666664</v>
+      </c>
+      <c r="E9" s="20">
+        <v>0</v>
+      </c>
     </row>
     <row r="10" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A10" s="17">
@@ -16905,14 +17328,92 @@
         <v>46282</v>
       </c>
       <c r="C10" s="19">
-        <f>44-SUM(E$2:E10)</f>
-        <v>18</v>
+        <f>61-SUM(E$2:E10)</f>
+        <v>30</v>
       </c>
       <c r="D10" s="20">
         <f t="shared" si="0"/>
+        <v>20.333333333333336</v>
+      </c>
+      <c r="E10" s="20">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="11" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A11" s="17">
+        <v>9</v>
+      </c>
+      <c r="B11" s="18">
+        <v>46283</v>
+      </c>
+      <c r="C11" s="19">
+        <f>61-SUM(E$2:E11)</f>
+        <v>25</v>
+      </c>
+      <c r="D11" s="20">
+        <f t="shared" si="0"/>
+        <v>15.25</v>
+      </c>
+      <c r="E11" s="20">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="12" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A12" s="17">
+        <v>10</v>
+      </c>
+      <c r="B12" s="18">
+        <v>46286</v>
+      </c>
+      <c r="C12" s="19">
+        <f>61-SUM(E$2:E12)</f>
+        <v>17</v>
+      </c>
+      <c r="D12" s="20">
+        <f t="shared" si="0"/>
+        <v>10.166666666666664</v>
+      </c>
+      <c r="E12" s="20">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="13" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A13" s="17">
+        <v>11</v>
+      </c>
+      <c r="B13" s="18">
+        <v>46287</v>
+      </c>
+      <c r="C13" s="19">
+        <f>61-SUM(E$2:E13)</f>
+        <v>17</v>
+      </c>
+      <c r="D13" s="20">
+        <f t="shared" si="0"/>
+        <v>5.0833333333333357</v>
+      </c>
+      <c r="E13" s="20">
         <v>0</v>
       </c>
-      <c r="E10" s="20"/>
+    </row>
+    <row r="14" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A14" s="17">
+        <v>12</v>
+      </c>
+      <c r="B14" s="18">
+        <v>46288</v>
+      </c>
+      <c r="C14" s="19">
+        <f>61-SUM(E$2:E14)</f>
+        <v>17</v>
+      </c>
+      <c r="D14" s="20">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="E14" s="20">
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Business Analysis/checkupp_sprint_plan_2026.xlsx
+++ b/Business Analysis/checkupp_sprint_plan_2026.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitHub\CheckUpp\Business Analysis\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{782DCFAC-0583-462F-A2C1-C10DDA8407FA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{50133B31-C3F8-4D0A-8A06-5E3644B59B08}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="2" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="2" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sprint 01" sheetId="1" r:id="rId1"/>
@@ -19,10 +19,12 @@
     <sheet name="Sprint 02 Burndown" sheetId="6" r:id="rId4"/>
     <sheet name="Sprint 03" sheetId="5" r:id="rId5"/>
     <sheet name="Sprint 03 Burndown" sheetId="8" r:id="rId6"/>
+    <sheet name="Sprint 04" sheetId="9" r:id="rId7"/>
+    <sheet name="Sprint 04 Burndown" sheetId="10" r:id="rId8"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Sprint 01'!$E$1:$E$112</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Sprint 03'!$J$1:$J$107</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Sprint 03'!$J$1:$J$103</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -62,7 +64,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="447" uniqueCount="140">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="459" uniqueCount="140">
   <si>
     <t>Epic</t>
   </si>
@@ -7565,43 +7567,43 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="13"/>
                 <c:pt idx="0">
-                  <c:v>61</c:v>
+                  <c:v>52</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>61</c:v>
+                  <c:v>52</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>61</c:v>
+                  <c:v>52</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>48</c:v>
+                  <c:v>39</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>35</c:v>
+                  <c:v>26</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>35</c:v>
+                  <c:v>26</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>35</c:v>
+                  <c:v>26</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>35</c:v>
+                  <c:v>26</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>30</c:v>
+                  <c:v>21</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>25</c:v>
+                  <c:v>16</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>17</c:v>
+                  <c:v>8</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>17</c:v>
+                  <c:v>8</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>17</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -7694,40 +7696,40 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="13"/>
                 <c:pt idx="0">
-                  <c:v>61</c:v>
+                  <c:v>52</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>55.916666666666664</c:v>
+                  <c:v>47.666666666666664</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>50.833333333333336</c:v>
+                  <c:v>43.333333333333336</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>45.75</c:v>
+                  <c:v>39</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>40.666666666666671</c:v>
+                  <c:v>34.666666666666671</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>35.583333333333329</c:v>
+                  <c:v>30.333333333333329</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>30.5</c:v>
+                  <c:v>26</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>25.416666666666664</c:v>
+                  <c:v>21.666666666666664</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>20.333333333333336</c:v>
+                  <c:v>17.333333333333336</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>15.25</c:v>
+                  <c:v>13</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>10.166666666666664</c:v>
+                  <c:v>8.6666666666666643</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>5.0833333333333357</c:v>
+                  <c:v>4.3333333333333357</c:v>
                 </c:pt>
                 <c:pt idx="12">
                   <c:v>0</c:v>
@@ -15018,8 +15020,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AA30D3B6-4BBC-427B-918A-C301767B692F}">
-  <sheetPr filterMode="1"/>
-  <dimension ref="A1:L107"/>
+  <dimension ref="A1:L103"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="6.88671875" bestFit="1" customWidth="1"/>
@@ -15074,7 +15075,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="2" spans="1:12" ht="201.6" hidden="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:12" ht="201.6" x14ac:dyDescent="0.3">
       <c r="A2" s="12">
         <v>1</v>
       </c>
@@ -15105,7 +15106,7 @@
       <c r="K2" s="12"/>
       <c r="L2" s="12"/>
     </row>
-    <row r="3" spans="1:12" ht="172.8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:12" ht="172.8" x14ac:dyDescent="0.3">
       <c r="A3" s="12">
         <v>2</v>
       </c>
@@ -15136,7 +15137,7 @@
       <c r="K3" s="12"/>
       <c r="L3" s="12"/>
     </row>
-    <row r="4" spans="1:12" ht="172.8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:12" ht="172.8" x14ac:dyDescent="0.3">
       <c r="A4" s="12">
         <v>3</v>
       </c>
@@ -15167,7 +15168,7 @@
       <c r="K4" s="12"/>
       <c r="L4" s="12"/>
     </row>
-    <row r="5" spans="1:12" ht="172.8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:12" ht="172.8" x14ac:dyDescent="0.3">
       <c r="A5" s="12">
         <v>4</v>
       </c>
@@ -15198,9 +15199,9 @@
       <c r="K5" s="12"/>
       <c r="L5" s="12"/>
     </row>
-    <row r="6" spans="1:12" ht="230.4" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:12" ht="273.60000000000002" x14ac:dyDescent="0.3">
       <c r="A6" s="12">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="B6" s="12" t="s">
         <v>94</v>
@@ -15211,10 +15212,10 @@
         <v>31</v>
       </c>
       <c r="F6" s="13" t="s">
-        <v>132</v>
+        <v>136</v>
       </c>
       <c r="G6" s="12" t="s">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="H6" s="12" t="s">
         <v>23</v>
@@ -15224,14 +15225,14 @@
         <v>2</v>
       </c>
       <c r="J6" s="12" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="K6" s="12"/>
       <c r="L6" s="12"/>
     </row>
-    <row r="7" spans="1:12" ht="316.8" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:12" ht="216" x14ac:dyDescent="0.3">
       <c r="A7" s="12">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="B7" s="12" t="s">
         <v>94</v>
@@ -15239,13 +15240,13 @@
       <c r="C7" s="12"/>
       <c r="D7" s="12"/>
       <c r="E7" s="12" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="F7" s="13" t="s">
-        <v>133</v>
+        <v>137</v>
       </c>
       <c r="G7" s="12" t="s">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="H7" s="12" t="s">
         <v>23</v>
@@ -15255,14 +15256,14 @@
         <v>2</v>
       </c>
       <c r="J7" s="12" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="K7" s="12"/>
       <c r="L7" s="12"/>
     </row>
     <row r="8" spans="1:12" ht="244.8" x14ac:dyDescent="0.3">
       <c r="A8" s="12">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="B8" s="12" t="s">
         <v>94</v>
@@ -15273,10 +15274,10 @@
         <v>31</v>
       </c>
       <c r="F8" s="13" t="s">
-        <v>134</v>
+        <v>138</v>
       </c>
       <c r="G8" s="12" t="s">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="H8" s="12" t="s">
         <v>23</v>
@@ -15286,14 +15287,14 @@
         <v>2</v>
       </c>
       <c r="J8" s="12" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="K8" s="12"/>
       <c r="L8" s="12"/>
     </row>
-    <row r="9" spans="1:12" ht="201.6" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:12" ht="187.2" x14ac:dyDescent="0.3">
       <c r="A9" s="12">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="B9" s="12" t="s">
         <v>94</v>
@@ -15304,151 +15305,151 @@
         <v>22</v>
       </c>
       <c r="F9" s="13" t="s">
-        <v>135</v>
+        <v>139</v>
       </c>
       <c r="G9" s="12" t="s">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="H9" s="12" t="s">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="I9" s="12">
         <f t="array" ref="I9">_xlfn.SWITCH(H9,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J9" s="12" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="K9" s="12"/>
       <c r="L9" s="12"/>
     </row>
-    <row r="10" spans="1:12" ht="273.60000000000002" x14ac:dyDescent="0.3">
-      <c r="A10" s="12">
-        <v>9</v>
-      </c>
-      <c r="B10" s="12" t="s">
-        <v>94</v>
-      </c>
-      <c r="C10" s="12"/>
-      <c r="D10" s="12"/>
-      <c r="E10" s="12" t="s">
+    <row r="10" spans="1:12" ht="100.8" x14ac:dyDescent="0.3">
+      <c r="A10" s="14">
+        <v>13</v>
+      </c>
+      <c r="B10" s="14" t="s">
+        <v>124</v>
+      </c>
+      <c r="C10" s="14"/>
+      <c r="D10" s="14"/>
+      <c r="E10" s="14" t="s">
+        <v>22</v>
+      </c>
+      <c r="F10" s="15" t="s">
+        <v>125</v>
+      </c>
+      <c r="G10" s="14" t="s">
+        <v>29</v>
+      </c>
+      <c r="H10" s="14" t="s">
+        <v>30</v>
+      </c>
+      <c r="I10" s="14">
+        <f t="array" ref="I10">_xlfn.SWITCH(H10,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
+        <v>5</v>
+      </c>
+      <c r="J10" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="K10" s="14"/>
+      <c r="L10" s="14"/>
+    </row>
+    <row r="11" spans="1:12" ht="100.8" x14ac:dyDescent="0.3">
+      <c r="A11" s="14">
+        <v>14</v>
+      </c>
+      <c r="B11" s="14" t="s">
+        <v>124</v>
+      </c>
+      <c r="C11" s="14"/>
+      <c r="D11" s="14"/>
+      <c r="E11" s="14" t="s">
         <v>31</v>
       </c>
-      <c r="F10" s="13" t="s">
-        <v>136</v>
-      </c>
-      <c r="G10" s="12" t="s">
+      <c r="F11" s="15" t="s">
+        <v>126</v>
+      </c>
+      <c r="G11" s="14" t="s">
         <v>29</v>
       </c>
-      <c r="H10" s="12" t="s">
+      <c r="H11" s="14" t="s">
         <v>23</v>
       </c>
-      <c r="I10" s="12">
-        <f t="array" ref="I10">_xlfn.SWITCH(H10,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
-        <v>2</v>
-      </c>
-      <c r="J10" s="12" t="s">
-        <v>76</v>
-      </c>
-      <c r="K10" s="12"/>
-      <c r="L10" s="12"/>
-    </row>
-    <row r="11" spans="1:12" ht="216" x14ac:dyDescent="0.3">
-      <c r="A11" s="12">
-        <v>10</v>
-      </c>
-      <c r="B11" s="12" t="s">
-        <v>94</v>
-      </c>
-      <c r="C11" s="12"/>
-      <c r="D11" s="12"/>
-      <c r="E11" s="12" t="s">
-        <v>20</v>
-      </c>
-      <c r="F11" s="13" t="s">
-        <v>137</v>
-      </c>
-      <c r="G11" s="12" t="s">
-        <v>29</v>
-      </c>
-      <c r="H11" s="12" t="s">
-        <v>23</v>
-      </c>
-      <c r="I11" s="12">
+      <c r="I11" s="14">
         <f t="array" ref="I11">_xlfn.SWITCH(H11,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
         <v>2</v>
       </c>
-      <c r="J11" s="12" t="s">
-        <v>76</v>
-      </c>
-      <c r="K11" s="12"/>
-      <c r="L11" s="12"/>
-    </row>
-    <row r="12" spans="1:12" ht="244.8" x14ac:dyDescent="0.3">
-      <c r="A12" s="12">
-        <v>11</v>
-      </c>
-      <c r="B12" s="12" t="s">
-        <v>94</v>
-      </c>
-      <c r="C12" s="12"/>
-      <c r="D12" s="12"/>
-      <c r="E12" s="12" t="s">
-        <v>31</v>
-      </c>
-      <c r="F12" s="13" t="s">
-        <v>138</v>
-      </c>
-      <c r="G12" s="12" t="s">
+      <c r="J11" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="K11" s="14"/>
+      <c r="L11" s="14"/>
+    </row>
+    <row r="12" spans="1:12" ht="115.2" x14ac:dyDescent="0.3">
+      <c r="A12" s="14">
+        <v>15</v>
+      </c>
+      <c r="B12" s="14" t="s">
+        <v>124</v>
+      </c>
+      <c r="C12" s="14"/>
+      <c r="D12" s="14"/>
+      <c r="E12" s="14" t="s">
+        <v>20</v>
+      </c>
+      <c r="F12" s="15" t="s">
+        <v>127</v>
+      </c>
+      <c r="G12" s="14" t="s">
         <v>29</v>
       </c>
-      <c r="H12" s="12" t="s">
-        <v>23</v>
-      </c>
-      <c r="I12" s="12">
+      <c r="H12" s="14" t="s">
+        <v>27</v>
+      </c>
+      <c r="I12" s="14">
         <f t="array" ref="I12">_xlfn.SWITCH(H12,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
-        <v>2</v>
-      </c>
-      <c r="J12" s="12" t="s">
-        <v>76</v>
-      </c>
-      <c r="K12" s="12"/>
-      <c r="L12" s="12"/>
-    </row>
-    <row r="13" spans="1:12" ht="187.2" x14ac:dyDescent="0.3">
-      <c r="A13" s="12">
-        <v>12</v>
-      </c>
-      <c r="B13" s="12" t="s">
-        <v>94</v>
-      </c>
-      <c r="C13" s="12"/>
-      <c r="D13" s="12"/>
-      <c r="E13" s="12" t="s">
-        <v>22</v>
-      </c>
-      <c r="F13" s="13" t="s">
-        <v>139</v>
-      </c>
-      <c r="G13" s="12" t="s">
+        <v>3</v>
+      </c>
+      <c r="J12" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="K12" s="14"/>
+      <c r="L12" s="14"/>
+    </row>
+    <row r="13" spans="1:12" ht="115.2" x14ac:dyDescent="0.3">
+      <c r="A13" s="14">
+        <v>16</v>
+      </c>
+      <c r="B13" s="14" t="s">
+        <v>124</v>
+      </c>
+      <c r="C13" s="14"/>
+      <c r="D13" s="14"/>
+      <c r="E13" s="14" t="s">
+        <v>20</v>
+      </c>
+      <c r="F13" s="15" t="s">
+        <v>128</v>
+      </c>
+      <c r="G13" s="14" t="s">
         <v>29</v>
       </c>
-      <c r="H13" s="12" t="s">
-        <v>23</v>
-      </c>
-      <c r="I13" s="12">
+      <c r="H13" s="14" t="s">
+        <v>30</v>
+      </c>
+      <c r="I13" s="14">
         <f t="array" ref="I13">_xlfn.SWITCH(H13,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
-        <v>2</v>
-      </c>
-      <c r="J13" s="12" t="s">
-        <v>76</v>
-      </c>
-      <c r="K13" s="12"/>
-      <c r="L13" s="12"/>
-    </row>
-    <row r="14" spans="1:12" ht="100.8" hidden="1" x14ac:dyDescent="0.3">
+        <v>5</v>
+      </c>
+      <c r="J13" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="K13" s="14"/>
+      <c r="L13" s="14"/>
+    </row>
+    <row r="14" spans="1:12" ht="100.8" x14ac:dyDescent="0.3">
       <c r="A14" s="14">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B14" s="14" t="s">
         <v>124</v>
@@ -15456,20 +15457,20 @@
       <c r="C14" s="14"/>
       <c r="D14" s="14"/>
       <c r="E14" s="14" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="F14" s="15" t="s">
-        <v>125</v>
+        <v>129</v>
       </c>
       <c r="G14" s="14" t="s">
         <v>29</v>
       </c>
       <c r="H14" s="14" t="s">
-        <v>30</v>
+        <v>23</v>
       </c>
       <c r="I14" s="14">
         <f t="array" ref="I14">_xlfn.SWITCH(H14,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="J14" s="14" t="s">
         <v>75</v>
@@ -15477,9 +15478,9 @@
       <c r="K14" s="14"/>
       <c r="L14" s="14"/>
     </row>
-    <row r="15" spans="1:12" ht="100.8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:12" ht="100.8" x14ac:dyDescent="0.3">
       <c r="A15" s="14">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="B15" s="14" t="s">
         <v>124</v>
@@ -15487,20 +15488,20 @@
       <c r="C15" s="14"/>
       <c r="D15" s="14"/>
       <c r="E15" s="14" t="s">
-        <v>31</v>
+        <v>20</v>
       </c>
       <c r="F15" s="15" t="s">
-        <v>126</v>
+        <v>130</v>
       </c>
       <c r="G15" s="14" t="s">
         <v>29</v>
       </c>
       <c r="H15" s="14" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="I15" s="14">
         <f t="array" ref="I15">_xlfn.SWITCH(H15,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J15" s="14" t="s">
         <v>75</v>
@@ -15508,131 +15509,72 @@
       <c r="K15" s="14"/>
       <c r="L15" s="14"/>
     </row>
-    <row r="16" spans="1:12" ht="115.2" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="14">
-        <v>15</v>
-      </c>
-      <c r="B16" s="14" t="s">
-        <v>124</v>
-      </c>
-      <c r="C16" s="14"/>
-      <c r="D16" s="14"/>
-      <c r="E16" s="14" t="s">
-        <v>20</v>
-      </c>
-      <c r="F16" s="15" t="s">
-        <v>127</v>
-      </c>
-      <c r="G16" s="14" t="s">
-        <v>29</v>
-      </c>
-      <c r="H16" s="14" t="s">
-        <v>27</v>
-      </c>
-      <c r="I16" s="14">
-        <f t="array" ref="I16">_xlfn.SWITCH(H16,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
-        <v>3</v>
-      </c>
-      <c r="J16" s="14" t="s">
-        <v>75</v>
-      </c>
-      <c r="K16" s="14"/>
-      <c r="L16" s="14"/>
-    </row>
-    <row r="17" spans="1:12" ht="115.2" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="14">
-        <v>16</v>
-      </c>
-      <c r="B17" s="14" t="s">
-        <v>124</v>
-      </c>
-      <c r="C17" s="14"/>
-      <c r="D17" s="14"/>
-      <c r="E17" s="14" t="s">
-        <v>20</v>
-      </c>
-      <c r="F17" s="15" t="s">
-        <v>128</v>
-      </c>
-      <c r="G17" s="14" t="s">
-        <v>29</v>
-      </c>
-      <c r="H17" s="14" t="s">
-        <v>30</v>
-      </c>
-      <c r="I17" s="14">
+    <row r="16" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A16" s="6"/>
+      <c r="B16" s="6"/>
+      <c r="C16" s="6"/>
+      <c r="D16" s="6"/>
+      <c r="E16" s="6"/>
+      <c r="F16" s="8"/>
+      <c r="G16" s="6"/>
+      <c r="H16" s="6"/>
+      <c r="I16" s="6"/>
+      <c r="J16" s="6"/>
+      <c r="K16" s="6"/>
+      <c r="L16" s="6"/>
+    </row>
+    <row r="17" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A17" s="6"/>
+      <c r="B17" s="6"/>
+      <c r="C17" s="6"/>
+      <c r="D17" s="6"/>
+      <c r="E17" s="6"/>
+      <c r="F17" s="8"/>
+      <c r="G17" s="6"/>
+      <c r="H17" s="6"/>
+      <c r="I17" s="6" t="str">
         <f t="array" ref="I17">_xlfn.SWITCH(H17,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
-        <v>5</v>
-      </c>
-      <c r="J17" s="14" t="s">
-        <v>75</v>
-      </c>
-      <c r="K17" s="14"/>
-      <c r="L17" s="14"/>
-    </row>
-    <row r="18" spans="1:12" ht="100.8" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A18" s="14">
-        <v>17</v>
-      </c>
-      <c r="B18" s="14" t="s">
-        <v>124</v>
-      </c>
-      <c r="C18" s="14"/>
-      <c r="D18" s="14"/>
-      <c r="E18" s="14" t="s">
-        <v>20</v>
-      </c>
-      <c r="F18" s="15" t="s">
-        <v>129</v>
-      </c>
-      <c r="G18" s="14" t="s">
-        <v>29</v>
-      </c>
-      <c r="H18" s="14" t="s">
-        <v>23</v>
-      </c>
-      <c r="I18" s="14">
+        <v/>
+      </c>
+      <c r="J17" s="6"/>
+      <c r="K17" s="6"/>
+      <c r="L17" s="6"/>
+    </row>
+    <row r="18" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A18" s="6"/>
+      <c r="B18" s="6"/>
+      <c r="C18" s="6"/>
+      <c r="D18" s="6"/>
+      <c r="E18" s="6"/>
+      <c r="F18" s="8"/>
+      <c r="G18" s="6"/>
+      <c r="H18" s="6"/>
+      <c r="I18" s="6" t="str">
         <f t="array" ref="I18">_xlfn.SWITCH(H18,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
-        <v>2</v>
-      </c>
-      <c r="J18" s="14" t="s">
-        <v>75</v>
-      </c>
-      <c r="K18" s="14"/>
-      <c r="L18" s="14"/>
-    </row>
-    <row r="19" spans="1:12" ht="100.8" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A19" s="14">
-        <v>18</v>
-      </c>
-      <c r="B19" s="14" t="s">
-        <v>124</v>
-      </c>
-      <c r="C19" s="14"/>
-      <c r="D19" s="14"/>
-      <c r="E19" s="14" t="s">
-        <v>20</v>
-      </c>
-      <c r="F19" s="15" t="s">
-        <v>130</v>
-      </c>
-      <c r="G19" s="14" t="s">
-        <v>29</v>
-      </c>
-      <c r="H19" s="14" t="s">
-        <v>19</v>
-      </c>
-      <c r="I19" s="14">
+        <v/>
+      </c>
+      <c r="J18" s="6"/>
+      <c r="K18" s="6"/>
+      <c r="L18" s="6"/>
+    </row>
+    <row r="19" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A19" s="6"/>
+      <c r="B19" s="6"/>
+      <c r="C19" s="6"/>
+      <c r="D19" s="6"/>
+      <c r="E19" s="6"/>
+      <c r="F19" s="8"/>
+      <c r="G19" s="6"/>
+      <c r="H19" s="6"/>
+      <c r="I19" s="6" t="str">
         <f t="array" ref="I19">_xlfn.SWITCH(H19,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
-        <v>1</v>
-      </c>
-      <c r="J19" s="14" t="s">
-        <v>75</v>
-      </c>
-      <c r="K19" s="14"/>
-      <c r="L19" s="14"/>
-    </row>
-    <row r="20" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+        <v/>
+      </c>
+      <c r="J19" s="6"/>
+      <c r="K19" s="6"/>
+      <c r="L19" s="6"/>
+    </row>
+    <row r="20" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A20" s="6"/>
       <c r="B20" s="6"/>
       <c r="C20" s="6"/>
@@ -15641,12 +15583,15 @@
       <c r="F20" s="8"/>
       <c r="G20" s="6"/>
       <c r="H20" s="6"/>
-      <c r="I20" s="6"/>
+      <c r="I20" s="6" t="str">
+        <f t="array" ref="I20">_xlfn.SWITCH(H20,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
+        <v/>
+      </c>
       <c r="J20" s="6"/>
       <c r="K20" s="6"/>
       <c r="L20" s="6"/>
     </row>
-    <row r="21" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A21" s="6"/>
       <c r="B21" s="6"/>
       <c r="C21" s="6"/>
@@ -15663,7 +15608,7 @@
       <c r="K21" s="6"/>
       <c r="L21" s="6"/>
     </row>
-    <row r="22" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A22" s="6"/>
       <c r="B22" s="6"/>
       <c r="C22" s="6"/>
@@ -15680,7 +15625,7 @@
       <c r="K22" s="6"/>
       <c r="L22" s="6"/>
     </row>
-    <row r="23" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A23" s="6"/>
       <c r="B23" s="6"/>
       <c r="C23" s="6"/>
@@ -15697,13 +15642,13 @@
       <c r="K23" s="6"/>
       <c r="L23" s="6"/>
     </row>
-    <row r="24" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A24" s="6"/>
       <c r="B24" s="6"/>
       <c r="C24" s="6"/>
       <c r="D24" s="6"/>
       <c r="E24" s="6"/>
-      <c r="F24" s="8"/>
+      <c r="F24" s="5"/>
       <c r="G24" s="6"/>
       <c r="H24" s="6"/>
       <c r="I24" s="6" t="str">
@@ -15714,13 +15659,13 @@
       <c r="K24" s="6"/>
       <c r="L24" s="6"/>
     </row>
-    <row r="25" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A25" s="6"/>
       <c r="B25" s="6"/>
       <c r="C25" s="6"/>
       <c r="D25" s="6"/>
       <c r="E25" s="6"/>
-      <c r="F25" s="8"/>
+      <c r="F25" s="7"/>
       <c r="G25" s="6"/>
       <c r="H25" s="6"/>
       <c r="I25" s="6" t="str">
@@ -15731,13 +15676,13 @@
       <c r="K25" s="6"/>
       <c r="L25" s="6"/>
     </row>
-    <row r="26" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A26" s="6"/>
       <c r="B26" s="6"/>
       <c r="C26" s="6"/>
       <c r="D26" s="6"/>
       <c r="E26" s="6"/>
-      <c r="F26" s="8"/>
+      <c r="F26" s="7"/>
       <c r="G26" s="6"/>
       <c r="H26" s="6"/>
       <c r="I26" s="6" t="str">
@@ -15748,13 +15693,13 @@
       <c r="K26" s="6"/>
       <c r="L26" s="6"/>
     </row>
-    <row r="27" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A27" s="6"/>
       <c r="B27" s="6"/>
       <c r="C27" s="6"/>
       <c r="D27" s="6"/>
       <c r="E27" s="6"/>
-      <c r="F27" s="8"/>
+      <c r="F27" s="7"/>
       <c r="G27" s="6"/>
       <c r="H27" s="6"/>
       <c r="I27" s="6" t="str">
@@ -15765,13 +15710,13 @@
       <c r="K27" s="6"/>
       <c r="L27" s="6"/>
     </row>
-    <row r="28" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A28" s="6"/>
       <c r="B28" s="6"/>
       <c r="C28" s="6"/>
       <c r="D28" s="6"/>
       <c r="E28" s="6"/>
-      <c r="F28" s="5"/>
+      <c r="F28" s="7"/>
       <c r="G28" s="6"/>
       <c r="H28" s="6"/>
       <c r="I28" s="6" t="str">
@@ -15782,7 +15727,7 @@
       <c r="K28" s="6"/>
       <c r="L28" s="6"/>
     </row>
-    <row r="29" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A29" s="6"/>
       <c r="B29" s="6"/>
       <c r="C29" s="6"/>
@@ -15799,7 +15744,7 @@
       <c r="K29" s="6"/>
       <c r="L29" s="6"/>
     </row>
-    <row r="30" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A30" s="6"/>
       <c r="B30" s="6"/>
       <c r="C30" s="6"/>
@@ -15816,7 +15761,7 @@
       <c r="K30" s="6"/>
       <c r="L30" s="6"/>
     </row>
-    <row r="31" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A31" s="6"/>
       <c r="B31" s="6"/>
       <c r="C31" s="6"/>
@@ -15833,7 +15778,7 @@
       <c r="K31" s="6"/>
       <c r="L31" s="6"/>
     </row>
-    <row r="32" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A32" s="6"/>
       <c r="B32" s="6"/>
       <c r="C32" s="6"/>
@@ -15850,7 +15795,7 @@
       <c r="K32" s="6"/>
       <c r="L32" s="6"/>
     </row>
-    <row r="33" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A33" s="6"/>
       <c r="B33" s="6"/>
       <c r="C33" s="6"/>
@@ -15867,7 +15812,7 @@
       <c r="K33" s="6"/>
       <c r="L33" s="6"/>
     </row>
-    <row r="34" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A34" s="6"/>
       <c r="B34" s="6"/>
       <c r="C34" s="6"/>
@@ -15884,7 +15829,7 @@
       <c r="K34" s="6"/>
       <c r="L34" s="6"/>
     </row>
-    <row r="35" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A35" s="6"/>
       <c r="B35" s="6"/>
       <c r="C35" s="6"/>
@@ -15901,7 +15846,7 @@
       <c r="K35" s="6"/>
       <c r="L35" s="6"/>
     </row>
-    <row r="36" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A36" s="6"/>
       <c r="B36" s="6"/>
       <c r="C36" s="6"/>
@@ -15918,7 +15863,7 @@
       <c r="K36" s="6"/>
       <c r="L36" s="6"/>
     </row>
-    <row r="37" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A37" s="6"/>
       <c r="B37" s="6"/>
       <c r="C37" s="6"/>
@@ -15935,7 +15880,7 @@
       <c r="K37" s="6"/>
       <c r="L37" s="6"/>
     </row>
-    <row r="38" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A38" s="6"/>
       <c r="B38" s="6"/>
       <c r="C38" s="6"/>
@@ -15952,7 +15897,7 @@
       <c r="K38" s="6"/>
       <c r="L38" s="6"/>
     </row>
-    <row r="39" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A39" s="6"/>
       <c r="B39" s="6"/>
       <c r="C39" s="6"/>
@@ -15969,7 +15914,7 @@
       <c r="K39" s="6"/>
       <c r="L39" s="6"/>
     </row>
-    <row r="40" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A40" s="6"/>
       <c r="B40" s="6"/>
       <c r="C40" s="6"/>
@@ -15986,7 +15931,7 @@
       <c r="K40" s="6"/>
       <c r="L40" s="6"/>
     </row>
-    <row r="41" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A41" s="6"/>
       <c r="B41" s="6"/>
       <c r="C41" s="6"/>
@@ -16003,13 +15948,13 @@
       <c r="K41" s="6"/>
       <c r="L41" s="6"/>
     </row>
-    <row r="42" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A42" s="6"/>
       <c r="B42" s="6"/>
       <c r="C42" s="6"/>
       <c r="D42" s="6"/>
       <c r="E42" s="6"/>
-      <c r="F42" s="7"/>
+      <c r="F42" s="8"/>
       <c r="G42" s="6"/>
       <c r="H42" s="6"/>
       <c r="I42" s="6" t="str">
@@ -16020,13 +15965,13 @@
       <c r="K42" s="6"/>
       <c r="L42" s="6"/>
     </row>
-    <row r="43" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A43" s="6"/>
       <c r="B43" s="6"/>
       <c r="C43" s="6"/>
       <c r="D43" s="6"/>
       <c r="E43" s="6"/>
-      <c r="F43" s="7"/>
+      <c r="F43" s="8"/>
       <c r="G43" s="6"/>
       <c r="H43" s="6"/>
       <c r="I43" s="6" t="str">
@@ -16037,13 +15982,13 @@
       <c r="K43" s="6"/>
       <c r="L43" s="6"/>
     </row>
-    <row r="44" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A44" s="6"/>
       <c r="B44" s="6"/>
       <c r="C44" s="6"/>
       <c r="D44" s="6"/>
       <c r="E44" s="6"/>
-      <c r="F44" s="7"/>
+      <c r="F44" s="8"/>
       <c r="G44" s="6"/>
       <c r="H44" s="6"/>
       <c r="I44" s="6" t="str">
@@ -16054,13 +15999,13 @@
       <c r="K44" s="6"/>
       <c r="L44" s="6"/>
     </row>
-    <row r="45" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A45" s="6"/>
       <c r="B45" s="6"/>
       <c r="C45" s="6"/>
       <c r="D45" s="6"/>
       <c r="E45" s="6"/>
-      <c r="F45" s="7"/>
+      <c r="F45" s="8"/>
       <c r="G45" s="6"/>
       <c r="H45" s="6"/>
       <c r="I45" s="6" t="str">
@@ -16071,7 +16016,7 @@
       <c r="K45" s="6"/>
       <c r="L45" s="6"/>
     </row>
-    <row r="46" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A46" s="6"/>
       <c r="B46" s="6"/>
       <c r="C46" s="6"/>
@@ -16088,7 +16033,7 @@
       <c r="K46" s="6"/>
       <c r="L46" s="6"/>
     </row>
-    <row r="47" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A47" s="6"/>
       <c r="B47" s="6"/>
       <c r="C47" s="6"/>
@@ -16105,13 +16050,13 @@
       <c r="K47" s="6"/>
       <c r="L47" s="6"/>
     </row>
-    <row r="48" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A48" s="6"/>
       <c r="B48" s="6"/>
       <c r="C48" s="6"/>
       <c r="D48" s="6"/>
       <c r="E48" s="6"/>
-      <c r="F48" s="8"/>
+      <c r="F48" s="7"/>
       <c r="G48" s="6"/>
       <c r="H48" s="6"/>
       <c r="I48" s="6" t="str">
@@ -16122,13 +16067,13 @@
       <c r="K48" s="6"/>
       <c r="L48" s="6"/>
     </row>
-    <row r="49" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A49" s="6"/>
       <c r="B49" s="6"/>
       <c r="C49" s="6"/>
       <c r="D49" s="6"/>
       <c r="E49" s="6"/>
-      <c r="F49" s="8"/>
+      <c r="F49" s="7"/>
       <c r="G49" s="6"/>
       <c r="H49" s="6"/>
       <c r="I49" s="6" t="str">
@@ -16139,13 +16084,13 @@
       <c r="K49" s="6"/>
       <c r="L49" s="6"/>
     </row>
-    <row r="50" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A50" s="6"/>
       <c r="B50" s="6"/>
       <c r="C50" s="6"/>
       <c r="D50" s="6"/>
       <c r="E50" s="6"/>
-      <c r="F50" s="8"/>
+      <c r="F50" s="7"/>
       <c r="G50" s="6"/>
       <c r="H50" s="6"/>
       <c r="I50" s="6" t="str">
@@ -16156,13 +16101,13 @@
       <c r="K50" s="6"/>
       <c r="L50" s="6"/>
     </row>
-    <row r="51" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A51" s="6"/>
       <c r="B51" s="6"/>
       <c r="C51" s="6"/>
       <c r="D51" s="6"/>
       <c r="E51" s="6"/>
-      <c r="F51" s="8"/>
+      <c r="F51" s="7"/>
       <c r="G51" s="6"/>
       <c r="H51" s="6"/>
       <c r="I51" s="6" t="str">
@@ -16173,7 +16118,7 @@
       <c r="K51" s="6"/>
       <c r="L51" s="6"/>
     </row>
-    <row r="52" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A52" s="6"/>
       <c r="B52" s="6"/>
       <c r="C52" s="6"/>
@@ -16190,7 +16135,7 @@
       <c r="K52" s="6"/>
       <c r="L52" s="6"/>
     </row>
-    <row r="53" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A53" s="6"/>
       <c r="B53" s="6"/>
       <c r="C53" s="6"/>
@@ -16207,7 +16152,7 @@
       <c r="K53" s="6"/>
       <c r="L53" s="6"/>
     </row>
-    <row r="54" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A54" s="6"/>
       <c r="B54" s="6"/>
       <c r="C54" s="6"/>
@@ -16224,7 +16169,7 @@
       <c r="K54" s="6"/>
       <c r="L54" s="6"/>
     </row>
-    <row r="55" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A55" s="6"/>
       <c r="B55" s="6"/>
       <c r="C55" s="6"/>
@@ -16241,7 +16186,7 @@
       <c r="K55" s="6"/>
       <c r="L55" s="6"/>
     </row>
-    <row r="56" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A56" s="6"/>
       <c r="B56" s="6"/>
       <c r="C56" s="6"/>
@@ -16258,7 +16203,7 @@
       <c r="K56" s="6"/>
       <c r="L56" s="6"/>
     </row>
-    <row r="57" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A57" s="6"/>
       <c r="B57" s="6"/>
       <c r="C57" s="6"/>
@@ -16275,7 +16220,7 @@
       <c r="K57" s="6"/>
       <c r="L57" s="6"/>
     </row>
-    <row r="58" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A58" s="6"/>
       <c r="B58" s="6"/>
       <c r="C58" s="6"/>
@@ -16292,13 +16237,13 @@
       <c r="K58" s="6"/>
       <c r="L58" s="6"/>
     </row>
-    <row r="59" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A59" s="6"/>
       <c r="B59" s="6"/>
       <c r="C59" s="6"/>
       <c r="D59" s="6"/>
       <c r="E59" s="6"/>
-      <c r="F59" s="7"/>
+      <c r="F59" s="5"/>
       <c r="G59" s="6"/>
       <c r="H59" s="6"/>
       <c r="I59" s="6" t="str">
@@ -16309,7 +16254,7 @@
       <c r="K59" s="6"/>
       <c r="L59" s="6"/>
     </row>
-    <row r="60" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A60" s="6"/>
       <c r="B60" s="6"/>
       <c r="C60" s="6"/>
@@ -16326,13 +16271,13 @@
       <c r="K60" s="6"/>
       <c r="L60" s="6"/>
     </row>
-    <row r="61" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A61" s="6"/>
       <c r="B61" s="6"/>
       <c r="C61" s="6"/>
       <c r="D61" s="6"/>
       <c r="E61" s="6"/>
-      <c r="F61" s="7"/>
+      <c r="F61" s="5"/>
       <c r="G61" s="6"/>
       <c r="H61" s="6"/>
       <c r="I61" s="6" t="str">
@@ -16343,13 +16288,13 @@
       <c r="K61" s="6"/>
       <c r="L61" s="6"/>
     </row>
-    <row r="62" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A62" s="6"/>
       <c r="B62" s="6"/>
       <c r="C62" s="6"/>
       <c r="D62" s="6"/>
       <c r="E62" s="6"/>
-      <c r="F62" s="7"/>
+      <c r="F62" s="5"/>
       <c r="G62" s="6"/>
       <c r="H62" s="6"/>
       <c r="I62" s="6" t="str">
@@ -16360,13 +16305,13 @@
       <c r="K62" s="6"/>
       <c r="L62" s="6"/>
     </row>
-    <row r="63" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A63" s="6"/>
       <c r="B63" s="6"/>
       <c r="C63" s="6"/>
       <c r="D63" s="6"/>
       <c r="E63" s="6"/>
-      <c r="F63" s="5"/>
+      <c r="F63" s="7"/>
       <c r="G63" s="6"/>
       <c r="H63" s="6"/>
       <c r="I63" s="6" t="str">
@@ -16377,7 +16322,7 @@
       <c r="K63" s="6"/>
       <c r="L63" s="6"/>
     </row>
-    <row r="64" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A64" s="6"/>
       <c r="B64" s="6"/>
       <c r="C64" s="6"/>
@@ -16394,13 +16339,13 @@
       <c r="K64" s="6"/>
       <c r="L64" s="6"/>
     </row>
-    <row r="65" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A65" s="6"/>
       <c r="B65" s="6"/>
       <c r="C65" s="6"/>
       <c r="D65" s="6"/>
       <c r="E65" s="6"/>
-      <c r="F65" s="5"/>
+      <c r="F65" s="7"/>
       <c r="G65" s="6"/>
       <c r="H65" s="6"/>
       <c r="I65" s="6" t="str">
@@ -16411,13 +16356,13 @@
       <c r="K65" s="6"/>
       <c r="L65" s="6"/>
     </row>
-    <row r="66" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A66" s="6"/>
       <c r="B66" s="6"/>
       <c r="C66" s="6"/>
       <c r="D66" s="6"/>
       <c r="E66" s="6"/>
-      <c r="F66" s="5"/>
+      <c r="F66" s="7"/>
       <c r="G66" s="6"/>
       <c r="H66" s="6"/>
       <c r="I66" s="6" t="str">
@@ -16428,7 +16373,7 @@
       <c r="K66" s="6"/>
       <c r="L66" s="6"/>
     </row>
-    <row r="67" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A67" s="6"/>
       <c r="B67" s="6"/>
       <c r="C67" s="6"/>
@@ -16445,13 +16390,13 @@
       <c r="K67" s="6"/>
       <c r="L67" s="6"/>
     </row>
-    <row r="68" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A68" s="6"/>
       <c r="B68" s="6"/>
       <c r="C68" s="6"/>
       <c r="D68" s="6"/>
       <c r="E68" s="6"/>
-      <c r="F68" s="7"/>
+      <c r="F68" s="8"/>
       <c r="G68" s="6"/>
       <c r="H68" s="6"/>
       <c r="I68" s="6" t="str">
@@ -16462,13 +16407,13 @@
       <c r="K68" s="6"/>
       <c r="L68" s="6"/>
     </row>
-    <row r="69" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A69" s="6"/>
       <c r="B69" s="6"/>
       <c r="C69" s="6"/>
       <c r="D69" s="6"/>
       <c r="E69" s="6"/>
-      <c r="F69" s="7"/>
+      <c r="F69" s="8"/>
       <c r="G69" s="6"/>
       <c r="H69" s="6"/>
       <c r="I69" s="6" t="str">
@@ -16479,13 +16424,13 @@
       <c r="K69" s="6"/>
       <c r="L69" s="6"/>
     </row>
-    <row r="70" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A70" s="6"/>
       <c r="B70" s="6"/>
       <c r="C70" s="6"/>
       <c r="D70" s="6"/>
       <c r="E70" s="6"/>
-      <c r="F70" s="7"/>
+      <c r="F70" s="8"/>
       <c r="G70" s="6"/>
       <c r="H70" s="6"/>
       <c r="I70" s="6" t="str">
@@ -16496,13 +16441,13 @@
       <c r="K70" s="6"/>
       <c r="L70" s="6"/>
     </row>
-    <row r="71" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A71" s="6"/>
       <c r="B71" s="6"/>
       <c r="C71" s="6"/>
       <c r="D71" s="6"/>
       <c r="E71" s="6"/>
-      <c r="F71" s="7"/>
+      <c r="F71" s="8"/>
       <c r="G71" s="6"/>
       <c r="H71" s="6"/>
       <c r="I71" s="6" t="str">
@@ -16513,7 +16458,7 @@
       <c r="K71" s="6"/>
       <c r="L71" s="6"/>
     </row>
-    <row r="72" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A72" s="6"/>
       <c r="B72" s="6"/>
       <c r="C72" s="6"/>
@@ -16530,7 +16475,7 @@
       <c r="K72" s="6"/>
       <c r="L72" s="6"/>
     </row>
-    <row r="73" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A73" s="6"/>
       <c r="B73" s="6"/>
       <c r="C73" s="6"/>
@@ -16547,7 +16492,7 @@
       <c r="K73" s="6"/>
       <c r="L73" s="6"/>
     </row>
-    <row r="74" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A74" s="6"/>
       <c r="B74" s="6"/>
       <c r="C74" s="6"/>
@@ -16564,7 +16509,7 @@
       <c r="K74" s="6"/>
       <c r="L74" s="6"/>
     </row>
-    <row r="75" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A75" s="6"/>
       <c r="B75" s="6"/>
       <c r="C75" s="6"/>
@@ -16581,7 +16526,7 @@
       <c r="K75" s="6"/>
       <c r="L75" s="6"/>
     </row>
-    <row r="76" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A76" s="6"/>
       <c r="B76" s="6"/>
       <c r="C76" s="6"/>
@@ -16598,7 +16543,7 @@
       <c r="K76" s="6"/>
       <c r="L76" s="6"/>
     </row>
-    <row r="77" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A77" s="6"/>
       <c r="B77" s="6"/>
       <c r="C77" s="6"/>
@@ -16615,7 +16560,7 @@
       <c r="K77" s="6"/>
       <c r="L77" s="6"/>
     </row>
-    <row r="78" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A78" s="6"/>
       <c r="B78" s="6"/>
       <c r="C78" s="6"/>
@@ -16632,7 +16577,7 @@
       <c r="K78" s="6"/>
       <c r="L78" s="6"/>
     </row>
-    <row r="79" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A79" s="6"/>
       <c r="B79" s="6"/>
       <c r="C79" s="6"/>
@@ -16649,7 +16594,7 @@
       <c r="K79" s="6"/>
       <c r="L79" s="6"/>
     </row>
-    <row r="80" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="80" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A80" s="6"/>
       <c r="B80" s="6"/>
       <c r="C80" s="6"/>
@@ -16666,7 +16611,7 @@
       <c r="K80" s="6"/>
       <c r="L80" s="6"/>
     </row>
-    <row r="81" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="81" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A81" s="6"/>
       <c r="B81" s="6"/>
       <c r="C81" s="6"/>
@@ -16683,7 +16628,7 @@
       <c r="K81" s="6"/>
       <c r="L81" s="6"/>
     </row>
-    <row r="82" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="82" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A82" s="6"/>
       <c r="B82" s="6"/>
       <c r="C82" s="6"/>
@@ -16700,7 +16645,7 @@
       <c r="K82" s="6"/>
       <c r="L82" s="6"/>
     </row>
-    <row r="83" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="83" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A83" s="6"/>
       <c r="B83" s="6"/>
       <c r="C83" s="6"/>
@@ -16717,7 +16662,7 @@
       <c r="K83" s="6"/>
       <c r="L83" s="6"/>
     </row>
-    <row r="84" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="84" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A84" s="6"/>
       <c r="B84" s="6"/>
       <c r="C84" s="6"/>
@@ -16734,7 +16679,7 @@
       <c r="K84" s="6"/>
       <c r="L84" s="6"/>
     </row>
-    <row r="85" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="85" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A85" s="6"/>
       <c r="B85" s="6"/>
       <c r="C85" s="6"/>
@@ -16751,7 +16696,7 @@
       <c r="K85" s="6"/>
       <c r="L85" s="6"/>
     </row>
-    <row r="86" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="86" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A86" s="6"/>
       <c r="B86" s="6"/>
       <c r="C86" s="6"/>
@@ -16768,7 +16713,7 @@
       <c r="K86" s="6"/>
       <c r="L86" s="6"/>
     </row>
-    <row r="87" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="87" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A87" s="6"/>
       <c r="B87" s="6"/>
       <c r="C87" s="6"/>
@@ -16785,7 +16730,7 @@
       <c r="K87" s="6"/>
       <c r="L87" s="6"/>
     </row>
-    <row r="88" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="88" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A88" s="6"/>
       <c r="B88" s="6"/>
       <c r="C88" s="6"/>
@@ -16802,7 +16747,7 @@
       <c r="K88" s="6"/>
       <c r="L88" s="6"/>
     </row>
-    <row r="89" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="89" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A89" s="6"/>
       <c r="B89" s="6"/>
       <c r="C89" s="6"/>
@@ -16819,7 +16764,7 @@
       <c r="K89" s="6"/>
       <c r="L89" s="6"/>
     </row>
-    <row r="90" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="90" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A90" s="6"/>
       <c r="B90" s="6"/>
       <c r="C90" s="6"/>
@@ -16836,7 +16781,7 @@
       <c r="K90" s="6"/>
       <c r="L90" s="6"/>
     </row>
-    <row r="91" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="91" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A91" s="6"/>
       <c r="B91" s="6"/>
       <c r="C91" s="6"/>
@@ -16853,7 +16798,7 @@
       <c r="K91" s="6"/>
       <c r="L91" s="6"/>
     </row>
-    <row r="92" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="92" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A92" s="6"/>
       <c r="B92" s="6"/>
       <c r="C92" s="6"/>
@@ -16870,7 +16815,7 @@
       <c r="K92" s="6"/>
       <c r="L92" s="6"/>
     </row>
-    <row r="93" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="93" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A93" s="6"/>
       <c r="B93" s="6"/>
       <c r="C93" s="6"/>
@@ -16887,7 +16832,7 @@
       <c r="K93" s="6"/>
       <c r="L93" s="6"/>
     </row>
-    <row r="94" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="94" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A94" s="6"/>
       <c r="B94" s="6"/>
       <c r="C94" s="6"/>
@@ -16904,7 +16849,7 @@
       <c r="K94" s="6"/>
       <c r="L94" s="6"/>
     </row>
-    <row r="95" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="95" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A95" s="6"/>
       <c r="B95" s="6"/>
       <c r="C95" s="6"/>
@@ -16921,7 +16866,7 @@
       <c r="K95" s="6"/>
       <c r="L95" s="6"/>
     </row>
-    <row r="96" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="96" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A96" s="6"/>
       <c r="B96" s="6"/>
       <c r="C96" s="6"/>
@@ -16938,7 +16883,7 @@
       <c r="K96" s="6"/>
       <c r="L96" s="6"/>
     </row>
-    <row r="97" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="97" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A97" s="6"/>
       <c r="B97" s="6"/>
       <c r="C97" s="6"/>
@@ -16955,7 +16900,7 @@
       <c r="K97" s="6"/>
       <c r="L97" s="6"/>
     </row>
-    <row r="98" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="98" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A98" s="6"/>
       <c r="B98" s="6"/>
       <c r="C98" s="6"/>
@@ -16972,7 +16917,7 @@
       <c r="K98" s="6"/>
       <c r="L98" s="6"/>
     </row>
-    <row r="99" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="99" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A99" s="6"/>
       <c r="B99" s="6"/>
       <c r="C99" s="6"/>
@@ -16989,7 +16934,7 @@
       <c r="K99" s="6"/>
       <c r="L99" s="6"/>
     </row>
-    <row r="100" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="100" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A100" s="6"/>
       <c r="B100" s="6"/>
       <c r="C100" s="6"/>
@@ -17006,7 +16951,7 @@
       <c r="K100" s="6"/>
       <c r="L100" s="6"/>
     </row>
-    <row r="101" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="101" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A101" s="6"/>
       <c r="B101" s="6"/>
       <c r="C101" s="6"/>
@@ -17023,7 +16968,7 @@
       <c r="K101" s="6"/>
       <c r="L101" s="6"/>
     </row>
-    <row r="102" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="102" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A102" s="6"/>
       <c r="B102" s="6"/>
       <c r="C102" s="6"/>
@@ -17040,7 +16985,7 @@
       <c r="K102" s="6"/>
       <c r="L102" s="6"/>
     </row>
-    <row r="103" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="103" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A103" s="6"/>
       <c r="B103" s="6"/>
       <c r="C103" s="6"/>
@@ -17057,82 +17002,8 @@
       <c r="K103" s="6"/>
       <c r="L103" s="6"/>
     </row>
-    <row r="104" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A104" s="6"/>
-      <c r="B104" s="6"/>
-      <c r="C104" s="6"/>
-      <c r="D104" s="6"/>
-      <c r="E104" s="6"/>
-      <c r="F104" s="8"/>
-      <c r="G104" s="6"/>
-      <c r="H104" s="6"/>
-      <c r="I104" s="6" t="str">
-        <f t="array" ref="I104">_xlfn.SWITCH(H104,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
-        <v/>
-      </c>
-      <c r="J104" s="6"/>
-      <c r="K104" s="6"/>
-      <c r="L104" s="6"/>
-    </row>
-    <row r="105" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A105" s="6"/>
-      <c r="B105" s="6"/>
-      <c r="C105" s="6"/>
-      <c r="D105" s="6"/>
-      <c r="E105" s="6"/>
-      <c r="F105" s="8"/>
-      <c r="G105" s="6"/>
-      <c r="H105" s="6"/>
-      <c r="I105" s="6" t="str">
-        <f t="array" ref="I105">_xlfn.SWITCH(H105,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
-        <v/>
-      </c>
-      <c r="J105" s="6"/>
-      <c r="K105" s="6"/>
-      <c r="L105" s="6"/>
-    </row>
-    <row r="106" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A106" s="6"/>
-      <c r="B106" s="6"/>
-      <c r="C106" s="6"/>
-      <c r="D106" s="6"/>
-      <c r="E106" s="6"/>
-      <c r="F106" s="8"/>
-      <c r="G106" s="6"/>
-      <c r="H106" s="6"/>
-      <c r="I106" s="6" t="str">
-        <f t="array" ref="I106">_xlfn.SWITCH(H106,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
-        <v/>
-      </c>
-      <c r="J106" s="6"/>
-      <c r="K106" s="6"/>
-      <c r="L106" s="6"/>
-    </row>
-    <row r="107" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A107" s="6"/>
-      <c r="B107" s="6"/>
-      <c r="C107" s="6"/>
-      <c r="D107" s="6"/>
-      <c r="E107" s="6"/>
-      <c r="F107" s="8"/>
-      <c r="G107" s="6"/>
-      <c r="H107" s="6"/>
-      <c r="I107" s="6" t="str">
-        <f t="array" ref="I107">_xlfn.SWITCH(H107,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
-        <v/>
-      </c>
-      <c r="J107" s="6"/>
-      <c r="K107" s="6"/>
-      <c r="L107" s="6"/>
-    </row>
   </sheetData>
-  <autoFilter ref="J1:J107" xr:uid="{AA30D3B6-4BBC-427B-918A-C301767B692F}">
-    <filterColumn colId="0">
-      <filters>
-        <filter val="ToDo"/>
-      </filters>
-    </filterColumn>
-  </autoFilter>
+  <autoFilter ref="J1:J103" xr:uid="{AA30D3B6-4BBC-427B-918A-C301767B692F}"/>
   <phoneticPr fontId="4" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -17175,12 +17046,12 @@
         <v>46272</v>
       </c>
       <c r="C2" s="19">
-        <f>61-SUM(E$2:E2)</f>
-        <v>61</v>
+        <f>52-SUM(E$2:E2)</f>
+        <v>52</v>
       </c>
       <c r="D2" s="20">
-        <f>61*(1-(A2/12))</f>
-        <v>61</v>
+        <f>52*(1-(A2/12))</f>
+        <v>52</v>
       </c>
       <c r="E2" s="20">
         <v>0</v>
@@ -17194,12 +17065,12 @@
         <v>46273</v>
       </c>
       <c r="C3" s="19">
-        <f>61-SUM(E$2:E3)</f>
-        <v>61</v>
+        <f>52-SUM(E$2:E3)</f>
+        <v>52</v>
       </c>
       <c r="D3" s="20">
-        <f t="shared" ref="D3:D14" si="0">61*(1-(A3/12))</f>
-        <v>55.916666666666664</v>
+        <f t="shared" ref="D3:D14" si="0">52*(1-(A3/12))</f>
+        <v>47.666666666666664</v>
       </c>
       <c r="E3" s="20">
         <v>0</v>
@@ -17213,12 +17084,12 @@
         <v>46274</v>
       </c>
       <c r="C4" s="19">
-        <f>61-SUM(E$2:E4)</f>
-        <v>61</v>
+        <f>52-SUM(E$2:E4)</f>
+        <v>52</v>
       </c>
       <c r="D4" s="20">
         <f t="shared" si="0"/>
-        <v>50.833333333333336</v>
+        <v>43.333333333333336</v>
       </c>
       <c r="E4" s="20">
         <v>0</v>
@@ -17233,12 +17104,12 @@
         <v>46275</v>
       </c>
       <c r="C5" s="19">
-        <f>61-SUM(E$2:E5)</f>
-        <v>48</v>
+        <f>52-SUM(E$2:E5)</f>
+        <v>39</v>
       </c>
       <c r="D5" s="20">
         <f t="shared" si="0"/>
-        <v>45.75</v>
+        <v>39</v>
       </c>
       <c r="E5" s="20">
         <v>13</v>
@@ -17252,12 +17123,12 @@
         <v>46276</v>
       </c>
       <c r="C6" s="19">
-        <f>61-SUM(E$2:E6)</f>
-        <v>35</v>
+        <f>52-SUM(E$2:E6)</f>
+        <v>26</v>
       </c>
       <c r="D6" s="20">
         <f t="shared" si="0"/>
-        <v>40.666666666666671</v>
+        <v>34.666666666666671</v>
       </c>
       <c r="E6" s="20">
         <v>13</v>
@@ -17271,12 +17142,12 @@
         <v>46279</v>
       </c>
       <c r="C7" s="19">
-        <f>61-SUM(E$2:E7)</f>
-        <v>35</v>
+        <f>52-SUM(E$2:E7)</f>
+        <v>26</v>
       </c>
       <c r="D7" s="20">
         <f t="shared" si="0"/>
-        <v>35.583333333333329</v>
+        <v>30.333333333333329</v>
       </c>
       <c r="E7" s="20">
         <v>0</v>
@@ -17290,12 +17161,12 @@
         <v>46280</v>
       </c>
       <c r="C8" s="19">
-        <f>61-SUM(E$2:E8)</f>
-        <v>35</v>
+        <f>52-SUM(E$2:E8)</f>
+        <v>26</v>
       </c>
       <c r="D8" s="20">
         <f t="shared" si="0"/>
-        <v>30.5</v>
+        <v>26</v>
       </c>
       <c r="E8" s="20">
         <v>0</v>
@@ -17309,12 +17180,12 @@
         <v>46281</v>
       </c>
       <c r="C9" s="19">
-        <f>61-SUM(E$2:E9)</f>
-        <v>35</v>
+        <f>52-SUM(E$2:E9)</f>
+        <v>26</v>
       </c>
       <c r="D9" s="20">
         <f t="shared" si="0"/>
-        <v>25.416666666666664</v>
+        <v>21.666666666666664</v>
       </c>
       <c r="E9" s="20">
         <v>0</v>
@@ -17328,12 +17199,12 @@
         <v>46282</v>
       </c>
       <c r="C10" s="19">
-        <f>61-SUM(E$2:E10)</f>
-        <v>30</v>
+        <f>52-SUM(E$2:E10)</f>
+        <v>21</v>
       </c>
       <c r="D10" s="20">
         <f t="shared" si="0"/>
-        <v>20.333333333333336</v>
+        <v>17.333333333333336</v>
       </c>
       <c r="E10" s="20">
         <v>5</v>
@@ -17347,12 +17218,12 @@
         <v>46283</v>
       </c>
       <c r="C11" s="19">
-        <f>61-SUM(E$2:E11)</f>
-        <v>25</v>
+        <f>52-SUM(E$2:E11)</f>
+        <v>16</v>
       </c>
       <c r="D11" s="20">
         <f t="shared" si="0"/>
-        <v>15.25</v>
+        <v>13</v>
       </c>
       <c r="E11" s="20">
         <v>5</v>
@@ -17366,12 +17237,12 @@
         <v>46286</v>
       </c>
       <c r="C12" s="19">
-        <f>61-SUM(E$2:E12)</f>
-        <v>17</v>
+        <f>52-SUM(E$2:E12)</f>
+        <v>8</v>
       </c>
       <c r="D12" s="20">
         <f t="shared" si="0"/>
-        <v>10.166666666666664</v>
+        <v>8.6666666666666643</v>
       </c>
       <c r="E12" s="20">
         <v>8</v>
@@ -17385,12 +17256,12 @@
         <v>46287</v>
       </c>
       <c r="C13" s="19">
-        <f>61-SUM(E$2:E13)</f>
-        <v>17</v>
+        <f>52-SUM(E$2:E13)</f>
+        <v>8</v>
       </c>
       <c r="D13" s="20">
         <f t="shared" si="0"/>
-        <v>5.0833333333333357</v>
+        <v>4.3333333333333357</v>
       </c>
       <c r="E13" s="20">
         <v>0</v>
@@ -17404,19 +17275,210 @@
         <v>46288</v>
       </c>
       <c r="C14" s="19">
-        <f>61-SUM(E$2:E14)</f>
-        <v>17</v>
+        <f>52-SUM(E$2:E14)</f>
+        <v>0</v>
       </c>
       <c r="D14" s="20">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="E14" s="20">
-        <v>0</v>
+        <v>8</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5C8CD023-91C8-44AF-AB04-2727DDB868DE}">
+  <dimension ref="A1:L5"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="6.88671875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="11" customWidth="1"/>
+    <col min="3" max="3" width="8.33203125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="7.33203125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="7.88671875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="82.88671875" customWidth="1"/>
+    <col min="7" max="7" width="8" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="7.109375" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="6" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="6.77734375" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="8" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="5.77734375" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:12" ht="46.8" x14ac:dyDescent="0.3">
+      <c r="A1" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="B1" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" s="4" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1" s="4" t="s">
+        <v>2</v>
+      </c>
+      <c r="E1" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="F1" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="G1" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="H1" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="I1" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="K1" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="L1" s="4" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2" spans="1:12" ht="244.8" x14ac:dyDescent="0.3">
+      <c r="A2" s="12">
+        <v>5</v>
+      </c>
+      <c r="B2" s="12" t="s">
+        <v>94</v>
+      </c>
+      <c r="C2" s="12"/>
+      <c r="D2" s="12"/>
+      <c r="E2" s="12" t="s">
+        <v>31</v>
+      </c>
+      <c r="F2" s="13" t="s">
+        <v>132</v>
+      </c>
+      <c r="G2" s="12" t="s">
+        <v>24</v>
+      </c>
+      <c r="H2" s="12" t="s">
+        <v>23</v>
+      </c>
+      <c r="I2" s="12">
+        <v>2</v>
+      </c>
+      <c r="J2" s="12" t="s">
+        <v>76</v>
+      </c>
+      <c r="K2" s="12"/>
+      <c r="L2" s="12"/>
+    </row>
+    <row r="3" spans="1:12" ht="316.8" x14ac:dyDescent="0.3">
+      <c r="A3" s="12">
+        <v>6</v>
+      </c>
+      <c r="B3" s="12" t="s">
+        <v>94</v>
+      </c>
+      <c r="C3" s="12"/>
+      <c r="D3" s="12"/>
+      <c r="E3" s="12" t="s">
+        <v>22</v>
+      </c>
+      <c r="F3" s="13" t="s">
+        <v>133</v>
+      </c>
+      <c r="G3" s="12" t="s">
+        <v>24</v>
+      </c>
+      <c r="H3" s="12" t="s">
+        <v>23</v>
+      </c>
+      <c r="I3" s="12">
+        <v>2</v>
+      </c>
+      <c r="J3" s="12" t="s">
+        <v>76</v>
+      </c>
+      <c r="K3" s="12"/>
+      <c r="L3" s="12"/>
+    </row>
+    <row r="4" spans="1:12" ht="244.8" x14ac:dyDescent="0.3">
+      <c r="A4" s="12">
+        <v>7</v>
+      </c>
+      <c r="B4" s="12" t="s">
+        <v>94</v>
+      </c>
+      <c r="C4" s="12"/>
+      <c r="D4" s="12"/>
+      <c r="E4" s="12" t="s">
+        <v>31</v>
+      </c>
+      <c r="F4" s="13" t="s">
+        <v>134</v>
+      </c>
+      <c r="G4" s="12" t="s">
+        <v>24</v>
+      </c>
+      <c r="H4" s="12" t="s">
+        <v>23</v>
+      </c>
+      <c r="I4" s="12">
+        <v>2</v>
+      </c>
+      <c r="J4" s="12" t="s">
+        <v>76</v>
+      </c>
+      <c r="K4" s="12"/>
+      <c r="L4" s="12"/>
+    </row>
+    <row r="5" spans="1:12" ht="216" x14ac:dyDescent="0.3">
+      <c r="A5" s="12">
+        <v>8</v>
+      </c>
+      <c r="B5" s="12" t="s">
+        <v>94</v>
+      </c>
+      <c r="C5" s="12"/>
+      <c r="D5" s="12"/>
+      <c r="E5" s="12" t="s">
+        <v>22</v>
+      </c>
+      <c r="F5" s="13" t="s">
+        <v>135</v>
+      </c>
+      <c r="G5" s="12" t="s">
+        <v>24</v>
+      </c>
+      <c r="H5" s="12" t="s">
+        <v>27</v>
+      </c>
+      <c r="I5" s="12">
+        <v>3</v>
+      </c>
+      <c r="J5" s="12" t="s">
+        <v>76</v>
+      </c>
+      <c r="K5" s="12"/>
+      <c r="L5" s="12"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4BED4A53-58DB-40BB-A13E-FB881A9A3A62}">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetData/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/Business Analysis/checkupp_sprint_plan_2026.xlsx
+++ b/Business Analysis/checkupp_sprint_plan_2026.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitHub\CheckUpp\Business Analysis\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{50133B31-C3F8-4D0A-8A06-5E3644B59B08}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{997BC128-41AB-4154-BDE0-0262C6EF3F4D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="2" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="2" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sprint 01" sheetId="1" r:id="rId1"/>

--- a/Business Analysis/checkupp_sprint_plan_2026.xlsx
+++ b/Business Analysis/checkupp_sprint_plan_2026.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitHub\CheckUpp\Business Analysis\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\CheckUpp\Business Analysis\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{997BC128-41AB-4154-BDE0-0262C6EF3F4D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E152211D-3EEE-40DC-8115-60626A46579A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="2" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" firstSheet="3" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sprint 01" sheetId="1" r:id="rId1"/>
@@ -21,6 +21,7 @@
     <sheet name="Sprint 03 Burndown" sheetId="8" r:id="rId6"/>
     <sheet name="Sprint 04" sheetId="9" r:id="rId7"/>
     <sheet name="Sprint 04 Burndown" sheetId="10" r:id="rId8"/>
+    <sheet name="sprint 05" sheetId="14" r:id="rId9"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Sprint 01'!$E$1:$E$112</definedName>
@@ -64,7 +65,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="459" uniqueCount="140">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="528" uniqueCount="173">
   <si>
     <t>Epic</t>
   </si>
@@ -6181,6 +6182,284 @@
 [ ] All tests defined in Ticket 7 pass successfully.
 [ ] API requests attempting to generate a Signed URL for unsupported files fail securely at the controller level.</t>
   </si>
+  <si>
+    <t>Mapped User Stories</t>
+  </si>
+  <si>
+    <t>Target File</t>
+  </si>
+  <si>
+    <t>Task#</t>
+  </si>
+  <si>
+    <t>US 5.2, 5.3, 5.4, 5.5, 5.6, 5.9</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Create test/Immunisation/use-immunisation-categories.test.ts</t>
+  </si>
+  <si>
+    <t>*Ambiguity-Free Technical Specification:*
+1. *Test Setup:* Initialize a pure Jest test suite using @testing-library/react-hooks (or React test renderer) to validate the pure logic of the useImmunisationCategories hook.
+2. *Age Mapping (US 5.2):*
+* Mock global profile age: 18. Assert recommended array strictly contains { id: 'adult', title: 'Adults' }.
+* Test boundary conditions: age: 49 (Adult), age: 50 (50+ Years), age: 15 (Adolescent), age: 75 (75+ Years). Assert only one age category is ever returned in recommended.
+3. *Pregnancy Mapping (US 5.3):*
+* Mock profile gender: 'female', lmpDate: '2026-08-01', age: 25. Assert recommended array has length 2 and contains both "Adults" and "Pregnancy".
+* Mock gender: 'male' with an lmpDate. Assert "Pregnancy" is strictly excluded from recommended and otherCategories.
+4. *Universal &amp; Age-Gated Categories (US 5.4, 5.5, 5.6):*
+* Assert *"Travel"* and *"At Risk"* are always present in the otherCategories array regardless of mock profile.
+* Mock age: 16. Assert "Children" appears in otherCategories. Mock age: 15. Assert it is excluded.
+5. *Graceful Degradation (US 5.9):*
+* Mock an empty profile (age: null, gender: undefined, lmpDate: null).
+* Assert the hook does not crash. Assert recommended array is [] (empty). Assert otherCategories contains "Travel", "At Risk", and any other universal fallbacks, but no age-specific cards.</t>
+  </si>
+  <si>
+    <t>US 5.0, 5.1, 5.7, 5.8</t>
+  </si>
+  <si>
+    <t>Create test/Immunisation/immunisation-ui-layout.test.tsx</t>
+  </si>
+  <si>
+    <t>Ambiguity-Free Technical Specification:*
+1. *Test Setup:* Use @testing-library/react-native to mount &lt;ImmunisationCheck/&gt;. Mock the expo-router to intercept navigation calls. Mock useImmunisationCategories to return standard dummy data.
+2. *Hierarchy &amp; Sections (US 5.1):*
+* Use getByText to assert the presence of exact text nodes: "Recommended for You", "Quick Actions", and "Other Categories".
+* Assert they appear in exactly that vertical order (by checking their relative positions or parent nodes).
+* Assert the old redundant text ("Recommended for Age 25") does not exist in the DOM.
+3. *Interactions &amp; Routing (US 5.7, 5.8):*
+* Query the CategoryCard for "Travel".
+* Execute fireEvent.press.
+* Assert router.push was called with the exact argument '/immunisation/travel'.
+4. *Text Truncation (US 5.1):*
+* Assert that the rendered CategoryCard's primary Text component contains the exact prop numberOfLines={1}. Do not allow Marquee components to pass the test.</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> US 5.0, 5.1, 5.7</t>
+  </si>
+  <si>
+    <t>* Create constants/ImmunisationData.ts
+* Modify app/(tabs)/health-screening.tsx</t>
+  </si>
+  <si>
+    <t xml:space="preserve">*Ambiguity-Free Technical Specification:*
+1. *Data Dictionary:* In ImmunisationData.ts, export the fully updated, strictly typed JSON structure containing the *9 categories*.
+* Ensure seventyFivePlus logic explicitly replaces the old 70+ bracket.
+* Ensure the atRisk category is included alongside its respective condition list.
+* Under the travel key, ensure the 3 new vaccines (Cholera, Tuberculosis, Rabies) and the external URL links are present.
+2. *Router State Extension:* In health-screening.tsx, locate const [activeTab, setActiveTab] = useState&lt;"cancer" | "health"&gt;(initialTab);.
+* Update the union type to include "vaccine": useState&lt;"cancer" | "health" | "vaccine"&gt;.
+* Update the initialTab useMemo hook to accept the incoming deep link: return tabParam === "cancer" || tabParam === "health" || tabParam === "vaccine" ? tabParam : "health";
+3. *UI Route Injection:* In the ScrollView return block of health-screening.tsx, update the ternary operator to render the container:
+tsx
+{activeTab === "cancer" ? (
+  /* existing cancer logic */
+) : activeTab === "health" ? (
+  /* existing health logic */
+) : (
+  &lt;ImmunisationCheck /&gt;
+)}
+</t>
+  </si>
+  <si>
+    <t>US 5.0, 5.1</t>
+  </si>
+  <si>
+    <t>* Modify components/screening/ScreeningTabs.tsx
+* Rename &amp; Modify components/screening/ImmunisationCheck.tsx (ensure 's' spelling).</t>
+  </si>
+  <si>
+    <t>*Ambiguity-Free Technical Specification:*
+1. *Tab UI (US 5.0):* In ScreeningTabs.tsx, append the 3rd touchable tab button: "Vaccine". Ensure the layout evenly distributes (e.g., flex-1 per tab). Wire its onPress to fire setActiveTab("vaccine").
+2. *Scaffold Implementation (US 5.1):* Open ImmunisationCheck.tsx. Delete the old redundant "Recommended for Age X" cards.
+3. *Layout Structure:* Implement a View with top-to-bottom layout:
+* Text component with bold styling for "Recommended for You".
+* (Empty injection View for FE-5.4).
+* Text component with bold styling for "Quick Actions".
+* Move the existing "Add New Vaccination" and "NSW Schedule" touchable buttons here. Ensure their existing onPress modal triggers remain completely intact.
+* Text component with bold styling for "Other Categories".</t>
+  </si>
+  <si>
+    <t>US 5.1, 5.8</t>
+  </si>
+  <si>
+    <t>Create components/screening/ImmunisationCategoryCard.tsx</t>
+  </si>
+  <si>
+    <t>*Ambiguity-Free Technical Specification:*
+1. *Component Signature:* export default function ImmunisationCategoryCard({ title, subtitle, isRecommended, onPress }: Props)
+2. *Styling Rules (Strict):*
+* Use TouchableOpacity for the container.
+* If isRecommended === true: Apply a colored accent border (e.g., borderColor: '#FDBA74' / Tailwind border-orange-200) or a left-border color stripe.
+* If isRecommended === false: Apply a standard grey border (borderColor: '#E5E7EB').
+3. *Typography &amp; Layout:*
+* Title Text: numberOfLines={1} and ellipsizeMode="tail".
+* Subtitle Text: numberOfLines={1} (rendered in a lighter grey font).
+* Trailing Icon: Place a ChevronRight (or equivalent from @expo/vector-icons) aligned to the absolute right side to clearly indicate it navigates to a new screen. Do not implement marquee scrolling.</t>
+  </si>
+  <si>
+    <t>* Create hooks/useImmunisationCategories.ts
+* Modify components/screening/ImmunisationCheck.tsx</t>
+  </si>
+  <si>
+    <t>Ambiguity-Free Technical Specification:*
+1. *Hook Logic:* Create the hook to ingest the user's global profile state (importing age, gender, dob, lmpDate from your existing Context/Zustand store).
+2. *Implementation:* Write the exact logic validated in QA-FE-5.1 to evaluate the profile against ImmunisationData.ts keys.
+* Update the age evaluation thresholds: Split logic must handle seventyFivePlus strictly for users aged &gt;= 75.
+* Ensure the atRisk array is universally pushed to the otherCategories array.
+* Return exactly two arrays: { recommended: CategoryItem[], otherCategories: CategoryItem[] }. If age is null, recommended must return [].
+3. *Component Wiring:* Inside ImmunisationCheck.tsx, call the hook.
+4. *Render Maps:*
+* Under "Recommended for You", execute recommended.map((cat) =&gt; ...). Render &lt;ImmunisationCategoryCard ... isRecommended="{true}" onPress="{()"&gt; router.push('/immunisation/' + cat.id)}/&gt;.
+* Empty State Check: If recommended.length === 0, render a fallback Text (e.g., "Update your profile age to see personalized recommendations.").
+* Under "Other Categories", execute otherCategories.map((cat) =&gt; ...). Render &lt;ImmunisationCategoryCard ... isRecommended="{false}" onPress="{()"&gt; router.push('/immunisation/' + cat.id)}/&gt;.</t>
+  </si>
+  <si>
+    <t>US 5.7, 5.8</t>
+  </si>
+  <si>
+    <t>* Create: components/screening/ImmunisationListItem.tsx
+* Create: app/immunisation/[category].tsx</t>
+  </si>
+  <si>
+    <t>*Ambiguity-Free Technical Specification:*
+*1. Create the ImmunisationListItem Component*
+* *Signature:* export default function ImmunisationListItem({ name, subtitle, onPress }: Props)
+* *Styling (Strict):*
+* Use a TouchableOpacity container with standard card styling: bg-white, rounded-xl, border border-gray-100, p-4, mb-3. Apply subtle shadow elevation.
+* *Primary Text:* Render name using font-pmedium text-gray-900.
+* *Secondary Text (CRITICAL):* If subtitle exists, render it directly below the name using font-pregular text-gray-500 text-sm. *Do NOT use numberOfLines={1}.* Allow this text to fully wrap so users can read the detailed clinical rules and conditions.
+* *Trailing Action:* Add a trailing Ionicons (e.g., chevron-forward or information-circle-outline) aligned to the right side.
+*2. Create the Dynamic Route Screen ([category].tsx)*
+* *Dynamic Route Init:* Use const { category } = useLocalSearchParams(); to grab the ID (e.g., 'travel').
+* *Navigation Header:* Use Stack.Screen to dynamically set the header title.
+* *Data Fetching:* Look up the category string as a key in constants/ImmunisationData.ts to retrieve the array of vaccines for that specific list.
+* *UI Layout (US 5.7):* Render a FlatList.
+* contentContainerStyle: Add standard padding (px-5, pt-4, pb-10).
+* renderItem: Return &lt;ImmunisationListItem name="{item.name}" onPress="{()" subtitle="{item.subtitle}"&gt; handleVaccinePress(item)} /&gt;.
+* ListEmptyComponent: Render an &lt;EmptyState message="No vaccines found for this category."/&gt; component gracefully.
+* *Interaction (US 5.8):* Write the handleVaccinePress function.
+* If item.link exists, execute WebBrowser.openBrowserAsync(item.link) to open external URLs (like for TB/Cholera).
+* Otherwise, log selection or wire to standard detail modal alert.</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> </t>
+  </si>
+  <si>
+    <t>.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  .</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Create test/Immunisation/use-immunisation-categories.test.ts  *Ambiguity-Free Technical Specification:*
+1. *Test Setup:* Initialize a pure Jest test suite using @testing-library/react-hooks (or React test renderer) to validate the pure logic of the useImmunisationCategories hook.
+2. *Age Mapping (US 5.2):*
+* Mock global profile age: 18. Assert recommended array strictly contains { id: 'adult', title: 'Adults' }.
+* Test boundary conditions: age: 49 (Adult), age: 50 (50+ Years), age: 15 (Adolescent), age: 75 (75+ Years). Assert only one age category is ever returned in recommended.
+3. *Pregnancy Mapping (US 5.3):*
+* Mock profile gender: 'female', lmpDate: '2026-08-01', age: 25. Assert recommended array has length 2 and contains both "Adults" and "Pregnancy".
+* Mock gender: 'male' with an lmpDate. Assert "Pregnancy" is strictly excluded from recommended and otherCategories.
+4. *Universal &amp; Age-Gated Categories (US 5.4, 5.5, 5.6):*
+* Assert *"Travel"* and *"At Risk"* are always present in the otherCategories array regardless of mock profile.
+* Mock age: 16. Assert "Children" appears in otherCategories. Mock age: 15. Assert it is excluded.
+5. *Graceful Degradation (US 5.9):*
+* Mock an empty profile (age: null, gender: undefined, lmpDate: null).
+* Assert the hook does not crash. Assert recommended array is [] (empty). Assert otherCategories contains "Travel", "At Risk", and any other universal fallbacks, but no age-specific cards.</t>
+  </si>
+  <si>
+    <t>Create test/Immunisation/immunisation-ui-layout.test.tsx         Ambiguity-Free Technical Specification:*
+1. *Test Setup:* Use @testing-library/react-native to mount &lt;ImmunisationCheck/&gt;. Mock the expo-router to intercept navigation calls. Mock useImmunisationCategories to return standard dummy data.
+2. *Hierarchy &amp; Sections (US 5.1):*
+* Use getByText to assert the presence of exact text nodes: "Recommended for You", "Quick Actions", and "Other Categories".
+* Assert they appear in exactly that vertical order (by checking their relative positions or parent nodes).
+* Assert the old redundant text ("Recommended for Age 25") does not exist in the DOM.
+3. *Interactions &amp; Routing (US 5.7, 5.8):*
+* Query the CategoryCard for "Travel".
+* Execute fireEvent.press.
+* Assert router.push was called with the exact argument '/immunisation/travel'.
+4. *Text Truncation (US 5.1):*
+* Assert that the rendered CategoryCard's primary Text component contains the exact prop numberOfLines={1}. Do not allow Marquee components to pass the test.</t>
+  </si>
+  <si>
+    <t>* Create constants/ImmunisationData.ts
+* Modify app/(tabs)/health-screening.tsx       *Ambiguity-Free Technical Specification:*
+1. *Data Dictionary:* In ImmunisationData.ts, export the fully updated, strictly typed JSON structure containing the *9 categories*.
+* Ensure seventyFivePlus logic explicitly replaces the old 70+ bracket.
+* Ensure the atRisk category is included alongside its respective condition list.
+* Under the travel key, ensure the 3 new vaccines (Cholera, Tuberculosis, Rabies) and the external URL links are present.
+2. *Router State Extension:* In health-screening.tsx, locate const [activeTab, setActiveTab] = useState&lt;"cancer" | "health"&gt;(initialTab);.
+* Update the union type to include "vaccine": useState&lt;"cancer" | "health" | "vaccine"&gt;.
+* Update the initialTab useMemo hook to accept the incoming deep link: return tabParam === "cancer" || tabParam === "health" || tabParam === "vaccine" ? tabParam : "health";
+3. *UI Route Injection:* In the ScrollView return block of health-screening.tsx, update the ternary operator to render the container:
+tsx
+{activeTab === "cancer" ? (
+  /* existing cancer logic */
+) : activeTab === "health" ? (
+  /* existing health logic */
+) : (
+  &lt;ImmunisationCheck /&gt;
+)}</t>
+  </si>
+  <si>
+    <t>* Modify components/screening/ScreeningTabs.tsx
+* Rename &amp; Modify components/screening/ImmunisationCheck.tsx (ensure 's' spelling).            *Ambiguity-Free Technical Specification:*
+1. *Tab UI (US 5.0):* In ScreeningTabs.tsx, append the 3rd touchable tab button: "Vaccine". Ensure the layout evenly distributes (e.g., flex-1 per tab). Wire its onPress to fire setActiveTab("vaccine").
+2. *Scaffold Implementation (US 5.1):* Open ImmunisationCheck.tsx. Delete the old redundant "Recommended for Age X" cards.
+3. *Layout Structure:* Implement a View with top-to-bottom layout:
+* Text component with bold styling for "Recommended for You".
+* (Empty injection View for FE-5.4).
+* Text component with bold styling for "Quick Actions".
+* Move the existing "Add New Vaccination" and "NSW Schedule" touchable buttons here. Ensure their existing onPress modal triggers remain completely intact.
+* Text component with bold styling for "Other Categories".</t>
+  </si>
+  <si>
+    <t>Create components/screening/ImmunisationCategoryCard.tsx       *Ambiguity-Free Technical Specification:*
+1. *Component Signature:* export default function ImmunisationCategoryCard({ title, subtitle, isRecommended, onPress }: Props)
+2. *Styling Rules (Strict):*
+* Use TouchableOpacity for the container.
+* If isRecommended === true: Apply a colored accent border (e.g., borderColor: '#FDBA74' / Tailwind border-orange-200) or a left-border color stripe.
+* If isRecommended === false: Apply a standard grey border (borderColor: '#E5E7EB').
+3. *Typography &amp; Layout:*
+* Title Text: numberOfLines={1} and ellipsizeMode="tail".
+* Subtitle Text: numberOfLines={1} (rendered in a lighter grey font).
+* Trailing Icon: Place a ChevronRight (or equivalent from @expo/vector-icons) aligned to the absolute right side to clearly indicate it navigates to a new screen. Do not implement marquee scrolling.</t>
+  </si>
+  <si>
+    <t>* Create hooks/useImmunisationCategories.ts
+* Modify components/screening/ImmunisationCheck.tsx           Ambiguity-Free Technical Specification:*
+1. *Hook Logic:* Create the hook to ingest the user's global profile state (importing age, gender, dob, lmpDate from your existing Context/Zustand store).
+2. *Implementation:* Write the exact logic validated in QA-FE-5.1 to evaluate the profile against ImmunisationData.ts keys.
+* Update the age evaluation thresholds: Split logic must handle seventyFivePlus strictly for users aged &gt;= 75.
+* Ensure the atRisk array is universally pushed to the otherCategories array.
+* Return exactly two arrays: { recommended: CategoryItem[], otherCategories: CategoryItem[] }. If age is null, recommended must return [].
+3. *Component Wiring:* Inside ImmunisationCheck.tsx, call the hook.
+4. *Render Maps:*
+* Under "Recommended for You", execute recommended.map((cat) =&gt; ...). Render &lt;ImmunisationCategoryCard ... isRecommended="{true}" onPress="{()"&gt; router.push('/immunisation/' + cat.id)}/&gt;.
+* Empty State Check: If recommended.length === 0, render a fallback Text (e.g., "Update your profile age to see personalized recommendations.").
+* Under "Other Categories", execute otherCategories.map((cat) =&gt; ...). Render &lt;ImmunisationCategoryCard ... isRecommended="{false}" onPress="{()"&gt; router.push('/immunisation/' + cat.id)}/&gt;.</t>
+  </si>
+  <si>
+    <t>* Create: components/screening/ImmunisationListItem.tsx
+* Create: app/immunisation/[category].tsx     *Ambiguity-Free Technical Specification:*
+*1. Create the ImmunisationListItem Component*
+* *Signature:* export default function ImmunisationListItem({ name, subtitle, onPress }: Props)
+* *Styling (Strict):*
+* Use a TouchableOpacity container with standard card styling: bg-white, rounded-xl, border border-gray-100, p-4, mb-3. Apply subtle shadow elevation.
+* *Primary Text:* Render name using font-pmedium text-gray-900.
+* *Secondary Text (CRITICAL):* If subtitle exists, render it directly below the name using font-pregular text-gray-500 text-sm. *Do NOT use numberOfLines={1}.* Allow this text to fully wrap so users can read the detailed clinical rules and conditions.
+* *Trailing Action:* Add a trailing Ionicons (e.g., chevron-forward or information-circle-outline) aligned to the right side.
+*2. Create the Dynamic Route Screen ([category].tsx)*
+* *Dynamic Route Init:* Use const { category } = useLocalSearchParams(); to grab the ID (e.g., 'travel').
+* *Navigation Header:* Use Stack.Screen to dynamically set the header title.
+* *Data Fetching:* Look up the category string as a key in constants/ImmunisationData.ts to retrieve the array of vaccines for that specific list.
+* *UI Layout (US 5.7):* Render a FlatList.
+* contentContainerStyle: Add standard padding (px-5, pt-4, pb-10).
+* renderItem: Return &lt;ImmunisationListItem name="{item.name}" onPress="{()" subtitle="{item.subtitle}"&gt; handleVaccinePress(item)} /&gt;.
+* ListEmptyComponent: Render an &lt;EmptyState message="No vaccines found for this category."/&gt; component gracefully.
+* *Interaction (US 5.8):* Write the handleVaccinePress function.
+* If item.link exists, execute WebBrowser.openBrowserAsync(item.link) to open external URLs (like for TB/Cholera).
+* Otherwise, log selection or wire to standard detail modal alert.</t>
+  </si>
 </sst>
 </file>
 
@@ -6246,7 +6525,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="8">
+  <fills count="9">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -6289,8 +6568,14 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.39997558519241921"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="2">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -6313,11 +6598,22 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="23">
+  <cellXfs count="31">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -6384,6 +6680,28 @@
     </xf>
     <xf numFmtId="0" fontId="3" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -17294,7 +17612,7 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5C8CD023-91C8-44AF-AB04-2727DDB868DE}">
-  <dimension ref="A1:L5"/>
+  <dimension ref="A1:L15"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="6.88671875" bestFit="1" customWidth="1"/>
@@ -17469,6 +17787,137 @@
       <c r="K5" s="12"/>
       <c r="L5" s="12"/>
     </row>
+    <row r="6" spans="1:12" ht="201" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A6" s="28">
+        <v>9</v>
+      </c>
+      <c r="B6" s="28" t="s">
+        <v>163</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>164</v>
+      </c>
+      <c r="D6" t="s">
+        <v>165</v>
+      </c>
+      <c r="E6" s="28" t="s">
+        <v>31</v>
+      </c>
+      <c r="F6" s="30" t="s">
+        <v>166</v>
+      </c>
+      <c r="G6" s="28" t="s">
+        <v>29</v>
+      </c>
+      <c r="J6" s="28" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="7" spans="1:12" ht="201" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A7" s="28">
+        <v>10</v>
+      </c>
+      <c r="E7" s="28" t="s">
+        <v>31</v>
+      </c>
+      <c r="F7" s="29" t="s">
+        <v>167</v>
+      </c>
+      <c r="G7" s="28" t="s">
+        <v>29</v>
+      </c>
+      <c r="J7" s="28" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="8" spans="1:12" ht="201" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A8" s="28">
+        <v>11</v>
+      </c>
+      <c r="E8" s="28" t="s">
+        <v>20</v>
+      </c>
+      <c r="F8" s="2" t="s">
+        <v>168</v>
+      </c>
+      <c r="G8" s="28" t="s">
+        <v>29</v>
+      </c>
+      <c r="J8" s="28" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="9" spans="1:12" ht="201" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A9" s="28">
+        <v>12</v>
+      </c>
+      <c r="E9" s="28" t="s">
+        <v>20</v>
+      </c>
+      <c r="F9" s="2" t="s">
+        <v>169</v>
+      </c>
+      <c r="G9" s="28" t="s">
+        <v>29</v>
+      </c>
+      <c r="J9" s="28" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="10" spans="1:12" ht="201" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A10" s="28">
+        <v>13</v>
+      </c>
+      <c r="E10" s="28" t="s">
+        <v>20</v>
+      </c>
+      <c r="F10" s="2" t="s">
+        <v>170</v>
+      </c>
+      <c r="G10" s="28" t="s">
+        <v>29</v>
+      </c>
+      <c r="J10" s="28" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="11" spans="1:12" ht="201" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A11" s="28">
+        <v>14</v>
+      </c>
+      <c r="E11" s="28" t="s">
+        <v>20</v>
+      </c>
+      <c r="F11" s="2" t="s">
+        <v>171</v>
+      </c>
+      <c r="G11" s="28" t="s">
+        <v>29</v>
+      </c>
+      <c r="J11" s="28" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="12" spans="1:12" ht="201" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A12" s="28">
+        <v>15</v>
+      </c>
+      <c r="E12" s="28" t="s">
+        <v>20</v>
+      </c>
+      <c r="F12" s="2" t="s">
+        <v>172</v>
+      </c>
+      <c r="G12" s="28" t="s">
+        <v>29</v>
+      </c>
+      <c r="J12" s="28" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="13" spans="1:12" ht="201" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="14" spans="1:12" ht="201" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="15" spans="1:12" ht="201" customHeight="1" x14ac:dyDescent="0.3"/>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -17481,4 +17930,179 @@
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{77C8A1D8-5FD1-4598-938B-0A9A8F9AF879}">
+  <dimension ref="A6:J14"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="4" max="4" width="18.109375" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="17.77734375" customWidth="1"/>
+    <col min="6" max="6" width="60.88671875" customWidth="1"/>
+    <col min="7" max="7" width="14.5546875" customWidth="1"/>
+    <col min="8" max="8" width="14.6640625" customWidth="1"/>
+    <col min="9" max="9" width="11.33203125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="6" spans="1:10" ht="40.799999999999997" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A6" s="23" t="s">
+        <v>142</v>
+      </c>
+      <c r="B6" s="23" t="s">
+        <v>0</v>
+      </c>
+      <c r="C6" s="23" t="s">
+        <v>10</v>
+      </c>
+      <c r="D6" s="24" t="s">
+        <v>140</v>
+      </c>
+      <c r="E6" s="23" t="s">
+        <v>141</v>
+      </c>
+      <c r="F6" s="23" t="s">
+        <v>3</v>
+      </c>
+      <c r="G6" s="23" t="s">
+        <v>4</v>
+      </c>
+      <c r="H6" s="23" t="s">
+        <v>8</v>
+      </c>
+      <c r="I6" s="23" t="s">
+        <v>9</v>
+      </c>
+      <c r="J6" s="23" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="7" spans="1:10" ht="300" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A7" s="1">
+        <v>1</v>
+      </c>
+      <c r="C7" s="25" t="s">
+        <v>31</v>
+      </c>
+      <c r="D7" s="26" t="s">
+        <v>143</v>
+      </c>
+      <c r="E7" s="26" t="s">
+        <v>144</v>
+      </c>
+      <c r="F7" s="2" t="s">
+        <v>145</v>
+      </c>
+      <c r="G7" s="3"/>
+    </row>
+    <row r="8" spans="1:10" ht="248.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A8" s="1">
+        <v>2</v>
+      </c>
+      <c r="C8" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="D8" s="1" t="s">
+        <v>146</v>
+      </c>
+      <c r="E8" s="27" t="s">
+        <v>147</v>
+      </c>
+      <c r="F8" s="2" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="9" spans="1:10" ht="216" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A9" s="1">
+        <v>3</v>
+      </c>
+      <c r="C9" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="D9" s="1" t="s">
+        <v>149</v>
+      </c>
+      <c r="E9" s="27" t="s">
+        <v>150</v>
+      </c>
+      <c r="F9" s="2" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="10" spans="1:10" ht="216" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A10" s="1">
+        <v>4</v>
+      </c>
+      <c r="C10" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="D10" s="1" t="s">
+        <v>152</v>
+      </c>
+      <c r="E10" s="27" t="s">
+        <v>153</v>
+      </c>
+      <c r="F10" s="26" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="11" spans="1:10" ht="216" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A11" s="1">
+        <v>5</v>
+      </c>
+      <c r="C11" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="D11" s="1" t="s">
+        <v>155</v>
+      </c>
+      <c r="E11" s="27" t="s">
+        <v>156</v>
+      </c>
+      <c r="F11" s="2" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="12" spans="1:10" ht="216" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A12" s="1">
+        <v>6</v>
+      </c>
+      <c r="C12" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="D12" s="27" t="s">
+        <v>143</v>
+      </c>
+      <c r="E12" s="27" t="s">
+        <v>158</v>
+      </c>
+      <c r="F12" s="2" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="13" spans="1:10" ht="216" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A13" s="1">
+        <v>7</v>
+      </c>
+      <c r="C13" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="D13" s="1" t="s">
+        <v>160</v>
+      </c>
+      <c r="E13" s="27" t="s">
+        <v>161</v>
+      </c>
+      <c r="F13" s="2" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="14" spans="1:10" ht="216" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A14">
+        <v>8</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/Business Analysis/checkupp_sprint_plan_2026.xlsx
+++ b/Business Analysis/checkupp_sprint_plan_2026.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\CheckUpp\Business Analysis\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitHub\CheckUpp\Business Analysis\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E152211D-3EEE-40DC-8115-60626A46579A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3FE411C8-EA14-45C1-ABEC-A4FB492A532B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" firstSheet="3" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="3" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sprint 01" sheetId="1" r:id="rId1"/>
@@ -65,7 +65,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="528" uniqueCount="173">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="546" uniqueCount="171">
   <si>
     <t>Epic</t>
   </si>
@@ -6317,40 +6317,6 @@
     <t>US 5.7, 5.8</t>
   </si>
   <si>
-    <t>* Create: components/screening/ImmunisationListItem.tsx
-* Create: app/immunisation/[category].tsx</t>
-  </si>
-  <si>
-    <t>*Ambiguity-Free Technical Specification:*
-*1. Create the ImmunisationListItem Component*
-* *Signature:* export default function ImmunisationListItem({ name, subtitle, onPress }: Props)
-* *Styling (Strict):*
-* Use a TouchableOpacity container with standard card styling: bg-white, rounded-xl, border border-gray-100, p-4, mb-3. Apply subtle shadow elevation.
-* *Primary Text:* Render name using font-pmedium text-gray-900.
-* *Secondary Text (CRITICAL):* If subtitle exists, render it directly below the name using font-pregular text-gray-500 text-sm. *Do NOT use numberOfLines={1}.* Allow this text to fully wrap so users can read the detailed clinical rules and conditions.
-* *Trailing Action:* Add a trailing Ionicons (e.g., chevron-forward or information-circle-outline) aligned to the right side.
-*2. Create the Dynamic Route Screen ([category].tsx)*
-* *Dynamic Route Init:* Use const { category } = useLocalSearchParams(); to grab the ID (e.g., 'travel').
-* *Navigation Header:* Use Stack.Screen to dynamically set the header title.
-* *Data Fetching:* Look up the category string as a key in constants/ImmunisationData.ts to retrieve the array of vaccines for that specific list.
-* *UI Layout (US 5.7):* Render a FlatList.
-* contentContainerStyle: Add standard padding (px-5, pt-4, pb-10).
-* renderItem: Return &lt;ImmunisationListItem name="{item.name}" onPress="{()" subtitle="{item.subtitle}"&gt; handleVaccinePress(item)} /&gt;.
-* ListEmptyComponent: Render an &lt;EmptyState message="No vaccines found for this category."/&gt; component gracefully.
-* *Interaction (US 5.8):* Write the handleVaccinePress function.
-* If item.link exists, execute WebBrowser.openBrowserAsync(item.link) to open external URLs (like for TB/Cholera).
-* Otherwise, log selection or wire to standard detail modal alert.</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> </t>
-  </si>
-  <si>
-    <t>.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  .</t>
-  </si>
-  <si>
     <t xml:space="preserve"> Create test/Immunisation/use-immunisation-categories.test.ts  *Ambiguity-Free Technical Specification:*
 1. *Test Setup:* Initialize a pure Jest test suite using @testing-library/react-hooks (or React test renderer) to validate the pure logic of the useImmunisationCategories hook.
 2. *Age Mapping (US 5.2):*
@@ -6439,9 +6405,9 @@
 * Under "Other Categories", execute otherCategories.map((cat) =&gt; ...). Render &lt;ImmunisationCategoryCard ... isRecommended="{false}" onPress="{()"&gt; router.push('/immunisation/' + cat.id)}/&gt;.</t>
   </si>
   <si>
-    <t>* Create: components/screening/ImmunisationListItem.tsx
+    <t>* Create: components/screening/VaccineListItem.tsx
 * Create: app/immunisation/[category].tsx     *Ambiguity-Free Technical Specification:*
-*1. Create the ImmunisationListItem Component*
+*1. Create the VaccineListItem Component*
 * *Signature:* export default function ImmunisationListItem({ name, subtitle, onPress }: Props)
 * *Styling (Strict):*
 * Use a TouchableOpacity container with standard card styling: bg-white, rounded-xl, border border-gray-100, p-4, mb-3. Apply subtle shadow elevation.
@@ -6454,11 +6420,21 @@
 * *Data Fetching:* Look up the category string as a key in constants/ImmunisationData.ts to retrieve the array of vaccines for that specific list.
 * *UI Layout (US 5.7):* Render a FlatList.
 * contentContainerStyle: Add standard padding (px-5, pt-4, pb-10).
-* renderItem: Return &lt;ImmunisationListItem name="{item.name}" onPress="{()" subtitle="{item.subtitle}"&gt; handleVaccinePress(item)} /&gt;.
+* renderItem: Return &lt;VaccineListItem name="{item.name}" onPress="{()" subtitle="{item.subtitle}"&gt; handleVaccinePress(item)} /&gt;.
 * ListEmptyComponent: Render an &lt;EmptyState message="No vaccines found for this category."/&gt; component gracefully.
 * *Interaction (US 5.8):* Write the handleVaccinePress function.
 * If item.link exists, execute WebBrowser.openBrowserAsync(item.link) to open external URLs (like for TB/Cholera).
 * Otherwise, log selection or wire to standard detail modal alert.</t>
+  </si>
+  <si>
+    <t>* Create: components/screening/VaccineListItem.tsx
+* Create: app/immunisation/[category].tsx</t>
+  </si>
+  <si>
+    <t>Immunisation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  </t>
   </si>
 </sst>
 </file>
@@ -6525,7 +6501,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="9">
+  <fills count="10">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -6574,8 +6550,14 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.39997558519241921"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="3">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -6598,22 +6580,11 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="31">
+  <cellXfs count="32">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -6694,13 +6665,14 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -17612,7 +17584,7 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5C8CD023-91C8-44AF-AB04-2727DDB868DE}">
-  <dimension ref="A1:L15"/>
+  <dimension ref="A1:M15"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="6.88671875" bestFit="1" customWidth="1"/>
@@ -17622,14 +17594,14 @@
     <col min="5" max="5" width="7.88671875" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="82.88671875" customWidth="1"/>
     <col min="7" max="7" width="8" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="7.109375" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="6" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="7.109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="6" style="1" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="6.77734375" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="8" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="5.77734375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" ht="46.8" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:13" ht="46.8" x14ac:dyDescent="0.3">
       <c r="A1" s="4" t="s">
         <v>11</v>
       </c>
@@ -17667,7 +17639,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="2" spans="1:12" ht="244.8" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:13" ht="244.8" x14ac:dyDescent="0.3">
       <c r="A2" s="12">
         <v>5</v>
       </c>
@@ -17688,7 +17660,8 @@
       <c r="H2" s="12" t="s">
         <v>23</v>
       </c>
-      <c r="I2" s="12">
+      <c r="I2" s="12" cm="1">
+        <f t="array" ref="I2">_xlfn.SWITCH(H2,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
         <v>2</v>
       </c>
       <c r="J2" s="12" t="s">
@@ -17697,7 +17670,7 @@
       <c r="K2" s="12"/>
       <c r="L2" s="12"/>
     </row>
-    <row r="3" spans="1:12" ht="316.8" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:13" ht="316.8" x14ac:dyDescent="0.3">
       <c r="A3" s="12">
         <v>6</v>
       </c>
@@ -17718,7 +17691,8 @@
       <c r="H3" s="12" t="s">
         <v>23</v>
       </c>
-      <c r="I3" s="12">
+      <c r="I3" s="12" cm="1">
+        <f t="array" ref="I3">_xlfn.SWITCH(H3,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
         <v>2</v>
       </c>
       <c r="J3" s="12" t="s">
@@ -17727,7 +17701,7 @@
       <c r="K3" s="12"/>
       <c r="L3" s="12"/>
     </row>
-    <row r="4" spans="1:12" ht="244.8" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:13" ht="244.8" x14ac:dyDescent="0.3">
       <c r="A4" s="12">
         <v>7</v>
       </c>
@@ -17748,7 +17722,8 @@
       <c r="H4" s="12" t="s">
         <v>23</v>
       </c>
-      <c r="I4" s="12">
+      <c r="I4" s="12" cm="1">
+        <f t="array" ref="I4">_xlfn.SWITCH(H4,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
         <v>2</v>
       </c>
       <c r="J4" s="12" t="s">
@@ -17757,7 +17732,7 @@
       <c r="K4" s="12"/>
       <c r="L4" s="12"/>
     </row>
-    <row r="5" spans="1:12" ht="216" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:13" ht="216" x14ac:dyDescent="0.3">
       <c r="A5" s="12">
         <v>8</v>
       </c>
@@ -17778,7 +17753,8 @@
       <c r="H5" s="12" t="s">
         <v>27</v>
       </c>
-      <c r="I5" s="12">
+      <c r="I5" s="12" cm="1">
+        <f t="array" ref="I5">_xlfn.SWITCH(H5,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
         <v>3</v>
       </c>
       <c r="J5" s="12" t="s">
@@ -17787,137 +17763,241 @@
       <c r="K5" s="12"/>
       <c r="L5" s="12"/>
     </row>
-    <row r="6" spans="1:12" ht="201" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:13" ht="201" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="28">
         <v>9</v>
       </c>
       <c r="B6" s="28" t="s">
-        <v>163</v>
-      </c>
-      <c r="C6" s="1" t="s">
-        <v>164</v>
-      </c>
-      <c r="D6" t="s">
-        <v>165</v>
+        <v>169</v>
+      </c>
+      <c r="C6" s="29"/>
+      <c r="D6" s="30" t="s">
+        <v>170</v>
       </c>
       <c r="E6" s="28" t="s">
         <v>31</v>
       </c>
-      <c r="F6" s="30" t="s">
-        <v>166</v>
+      <c r="F6" s="31" t="s">
+        <v>161</v>
       </c>
       <c r="G6" s="28" t="s">
         <v>29</v>
       </c>
+      <c r="H6" s="29" t="s">
+        <v>27</v>
+      </c>
+      <c r="I6" s="29" cm="1">
+        <f t="array" ref="I6">_xlfn.SWITCH(H6,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
+        <v>3</v>
+      </c>
       <c r="J6" s="28" t="s">
         <v>76</v>
       </c>
-    </row>
-    <row r="7" spans="1:12" ht="201" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="K6" s="30"/>
+      <c r="L6" s="30"/>
+      <c r="M6" s="25"/>
+    </row>
+    <row r="7" spans="1:13" ht="201" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="28">
         <v>10</v>
       </c>
+      <c r="B7" s="28" t="s">
+        <v>169</v>
+      </c>
+      <c r="C7" s="29"/>
+      <c r="D7" s="30" t="s">
+        <v>170</v>
+      </c>
       <c r="E7" s="28" t="s">
         <v>31</v>
       </c>
-      <c r="F7" s="29" t="s">
-        <v>167</v>
+      <c r="F7" s="31" t="s">
+        <v>162</v>
       </c>
       <c r="G7" s="28" t="s">
         <v>29</v>
       </c>
+      <c r="H7" s="29" t="s">
+        <v>27</v>
+      </c>
+      <c r="I7" s="29" cm="1">
+        <f t="array" ref="I7">_xlfn.SWITCH(H7,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
+        <v>3</v>
+      </c>
       <c r="J7" s="28" t="s">
         <v>76</v>
       </c>
-    </row>
-    <row r="8" spans="1:12" ht="201" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="K7" s="30"/>
+      <c r="L7" s="30"/>
+    </row>
+    <row r="8" spans="1:13" ht="201" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="28">
         <v>11</v>
       </c>
+      <c r="B8" s="28" t="s">
+        <v>169</v>
+      </c>
+      <c r="C8" s="29"/>
+      <c r="D8" s="30" t="s">
+        <v>170</v>
+      </c>
       <c r="E8" s="28" t="s">
         <v>20</v>
       </c>
-      <c r="F8" s="2" t="s">
-        <v>168</v>
+      <c r="F8" s="31" t="s">
+        <v>163</v>
       </c>
       <c r="G8" s="28" t="s">
         <v>29</v>
       </c>
+      <c r="H8" s="29" t="s">
+        <v>23</v>
+      </c>
+      <c r="I8" s="29" cm="1">
+        <f t="array" ref="I8">_xlfn.SWITCH(H8,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
+        <v>2</v>
+      </c>
       <c r="J8" s="28" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="9" spans="1:12" ht="201" customHeight="1" x14ac:dyDescent="0.3">
+        <v>75</v>
+      </c>
+      <c r="K8" s="30"/>
+      <c r="L8" s="30"/>
+    </row>
+    <row r="9" spans="1:13" ht="201" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="28">
         <v>12</v>
       </c>
+      <c r="B9" s="28" t="s">
+        <v>169</v>
+      </c>
+      <c r="C9" s="29"/>
+      <c r="D9" s="30" t="s">
+        <v>170</v>
+      </c>
       <c r="E9" s="28" t="s">
         <v>20</v>
       </c>
-      <c r="F9" s="2" t="s">
-        <v>169</v>
+      <c r="F9" s="31" t="s">
+        <v>164</v>
       </c>
       <c r="G9" s="28" t="s">
         <v>29</v>
       </c>
+      <c r="H9" s="29" t="s">
+        <v>30</v>
+      </c>
+      <c r="I9" s="29" cm="1">
+        <f t="array" ref="I9">_xlfn.SWITCH(H9,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
+        <v>5</v>
+      </c>
       <c r="J9" s="28" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="10" spans="1:12" ht="201" customHeight="1" x14ac:dyDescent="0.3">
+        <v>75</v>
+      </c>
+      <c r="K9" s="30"/>
+      <c r="L9" s="30"/>
+    </row>
+    <row r="10" spans="1:13" ht="201" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="28">
         <v>13</v>
       </c>
+      <c r="B10" s="28" t="s">
+        <v>169</v>
+      </c>
+      <c r="C10" s="29"/>
+      <c r="D10" s="30" t="s">
+        <v>170</v>
+      </c>
       <c r="E10" s="28" t="s">
         <v>20</v>
       </c>
-      <c r="F10" s="2" t="s">
-        <v>170</v>
+      <c r="F10" s="31" t="s">
+        <v>165</v>
       </c>
       <c r="G10" s="28" t="s">
         <v>29</v>
       </c>
+      <c r="H10" s="29" t="s">
+        <v>23</v>
+      </c>
+      <c r="I10" s="29" cm="1">
+        <f t="array" ref="I10">_xlfn.SWITCH(H10,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
+        <v>2</v>
+      </c>
       <c r="J10" s="28" t="s">
         <v>76</v>
       </c>
-    </row>
-    <row r="11" spans="1:12" ht="201" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="K10" s="30"/>
+      <c r="L10" s="30"/>
+    </row>
+    <row r="11" spans="1:13" ht="201" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="28">
         <v>14</v>
       </c>
+      <c r="B11" s="28" t="s">
+        <v>169</v>
+      </c>
+      <c r="C11" s="29"/>
+      <c r="D11" s="30" t="s">
+        <v>170</v>
+      </c>
       <c r="E11" s="28" t="s">
         <v>20</v>
       </c>
-      <c r="F11" s="2" t="s">
-        <v>171</v>
+      <c r="F11" s="31" t="s">
+        <v>166</v>
       </c>
       <c r="G11" s="28" t="s">
         <v>29</v>
       </c>
+      <c r="H11" s="29" t="s">
+        <v>27</v>
+      </c>
+      <c r="I11" s="29" cm="1">
+        <f t="array" ref="I11">_xlfn.SWITCH(H11,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
+        <v>3</v>
+      </c>
       <c r="J11" s="28" t="s">
         <v>76</v>
       </c>
-    </row>
-    <row r="12" spans="1:12" ht="201" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="K11" s="30"/>
+      <c r="L11" s="30"/>
+    </row>
+    <row r="12" spans="1:13" ht="201" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="28">
         <v>15</v>
       </c>
+      <c r="B12" s="28" t="s">
+        <v>169</v>
+      </c>
+      <c r="C12" s="29"/>
+      <c r="D12" s="30" t="s">
+        <v>170</v>
+      </c>
       <c r="E12" s="28" t="s">
         <v>20</v>
       </c>
-      <c r="F12" s="2" t="s">
-        <v>172</v>
+      <c r="F12" s="31" t="s">
+        <v>167</v>
       </c>
       <c r="G12" s="28" t="s">
         <v>29</v>
       </c>
+      <c r="H12" s="29" t="s">
+        <v>27</v>
+      </c>
+      <c r="I12" s="29" cm="1">
+        <f t="array" ref="I12">_xlfn.SWITCH(H12,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
+        <v>3</v>
+      </c>
       <c r="J12" s="28" t="s">
         <v>76</v>
       </c>
-    </row>
-    <row r="13" spans="1:12" ht="201" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="14" spans="1:12" ht="201" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="15" spans="1:12" ht="201" customHeight="1" x14ac:dyDescent="0.3"/>
+      <c r="K12" s="30"/>
+      <c r="L12" s="30"/>
+    </row>
+    <row r="13" spans="1:13" ht="201" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="14" spans="1:13" ht="201" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="15" spans="1:13" ht="201" customHeight="1" x14ac:dyDescent="0.3"/>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -18091,10 +18171,10 @@
         <v>160</v>
       </c>
       <c r="E13" s="27" t="s">
-        <v>161</v>
+        <v>168</v>
       </c>
       <c r="F13" s="2" t="s">
-        <v>162</v>
+        <v>167</v>
       </c>
     </row>
     <row r="14" spans="1:10" ht="216" customHeight="1" x14ac:dyDescent="0.3">
